--- a/hochschule/Hassine_3399727_Tätigkeitsnachweis.xlsx
+++ b/hochschule/Hassine_3399727_Tätigkeitsnachweis.xlsx
@@ -3029,7 +3029,7 @@
       <c r="A40" s="37" t="n"/>
       <c r="B40" s="104" t="inlineStr">
         <is>
-          <t>Beratung und Planung</t>
+          <t>Informatik und Software</t>
         </is>
       </c>
       <c r="C40" s="114" t="n"/>
@@ -3088,7 +3088,7 @@
       <c r="A43" s="37" t="n"/>
       <c r="B43" s="104" t="inlineStr">
         <is>
-          <t>Konstruktion</t>
+          <t>Beratung und Planung</t>
         </is>
       </c>
       <c r="C43" s="114" t="n"/>
@@ -6046,7 +6046,7 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="E82" s="68" t="n">
+      <c r="E82" s="97" t="n">
         <v>5</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -6087,7 +6087,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E83" s="68" t="n">
+      <c r="E83" s="97" t="n">
         <v>8.75</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="H84" s="67" t="inlineStr">
         <is>
-          <t>Ergonomische Grundmaße für den Arbeitsplatz zusammengetragen (Arbeitshöhe, Greifräume, Beleuchtung) und mit den Normvorgaben abgeglichen.</t>
+          <t>Mit dem digitalen Lagerbestand-System begonnen: Aufbau der Excel-Arbeitsmappe festgelegt und die Artikelliste mit Barcode, Bezeichnung, Profil, Maß, Material und Bestand angelegt.</t>
         </is>
       </c>
       <c r="I84" s="86" t="n"/>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="H102" s="61" t="inlineStr">
         <is>
-          <t>Erstes Layout-Konzept für den Platz gezeichnet und die Wege zwischen Tisch, Maschine und Materialablage geprüft.</t>
+          <t>Ergonomische Grundmaße für den Arbeitsplatz zusammengetragen (Arbeitshöhe, Greifräume, Beleuchtung) und mit den Normvorgaben abgeglichen.</t>
         </is>
       </c>
       <c r="I102" s="86" t="n"/>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="H103" s="67" t="inlineStr">
         <is>
-          <t>Zwei weitere Layout-Varianten entwickelt und die drei Konzepte nebeneinandergestellt.</t>
+          <t>Erstes Layout-Konzept für den Platz gezeichnet und die Wege zwischen Tisch, Maschine und Materialablage geprüft.</t>
         </is>
       </c>
       <c r="I103" s="86" t="n"/>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="H104" s="67" t="inlineStr">
         <is>
-          <t>Nutzwertanalyse für die Werkbank-Ausführung aufgestellt: Kriterien festgelegt und gewichtet.</t>
+          <t>Zweites Tabellenblatt für das Verlaufsprotokoll aufgebaut: jede Buchung wird mit Zeitstempel, Buchungsart und Mengenänderung festgehalten.</t>
         </is>
       </c>
       <c r="I104" s="86" t="n"/>
@@ -6683,7 +6683,7 @@
       </c>
       <c r="H105" s="67" t="inlineStr">
         <is>
-          <t>Nutzwertanalyse für das Layout-Konzept gerechnet und die Ergebnisse ausgewertet.</t>
+          <t>Zwei weitere Layout-Varianten entwickelt und die drei Konzepte nebeneinandergestellt.</t>
         </is>
       </c>
       <c r="I105" s="86" t="n"/>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="H109" s="94" t="inlineStr">
         <is>
-          <t>Kostenschätzung je Variante erstellt und der Nutzwertanalyse gegenübergestellt.</t>
+          <t>Nutzwertanalyse für die Werkbank-Ausführung aufgestellt: Kriterien festgelegt und gewichtet.</t>
         </is>
       </c>
       <c r="I109" s="86" t="n"/>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="H110" s="94" t="inlineStr">
         <is>
-          <t>5S-Konzept für den Schweißplatz ausgearbeitet: feste Plätze, Schattenbrett und Beschriftung festgelegt.</t>
+          <t>Erste VBA-Makros geschrieben: Ein- und Ausbuchen über ein Eingabefeld, Menge abfragen und Bestand fortschreiben.</t>
         </is>
       </c>
       <c r="I110" s="86" t="n"/>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="H111" s="94" t="inlineStr">
         <is>
-          <t>Aufteilung zwischen fester Station und mobilem Wagen festgelegt und je Werkzeug zugeordnet.</t>
+          <t>Nutzwertanalyse für das Layout-Konzept gerechnet und die Ergebnisse ausgewertet.</t>
         </is>
       </c>
       <c r="I111" s="86" t="n"/>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="H112" s="94" t="inlineStr">
         <is>
-          <t>Sicherheitsanforderungen recherchiert und den Maßnahmen zugeordnet (Absaugung, Schweißvorhang, PSA, Feuerlöscher).</t>
+          <t>Kostenschätzung je Variante erstellt und der Nutzwertanalyse gegenübergestellt.</t>
         </is>
       </c>
       <c r="I112" s="86" t="n"/>
@@ -6989,7 +6989,7 @@
       </c>
       <c r="H113" s="67" t="inlineStr">
         <is>
-          <t>Gefährdungsbeurteilung für den Schweißplatz aufgestellt und die Restrisiken bewertet.</t>
+          <t>Barcode-Suche umgesetzt: Der eingescannte Code springt zum Artikel und zeigt alle Felder im Dashboard an.</t>
         </is>
       </c>
       <c r="I113" s="86" t="n"/>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="H118" s="94" t="inlineStr">
         <is>
-          <t>Recherche zu Schweißtisch-Konzepten und Spannsystemen durchgeführt, Beispiele gesammelt und bewertet.</t>
+          <t>Dashboard als Bedienoberfläche gestaltet: Scannfunktionen links, Suchergebnis in der Mitte, Exportbereich rechts.</t>
         </is>
       </c>
       <c r="I118" s="86" t="n"/>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="H120" s="94" t="inlineStr">
         <is>
-          <t>Erste Handskizzen für den neuen Tisch angefertigt und mit dem Betreuer besprochen.</t>
+          <t>Recherche zu Schweißtisch-Konzepten und Spannsystemen durchgeführt, Beispiele gesammelt und bewertet.</t>
         </is>
       </c>
       <c r="I120" s="86" t="n"/>
@@ -7357,7 +7357,7 @@
       </c>
       <c r="H123" s="94" t="inlineStr">
         <is>
-          <t>Grundkonzept festgelegt: ausziehbarer Tisch mit Lochplatten-Spannsystem auf fahrbarem Untergestell.</t>
+          <t>Erste Handskizzen für den neuen Tisch angefertigt und mit dem Betreuer besprochen.</t>
         </is>
       </c>
       <c r="I123" s="86" t="n"/>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="H124" s="67" t="inlineStr">
         <is>
-          <t>Marktrecherche zu Lochplatten durchgeführt, Angebote verglichen und das D16-Raster ausgewählt.</t>
+          <t>Automatische Färbung des Bestands nach Soll- und Ist-Wert eingebaut, damit knapper Bestand sofort auffällt.</t>
         </is>
       </c>
       <c r="I124" s="86" t="n"/>
@@ -7424,7 +7424,7 @@
           <t>VA</t>
         </is>
       </c>
-      <c r="E125" s="68" t="n">
+      <c r="E125" s="97" t="n">
         <v>5.5</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="H125" s="67" t="inlineStr">
         <is>
-          <t>Mit der CAD-Konstruktion begonnen: Tischplatte mit Lochraster aufgebaut.</t>
+          <t>Grundkonzept festgelegt: ausziehbarer Tisch mit Lochplatten-Spannsystem auf fahrbarem Untergestell.</t>
         </is>
       </c>
       <c r="I125" s="86" t="n"/>
@@ -7465,7 +7465,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E126" s="68" t="n">
+      <c r="E126" s="97" t="n">
         <v>9.25</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="H126" s="67" t="inlineStr">
         <is>
-          <t>Oberteil konstruiert: Träger und Profile modelliert und die Teilenummern vergeben.</t>
+          <t>Marktrecherche zu Lochplatten durchgeführt, Angebote verglichen und das D16-Raster ausgewählt.</t>
         </is>
       </c>
       <c r="I126" s="86" t="n"/>
@@ -7521,7 +7521,7 @@
       </c>
       <c r="H127" s="67" t="inlineStr">
         <is>
-          <t>Unterteil konstruiert: Beine, Streben und Fußplatten aufgebaut.</t>
+          <t>Eigene Eingabemaske für das Anlegen neuer Artikel als UserForm erstellt und mit der Artikelliste verbunden.</t>
         </is>
       </c>
       <c r="I127" s="86" t="n"/>
@@ -7977,7 +7977,7 @@
       </c>
       <c r="H146" s="94" t="inlineStr">
         <is>
-          <t>Erweiterungssystem als Teleskop-Rahmen konstruiert, beidseitig ausziehbar.</t>
+          <t>Mit der CAD-Konstruktion begonnen: Tischplatte mit Lochraster aufgebaut.</t>
         </is>
       </c>
       <c r="I146" s="86" t="n"/>
@@ -8018,7 +8018,7 @@
       </c>
       <c r="H147" s="94" t="inlineStr">
         <is>
-          <t>Baugruppen zum Gesamtzusammenbau zusammengeführt und die Struktur geordnet.</t>
+          <t>Oberteil konstruiert: Träger und Profile modelliert und die Teilenummern vergeben.</t>
         </is>
       </c>
       <c r="I147" s="86" t="n"/>
@@ -8059,7 +8059,7 @@
       </c>
       <c r="H148" s="94" t="inlineStr">
         <is>
-          <t>Kollisionen und Verfahrwege im Modell geprüft und die Führungen angepasst.</t>
+          <t>Weitere Eingabemasken für Bearbeiten und Löschen ergänzt und eine Sicherheitsabfrage vor dem Löschen eingebaut.</t>
         </is>
       </c>
       <c r="I148" s="86" t="n"/>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="H149" s="94" t="inlineStr">
         <is>
-          <t>Erste Zeichnungsblätter abgeleitet und bemaßt.</t>
+          <t>Unterteil konstruiert: Beine, Streben und Fußplatten aufgebaut.</t>
         </is>
       </c>
       <c r="I149" s="86" t="n"/>
@@ -8203,7 +8203,7 @@
       </c>
       <c r="H152" s="94" t="inlineStr">
         <is>
-          <t>Weitere Einzelteilzeichnungen erstellt und die Schriftfelder ausgefüllt.</t>
+          <t>Erweiterungssystem als Teleskop-Rahmen konstruiert, beidseitig ausziehbar.</t>
         </is>
       </c>
       <c r="I152" s="86" t="n"/>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="H153" s="67" t="inlineStr">
         <is>
-          <t>Stücklisten der Baugruppen erstellt und die Zukaufteile gekennzeichnet.</t>
+          <t>Filterfunktion über Bezeichnung, Profil, Maß und Materialgruppe umgesetzt und getestet.</t>
         </is>
       </c>
       <c r="I153" s="86" t="n"/>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="H154" s="94" t="inlineStr">
         <is>
-          <t>Materialbedarf aus den Stücklisten abgeleitet und die Rohrlängen zusammengestellt.</t>
+          <t>Baugruppen zum Gesamtzusammenbau zusammengeführt und die Struktur geordnet.</t>
         </is>
       </c>
       <c r="I154" s="86" t="n"/>
@@ -8365,7 +8365,7 @@
       </c>
       <c r="H156" s="67" t="inlineStr">
         <is>
-          <t>Lenkrollen ausgelegt und gegen das errechnete Gesamtgewicht geprüft.</t>
+          <t>Kollisionen und Verfahrwege im Modell geprüft und die Führungen angepasst.</t>
         </is>
       </c>
       <c r="I156" s="86" t="n"/>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="H159" s="94" t="inlineStr">
         <is>
-          <t>Aufgabenstellung zum Schweißmaschinenwagen erhalten. Vorhandenen Wagen im Betrieb fotografiert und den Zustand aufgenommen.</t>
+          <t>Export auf Knopfdruck umgesetzt: ausgewählte Blätter als Excel- oder PDF-Datei in einen festen Zielordner speichern.</t>
         </is>
       </c>
       <c r="I159" s="86" t="n"/>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="H160" s="94" t="inlineStr">
         <is>
-          <t>Schweißgerät und Gasflasche vor Ort aufgemessen und die Maße in einer Handskizze festgehalten.</t>
+          <t>Aufgabenstellung zum Schweißmaschinenwagen erhalten. Vorhandenen Wagen im Betrieb fotografiert und den Zustand aufgenommen.</t>
         </is>
       </c>
       <c r="I160" s="86" t="n"/>
@@ -8550,7 +8550,7 @@
       </c>
       <c r="H161" s="94" t="inlineStr">
         <is>
-          <t>Vereinfachte CAD-Platzhalter für Gerät und Flasche erstellt, um den Bauraum abzubilden.</t>
+          <t>Schweißgerät und Gasflasche vor Ort aufgemessen und die Maße in einer Handskizze festgehalten.</t>
         </is>
       </c>
       <c r="I161" s="86" t="n"/>
@@ -8591,7 +8591,7 @@
       </c>
       <c r="H162" s="94" t="inlineStr">
         <is>
-          <t>Anforderungsliste aufgestellt: was der Wagen tragen und was er können muss.</t>
+          <t>Versand der Bestandsliste per E-Mail ergänzt und mit Testdaten geprüft.</t>
         </is>
       </c>
       <c r="I162" s="86" t="n"/>
@@ -8632,7 +8632,7 @@
       </c>
       <c r="H163" s="94" t="inlineStr">
         <is>
-          <t>Anforderungsliste auf 14 nummerierte Punkte gebracht und mit dem Betreuer abgestimmt.</t>
+          <t>Vereinfachte CAD-Platzhalter für Gerät und Flasche erstellt, um den Bauraum abzubilden.</t>
         </is>
       </c>
       <c r="I163" s="86" t="n"/>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="H166" s="94" t="inlineStr">
         <is>
-          <t>Referenzprojekte recherchiert und fünf Designrichtungen für den Wagen gesammelt.</t>
+          <t>Anforderungsliste aufgestellt: was der Wagen tragen und was er können muss.</t>
         </is>
       </c>
       <c r="I166" s="86" t="n"/>
@@ -8776,7 +8776,7 @@
       </c>
       <c r="H167" s="94" t="inlineStr">
         <is>
-          <t>Zwei erste Entwürfe im CAD aufgebaut und gegenübergestellt.</t>
+          <t>Einstellungsblatt angelegt, damit Zielordner, Empfängeradresse und Schwellenwerte ohne Eingriff in den Code änderbar sind.</t>
         </is>
       </c>
       <c r="I167" s="86" t="n"/>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="H168" s="94" t="inlineStr">
         <is>
-          <t>Maße und Ergonomie festgelegt, Gewicht des beladenen Wagens grob abgeschätzt.</t>
+          <t>Anforderungsliste auf 14 nummerierte Punkte gebracht und mit dem Betreuer abgestimmt.</t>
         </is>
       </c>
       <c r="I168" s="86" t="n"/>
@@ -8858,7 +8858,7 @@
       </c>
       <c r="H169" s="67" t="inlineStr">
         <is>
-          <t>Kompletten Neubau als Variante A konstruiert und einen Belegungsplan mit 16 Werkzeugpositionen erstellt.</t>
+          <t>Referenzprojekte recherchiert und fünf Designrichtungen für den Wagen gesammelt.</t>
         </is>
       </c>
       <c r="I169" s="86" t="n"/>
@@ -8899,7 +8899,7 @@
       </c>
       <c r="H170" s="94" t="inlineStr">
         <is>
-          <t>Beim Maßabgleich festgestellt, dass das geplante Gerätefach zu niedrig für die vorhandene Maschine ist.</t>
+          <t>Tablet-Modus entwickelt: Vollbild-Oberfläche ohne Excel-Bedienelemente, damit das System direkt in der Werkstatt bedienbar ist.</t>
         </is>
       </c>
       <c r="I170" s="86" t="n"/>
@@ -9316,7 +9316,7 @@
       </c>
       <c r="H188" s="94" t="inlineStr">
         <is>
-          <t>Als Variante B ein Aufsatzgestell entworfen, das über den vorhandenen Wagen fährt.</t>
+          <t>Zwei erste Entwürfe im CAD aufgebaut und gegenübergestellt.</t>
         </is>
       </c>
       <c r="I188" s="86" t="n"/>
@@ -9357,7 +9357,7 @@
       </c>
       <c r="H189" s="94" t="inlineStr">
         <is>
-          <t>Variante B überarbeitet, sodass die Gasflasche innerhalb der Aufstandsfläche steht.</t>
+          <t>Maße und Ergonomie festgelegt, Gewicht des beladenen Wagens grob abgeschätzt.</t>
         </is>
       </c>
       <c r="I189" s="86" t="n"/>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="H190" s="94" t="inlineStr">
         <is>
-          <t>Vorzugsvariante festgelegt: modularer Aufbau in vier Etagen.</t>
+          <t>Schwachstellen des Excel-Systems zusammengetragen: Bindung an einen Rechner, kein Mehrbenutzerbetrieb, Abhängigkeit von einer Person.</t>
         </is>
       </c>
       <c r="I190" s="86" t="n"/>
@@ -9439,7 +9439,7 @@
       </c>
       <c r="H191" s="94" t="inlineStr">
         <is>
-          <t>Etagen im CAD konstruiert: Aufnahme unten, zwei Schubladenetagen, Deckel mit Lochwand.</t>
+          <t>Kompletten Neubau als Variante A konstruiert und einen Belegungsplan mit 16 Werkzeugpositionen erstellt.</t>
         </is>
       </c>
       <c r="I191" s="86" t="n"/>
@@ -9480,7 +9480,7 @@
       </c>
       <c r="H192" s="94" t="inlineStr">
         <is>
-          <t>Zeichnungsblätter für die Einzelteile abgeleitet und bemaßt.</t>
+          <t>Beim Maßabgleich festgestellt, dass das geplante Gerätefach zu niedrig für die vorhandene Maschine ist.</t>
         </is>
       </c>
       <c r="I192" s="86" t="n"/>
@@ -9583,7 +9583,7 @@
       </c>
       <c r="H195" s="94" t="inlineStr">
         <is>
-          <t>Aufgabenstellung zum Zerspanarbeitsplatz erhalten und die Rahmenbedingungen aufgenommen (Drehen und Fräsen, drei Personen, eine Schicht).</t>
+          <t>Neuentwicklung als eigenständige Web-Anwendung mit dem Betreuer besprochen und die Architektur in drei Schichten festgelegt.</t>
         </is>
       </c>
       <c r="I195" s="86" t="n"/>
@@ -9624,7 +9624,7 @@
       </c>
       <c r="H196" s="94" t="inlineStr">
         <is>
-          <t>Bestehenden Platz besichtigt, Maschinen und vorhandene Ausstattung fotografiert.</t>
+          <t>Aufgabenstellung zum Zerspanarbeitsplatz erhalten und die Rahmenbedingungen aufgenommen (Drehen und Fräsen, drei Personen, eine Schicht).</t>
         </is>
       </c>
       <c r="I196" s="86" t="n"/>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="H197" s="94" t="inlineStr">
         <is>
-          <t>Werkzeugbedarf für das Drehen zusammengestellt.</t>
+          <t>Bestehenden Platz besichtigt, Maschinen und vorhandene Ausstattung fotografiert.</t>
         </is>
       </c>
       <c r="I197" s="86" t="n"/>
@@ -9706,7 +9706,7 @@
       </c>
       <c r="H198" s="94" t="inlineStr">
         <is>
-          <t>Werkzeugbedarf für das Fräsen sowie die Spann- und Aufspannmittel erfasst.</t>
+          <t>Datenmodell aus den Excel-Blättern abgeleitet und als Datenbanktabellen umgesetzt.</t>
         </is>
       </c>
       <c r="I198" s="86" t="n"/>
@@ -9848,7 +9848,7 @@
       </c>
       <c r="H202" s="94" t="inlineStr">
         <is>
-          <t>Mess- und Prüfmittel sowie Nacharbeit und Hilfsmittel ergänzt. Damit sind alle sechs Gruppen erfasst.</t>
+          <t>Werkzeugbedarf für das Drehen zusammengestellt.</t>
         </is>
       </c>
       <c r="I202" s="86" t="n"/>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="H203" s="94" t="inlineStr">
         <is>
-          <t>Mengen je Position festgelegt und begründet, welche Werkzeuge dreifach beschafft werden müssen.</t>
+          <t>Werkzeugbedarf für das Fräsen sowie die Spann- und Aufspannmittel erfasst.</t>
         </is>
       </c>
       <c r="I203" s="86" t="n"/>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="H204" s="67" t="inlineStr">
         <is>
-          <t>Preise recherchiert und die Werkzeugliste mit 35 Positionen bepreist.</t>
+          <t>Grundfunktionen portiert: Artikel anlegen, suchen, bearbeiten und löschen.</t>
         </is>
       </c>
       <c r="I204" s="86" t="n"/>
@@ -9971,7 +9971,7 @@
       </c>
       <c r="H205" s="99" t="inlineStr">
         <is>
-          <t>Kosten nach Kategorien ausgewertet und die teuersten Positionen herausgearbeitet.</t>
+          <t>Mess- und Prüfmittel sowie Nacharbeit und Hilfsmittel ergänzt. Damit sind alle sechs Gruppen erfasst.</t>
         </is>
       </c>
       <c r="I205" s="86" t="n"/>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="H206" s="67" t="inlineStr">
         <is>
-          <t>5S-Ordnung ausgearbeitet und die Werkzeuge den Zonen A, B und C zugeordnet.</t>
+          <t>Mengen je Position festgelegt und begründet, welche Werkzeuge dreifach beschafft werden müssen.</t>
         </is>
       </c>
       <c r="I206" s="86" t="n"/>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="H209" s="67" t="inlineStr">
         <is>
-          <t>Grundmaße der Werkbank festgelegt und mit den Ergonomienormen abgeglichen.</t>
+          <t>Buchungslogik und Verlaufsprotokoll übertragen und gegen das Excel-Original geprüft.</t>
         </is>
       </c>
       <c r="I209" s="86" t="n"/>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="H210" s="67" t="inlineStr">
         <is>
-          <t>Vier Bauvarianten skizziert und in 3D dargestellt: Aluprofil, Stahl-Standard, Systemmodule und Eigenbau.</t>
+          <t>Preise recherchiert und die Werkzeugliste mit 35 Positionen bepreist.</t>
         </is>
       </c>
       <c r="I210" s="86" t="n"/>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="H211" s="67" t="inlineStr">
         <is>
-          <t>Vier Layout-Konzepte entwickelt und die Vor- und Nachteile gegenübergestellt.</t>
+          <t>Kosten nach Kategorien ausgewertet und die teuersten Positionen herausgearbeitet.</t>
         </is>
       </c>
       <c r="I211" s="86" t="n"/>
@@ -10238,7 +10238,7 @@
       </c>
       <c r="H212" s="67" t="inlineStr">
         <is>
-          <t>Werkstatt-Grundriss maßstäblich gezeichnet und die Freiräume an den Maschinen geprüft.</t>
+          <t>Material-Entnahme mit Resteverwaltung in die neue Anwendung übernommen und mit denselben Beispielen nachgerechnet.</t>
         </is>
       </c>
       <c r="I212" s="86" t="n"/>
@@ -10279,7 +10279,7 @@
       </c>
       <c r="H213" s="67" t="inlineStr">
         <is>
-          <t>Nutzwertanalyse aufgestellt: sieben Kriterien festgelegt und gewichtet.</t>
+          <t>5S-Ordnung ausgearbeitet und die Werkzeuge den Zonen A, B und C zugeordnet.</t>
         </is>
       </c>
       <c r="I213" s="86" t="n"/>
@@ -10737,7 +10737,7 @@
       </c>
       <c r="H232" s="67" t="inlineStr">
         <is>
-          <t>Bestehende Rostschäden begutachtet und die Ursachen mit den Mitarbeitern besprochen (Feuchtigkeit, Kondenswasser, Lagerdauer).</t>
+          <t>86 reale Artikel-Datensätze und 50 Artikelgruppen aus dem Altsystem übernommen und die Übernahme kontrolliert.</t>
         </is>
       </c>
       <c r="I232" s="86" t="n"/>
@@ -10778,7 +10778,7 @@
       </c>
       <c r="H233" s="67" t="inlineStr">
         <is>
-          <t>Recherche zu Korrosionsschutzverfahren durchgeführt: Ölen, Wachsen, VCI-Folie und trockene Lagerung verglichen.</t>
+          <t>Bestehende Rostschäden begutachtet und die Ursachen mit den Mitarbeitern besprochen (Feuchtigkeit, Kondenswasser, Lagerdauer).</t>
         </is>
       </c>
       <c r="I233" s="86" t="n"/>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="H234" s="67" t="inlineStr">
         <is>
-          <t>Verfahren gegenübergestellt und nach Wirksamkeit, Aufwand und Kosten bewertet.</t>
+          <t>Recherche zu Korrosionsschutzverfahren durchgeführt: Ölen, Wachsen, VCI-Folie und trockene Lagerung verglichen.</t>
         </is>
       </c>
       <c r="I234" s="86" t="n"/>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="H235" s="67" t="inlineStr">
         <is>
-          <t>Konzept für eine geschlossene Lagerbox mit VCI-Schutz entworfen und die benötigten Maße aufgenommen.</t>
+          <t>Papierkorb und Löschabfrage eingebaut, um Bedienfehler abzufangen.</t>
         </is>
       </c>
       <c r="I235" s="86" t="n"/>
@@ -10963,7 +10963,7 @@
       </c>
       <c r="H238" s="67" t="inlineStr">
         <is>
-          <t>Lagerbox im CAD konstruiert und die Aufteilung für die verschiedenen Profillängen festgelegt.</t>
+          <t>Verfahren gegenübergestellt und nach Wirksamkeit, Aufwand und Kosten bewertet.</t>
         </is>
       </c>
       <c r="I238" s="86" t="n"/>
@@ -11004,7 +11004,7 @@
       </c>
       <c r="H239" s="67" t="inlineStr">
         <is>
-          <t>Material- und Kostenaufstellung für die Schutzbox erstellt.</t>
+          <t>Konzept für eine geschlossene Lagerbox mit VCI-Schutz entworfen und die benötigten Maße aufgenommen.</t>
         </is>
       </c>
       <c r="I239" s="86" t="n"/>
@@ -11045,7 +11045,7 @@
       </c>
       <c r="H240" s="67" t="inlineStr">
         <is>
-          <t>Zeitersparnis durch den Wegfall des Nacharbeitens abgeschätzt und der Investition gegenübergestellt.</t>
+          <t>Oberfläche überarbeitet: Suche, Filter und Bestandsanzeige übersichtlicher angeordnet.</t>
         </is>
       </c>
       <c r="I240" s="86" t="n"/>
@@ -11086,7 +11086,7 @@
       </c>
       <c r="H241" s="67" t="inlineStr">
         <is>
-          <t>Arbeitsanweisung für die Einlagerung und Entnahme der Schienenprofile entworfen.</t>
+          <t>Lagerbox im CAD konstruiert und die Aufteilung für die verschiedenen Profillängen festgelegt.</t>
         </is>
       </c>
       <c r="I241" s="86" t="n"/>
@@ -11127,7 +11127,7 @@
       </c>
       <c r="H242" s="67" t="inlineStr">
         <is>
-          <t>Rostschutz-Konzept zusammengeschrieben, dem Betreuer vorgestellt und die Praktikumsunterlagen abschließend sortiert.</t>
+          <t>Material- und Kostenaufstellung für die Schutzbox erstellt.</t>
         </is>
       </c>
       <c r="I242" s="86" t="n"/>
@@ -11446,7 +11446,7 @@
         <v/>
       </c>
       <c r="D254" s="65" t="n"/>
-      <c r="E254" s="68" t="n"/>
+      <c r="E254" s="97" t="n"/>
       <c r="F254" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -11473,7 +11473,7 @@
         <v/>
       </c>
       <c r="D255" s="65" t="n"/>
-      <c r="E255" s="68" t="n"/>
+      <c r="E255" s="97" t="n"/>
       <c r="F255" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -12516,7 +12516,7 @@
         <v/>
       </c>
       <c r="D297" s="65" t="n"/>
-      <c r="E297" s="68" t="n"/>
+      <c r="E297" s="97" t="n"/>
       <c r="F297" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -12543,7 +12543,7 @@
         <v/>
       </c>
       <c r="D298" s="65" t="n"/>
-      <c r="E298" s="68" t="n"/>
+      <c r="E298" s="97" t="n"/>
       <c r="F298" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -13586,7 +13586,7 @@
         <v/>
       </c>
       <c r="D340" s="65" t="n"/>
-      <c r="E340" s="68" t="n"/>
+      <c r="E340" s="97" t="n"/>
       <c r="F340" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -13613,7 +13613,7 @@
         <v/>
       </c>
       <c r="D341" s="65" t="n"/>
-      <c r="E341" s="68" t="n"/>
+      <c r="E341" s="97" t="n"/>
       <c r="F341" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -14656,7 +14656,7 @@
         <v/>
       </c>
       <c r="D383" s="45" t="n"/>
-      <c r="E383" s="47" t="n"/>
+      <c r="E383" s="96" t="n"/>
       <c r="F383" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -14683,7 +14683,7 @@
         <v/>
       </c>
       <c r="D384" s="45" t="n"/>
-      <c r="E384" s="47" t="n"/>
+      <c r="E384" s="96" t="n"/>
       <c r="F384" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -15726,7 +15726,7 @@
         <v/>
       </c>
       <c r="D426" s="45" t="n"/>
-      <c r="E426" s="47" t="n"/>
+      <c r="E426" s="96" t="n"/>
       <c r="F426" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -15753,7 +15753,7 @@
         <v/>
       </c>
       <c r="D427" s="45" t="n"/>
-      <c r="E427" s="47" t="n"/>
+      <c r="E427" s="96" t="n"/>
       <c r="F427" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -16796,7 +16796,7 @@
         <v/>
       </c>
       <c r="D469" s="45" t="n"/>
-      <c r="E469" s="47" t="n"/>
+      <c r="E469" s="96" t="n"/>
       <c r="F469" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -16823,7 +16823,7 @@
         <v/>
       </c>
       <c r="D470" s="45" t="n"/>
-      <c r="E470" s="47" t="n"/>
+      <c r="E470" s="96" t="n"/>
       <c r="F470" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -17866,7 +17866,7 @@
         <v/>
       </c>
       <c r="D512" s="45" t="n"/>
-      <c r="E512" s="47" t="n"/>
+      <c r="E512" s="96" t="n"/>
       <c r="F512" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -17893,7 +17893,7 @@
         <v/>
       </c>
       <c r="D513" s="45" t="n"/>
-      <c r="E513" s="47" t="n"/>
+      <c r="E513" s="96" t="n"/>
       <c r="F513" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -18936,7 +18936,7 @@
         <v/>
       </c>
       <c r="D555" s="45" t="n"/>
-      <c r="E555" s="47" t="n"/>
+      <c r="E555" s="96" t="n"/>
       <c r="F555" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -18963,7 +18963,7 @@
         <v/>
       </c>
       <c r="D556" s="45" t="n"/>
-      <c r="E556" s="47" t="n"/>
+      <c r="E556" s="96" t="n"/>
       <c r="F556" s="2" t="inlineStr">
         <is>
           <t>h</t>

--- a/hochschule/Hassine_3399727_Tätigkeitsnachweis.xlsx
+++ b/hochschule/Hassine_3399727_Tätigkeitsnachweis.xlsx
@@ -3823,7 +3823,7 @@
       </c>
       <c r="H17" s="67" t="inlineStr">
         <is>
-          <t>Unterweisung an den Maschinen und Arbeitsplätzen durch den Betreuer (Dreh- und Fräsmaschine, Schweißplätze, Trennschleifer). Persönliche Schutzausrüstung erhalten und angepasst.</t>
+          <t>Unterweisung an den Maschinen und Arbeitsplätzen durch den Betreuer. Persönliche Schutzausrüstung erhalten, Arbeitsplatz und Rechner eingerichtet, Zugänge zur CAD-Software und zu den Netzlaufwerken angelegt.</t>
         </is>
       </c>
       <c r="I17" s="86" t="n"/>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="H18" s="67" t="inlineStr">
         <is>
-          <t>Arbeitsplatz und Rechner eingerichtet, Zugänge zur CAD-Software und zu den Netzlaufwerken eingerichtet. Ablagestruktur für die Praktikumsdokumentation angelegt.</t>
+          <t>Aufgaben des Praxissemesters mit dem Betreuer besprochen und zeitlich eingeordnet. Abläufe von der Auftragsannahme bis zur Auslieferung kennengelernt und bei laufenden Arbeiten in der Werkstatt mitgeholfen.</t>
         </is>
       </c>
       <c r="I18" s="86" t="n"/>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="H19" s="94" t="inlineStr">
         <is>
-          <t>Aufgaben des Praxissemesters mit dem Betreuer besprochen und die fünf Themen zeitlich grob eingeordnet. Abläufe von der Auftragsannahme bis zur Auslieferung erklärt bekommen.</t>
+          <t>Aufgabenstellung zum Schraubenlager erhalten und mit dem Betreuer besprochen. Das neue Regal im Keller angeschaut und vermessen (6 Fächer, je 930 × 500 mm), Ausgangszustand fotografiert.</t>
         </is>
       </c>
       <c r="I19" s="86" t="n"/>
@@ -3949,7 +3949,7 @@
       </c>
       <c r="H20" s="67" t="inlineStr">
         <is>
-          <t>Bei laufenden Arbeiten in der Werkstatt zugesehen und mitgeholfen, um Material, Werkzeuge und die üblichen Arbeitsschritte kennenzulernen. Erste Fotos für die Dokumentation gemacht.</t>
+          <t>Bestandsaufnahme begonnen: Zylinderkopf- und Sechskantschrauben nach Gewinde (M5–M20) und Länge erfasst. Matrix-Struktur Gewinde × Länge in Excel angelegt.</t>
         </is>
       </c>
       <c r="I20" s="86" t="n"/>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="H23" s="94" t="inlineStr">
         <is>
-          <t>Aufgabenstellung zum Schraubenlager erhalten und mit dem Betreuer besprochen. Das neue Regal im Keller angeschaut und vermessen (6 Fächer, je 930 × 500 mm).</t>
+          <t>Bestandsaufnahme mit Holz- und Schloßschrauben abgeschlossen. Insgesamt 135 Sorten erfasst; beim Gegenprüfen drei Rechenfehler in den Ausgangsdateien gefunden und korrigiert.</t>
         </is>
       </c>
       <c r="I23" s="86" t="n"/>
@@ -4097,7 +4097,7 @@
       </c>
       <c r="H24" s="67" t="inlineStr">
         <is>
-          <t>Ausgangszustand des bestehenden Lagers fotografiert und dokumentiert. Vorhandene Behälter und das Bito-Box-Prinzip erfasst.</t>
+          <t>Bestand ausgewertet: Verteilung nach Typ, Gewindegröße und Länge zusammengestellt und eine ABC-Analyse durchgeführt. Schwerpunkt bei M8 und M10, daraus die drei Boxgrößen S, M und L abgeleitet.</t>
         </is>
       </c>
       <c r="I24" s="86" t="n"/>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="H25" s="94" t="inlineStr">
         <is>
-          <t>Bestandsaufnahme begonnen: Zylinderkopfschrauben nach Gewinde (M5–M20) und Länge erfasst. Matrix-Struktur Gewinde × Länge in Excel angelegt.</t>
+          <t>Ordnungskonzepte für die vier Schraubentypen erstellt: je Typ die vollständige Matrix aufgebaut und zwei Schubladenvarianten entwickelt und verglichen.</t>
         </is>
       </c>
       <c r="I25" s="86" t="n"/>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="H26" s="94" t="inlineStr">
         <is>
-          <t>Bestandsaufnahme der Zylinderkopfschrauben abgeschlossen und die Werte stichprobenartig gegengeprüft.</t>
+          <t>Alle vier Typen in einer Gesamtmatrix zusammengeführt, Schubladeneinteilung nach Länge festgelegt und den Gesamtbedarf ermittelt: 14 kleine, 81 mittlere und 40 große Behälter.</t>
         </is>
       </c>
       <c r="I26" s="86" t="n"/>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="H27" s="67" t="inlineStr">
         <is>
-          <t>Sechskantschrauben nach Gewinde und Länge aufgenommen und in die Matrix eingetragen.</t>
+          <t>Boxen- und Regallayout geplant: Rastermaß 100 mm festgelegt, Boxgrößen mit 102, 115 und 145 mm definiert und die Anzahl Boxen je Fach mit den Regalmaßen abgeglichen.</t>
         </is>
       </c>
       <c r="I27" s="86" t="n"/>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="H30" s="94" t="inlineStr">
         <is>
-          <t>Holzschrauben aufgenommen und eingetragen. Sortiment auf Doppelungen und nicht mehr verwendete Größen geprüft.</t>
+          <t>Behälter und Fach-Varianten im CAD konstruiert (12 bis 27 Boxen je Fach) und daraus drei komplette Regalvarianten mit 144, 156 und 162 Boxplätzen aufgebaut.</t>
         </is>
       </c>
       <c r="I30" s="86" t="n"/>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="H31" s="94" t="inlineStr">
         <is>
-          <t>Schloßschrauben aufgenommen. Damit sind alle vier Schraubentypen erfasst — insgesamt 135 Sorten.</t>
+          <t>Nutzwertanalyse der drei Regalvarianten aufgestellt und gewichtet, Kapazitätsnachweis gerechnet (144 Plätze für 135 Sorten) und die Variante S · M · L als Empfehlung begründet.</t>
         </is>
       </c>
       <c r="I31" s="86" t="n"/>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="H32" s="94" t="inlineStr">
         <is>
-          <t>Beim Prüfen der Aufnahmedaten drei Rechenfehler in den Ausgangsdateien gefunden und korrigiert.</t>
+          <t>Belegungsplan erstellt: jeder der 135 Sorten einen festen, beschrifteten Platz zugeordnet. Bezugsquellen recherchiert, Ergebnisse dem Betreuer vorgestellt und eine Arbeitsanweisung für die Materialentnahme entworfen.</t>
         </is>
       </c>
       <c r="I32" s="86" t="n"/>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="H33" s="94" t="inlineStr">
         <is>
-          <t>Bestand ausgewertet: Verteilung nach Schraubentyp, Gewindegröße und Länge zusammengestellt.</t>
+          <t>Mit dem digitalen Lagerbestand-System begonnen: Aufbau der Excel-Arbeitsmappe festgelegt und die Artikelliste mit Barcode, Bezeichnung, Profil, Maß, Material und Bestand angelegt.</t>
         </is>
       </c>
       <c r="I33" s="86" t="n"/>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="H37" s="67" t="inlineStr">
         <is>
-          <t>ABC-Analyse durchgeführt (Schwerpunkt M8 und M10) und daraus die drei Boxgrößen S, M und L abgeleitet.</t>
+          <t>Zweites Tabellenblatt für das Verlaufsprotokoll aufgebaut: jede Buchung wird mit Zeitstempel, Buchungsart und Mengenänderung festgehalten.</t>
         </is>
       </c>
       <c r="I37" s="86" t="n"/>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H38" s="67" t="inlineStr">
         <is>
-          <t>Ordnungskonzept für die Zylinderkopfschrauben erstellt: vollständige Matrix aufgebaut sowie zwei Schubladenvarianten entwickelt und verglichen.</t>
+          <t>Erste VBA-Makros geschrieben: Ein- und Ausbuchen über ein Eingabefeld, Menge abfragen und Bestand fortschreiben.</t>
         </is>
       </c>
       <c r="I38" s="86" t="n"/>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="H39" s="95" t="inlineStr">
         <is>
-          <t>Ordnungskonzept für die Sechskantschrauben erstellt und die Varianten gegenübergestellt.</t>
+          <t>Barcode-Suche umgesetzt: Der eingescannte Code springt zum Artikel und zeigt alle Felder im Dashboard an.</t>
         </is>
       </c>
       <c r="I39" s="86" t="n"/>
@@ -4724,7 +4724,7 @@
       </c>
       <c r="H40" s="94" t="inlineStr">
         <is>
-          <t>Ordnungskonzept für die Holzschrauben erstellt.</t>
+          <t>Dashboard als Bedienoberfläche gestaltet: Scannfunktionen links, Suchergebnis in der Mitte, Exportbereich rechts.</t>
         </is>
       </c>
       <c r="I40" s="86" t="n"/>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="H41" s="67" t="inlineStr">
         <is>
-          <t>Ordnungskonzept für die Schloßschrauben erstellt. Damit sind alle vier Typen einzeln durchgeplant.</t>
+          <t>Automatische Färbung des Bestands nach Soll- und Ist-Wert eingebaut, damit knapper Bestand sofort auffällt.</t>
         </is>
       </c>
       <c r="I41" s="86" t="n"/>
@@ -5182,7 +5182,7 @@
       </c>
       <c r="H59" s="94" t="inlineStr">
         <is>
-          <t>Alle vier Typen in einer Gesamtmatrix zusammengeführt und die Schubladeneinteilung nach Länge festgelegt.</t>
+          <t>Eigene Eingabemaske für das Anlegen neuer Artikel als UserForm erstellt und mit der Artikelliste verbunden.</t>
         </is>
       </c>
       <c r="I59" s="86" t="n"/>
@@ -5223,7 +5223,7 @@
       </c>
       <c r="H60" s="94" t="inlineStr">
         <is>
-          <t>Gesamtbedarf an Boxen ermittelt: 14 kleine, 81 mittlere und 40 große Behälter.</t>
+          <t>Weitere Eingabemasken für Bearbeiten und Löschen ergänzt und eine Sicherheitsabfrage vor dem Löschen eingebaut.</t>
         </is>
       </c>
       <c r="I60" s="86" t="n"/>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="H61" s="94" t="inlineStr">
         <is>
-          <t>Boxen- und Regallayout geplant: Rastermaß 100 mm festgelegt, Boxgrößen S/M/L mit 102, 115 und 145 mm definiert.</t>
+          <t>Filterfunktion über Bezeichnung, Profil, Maß und Materialgruppe umgesetzt und getestet.</t>
         </is>
       </c>
       <c r="I61" s="86" t="n"/>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="H62" s="94" t="inlineStr">
         <is>
-          <t>Anzahl der Boxen je Fach skizziert und mit den gemessenen Regalmaßen abgeglichen.</t>
+          <t>Export auf Knopfdruck umgesetzt: ausgewählte Blätter als Excel- oder PDF-Datei in einen festen Zielordner speichern.</t>
         </is>
       </c>
       <c r="I62" s="86" t="n"/>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="H67" s="94" t="inlineStr">
         <is>
-          <t>Mit der CAD-Konstruktion begonnen und die drei Boxgrößen als Modelle aufgebaut.</t>
+          <t>Versand der Bestandsliste per E-Mail ergänzt und mit Testdaten geprüft.</t>
         </is>
       </c>
       <c r="I67" s="86" t="n"/>
@@ -5527,7 +5527,7 @@
       </c>
       <c r="H68" s="94" t="inlineStr">
         <is>
-          <t>Fach-Varianten im CAD konstruiert, von 12 bis 27 Boxen je Fach.</t>
+          <t>Einstellungsblatt angelegt, damit Zielordner, Empfängeradresse und Schwellenwerte ohne Eingriff in den Code änderbar sind.</t>
         </is>
       </c>
       <c r="I68" s="86" t="n"/>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="H69" s="94" t="inlineStr">
         <is>
-          <t>Drei komplette Regalvarianten modelliert und die Boxplätze gezählt (144, 156 und 162 Plätze).</t>
+          <t>Tablet-Modus entwickelt: Vollbild-Oberfläche ohne Excel-Bedienelemente, damit das System direkt in der Werkstatt bedienbar ist.</t>
         </is>
       </c>
       <c r="I69" s="86" t="n"/>
@@ -5609,7 +5609,7 @@
       </c>
       <c r="H70" s="67" t="inlineStr">
         <is>
-          <t>Kapazitätsnachweis gerechnet: 144 Plätze reichen für die 135 erfassten Sorten.</t>
+          <t>Entwicklermodus ergänzt, der die Excel-Oberfläche für Wartungsarbeiten wieder einblendet, und mit einem Kennwort geschützt.</t>
         </is>
       </c>
       <c r="I70" s="86" t="n"/>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="H73" s="94" t="inlineStr">
         <is>
-          <t>Aufgabenstellung zum Schweißarbeitsplatz erhalten. Bestehenden Platz besichtigt, fotografiert und die verfügbare Fläche aufgemessen (rund 29 m²).</t>
+          <t>Makros in Modulgruppen aufgeteilt und benannt, damit die Datei wartbar bleibt und Funktionen wiederverwendet werden können.</t>
         </is>
       </c>
       <c r="I73" s="86" t="n"/>
@@ -5753,7 +5753,7 @@
       </c>
       <c r="H74" s="94" t="inlineStr">
         <is>
-          <t>Verwendete Schweißverfahren mit dem Betreuer besprochen (MAG/MIG und E-Hand) und die Unterschiede für die spätere Ausstattung festgehalten.</t>
+          <t>Material-Entnahme-Logik entworfen: Beim Zuschnitt soll die Restlänge selbstständig eingebucht werden.</t>
         </is>
       </c>
       <c r="I74" s="86" t="n"/>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="H75" s="94" t="inlineStr">
         <is>
-          <t>Aufnahme der vorhandenen Werkzeuge am Schweißplatz begonnen und nach Verwendungszweck gruppiert.</t>
+          <t>Material-Entnahme umgesetzt: Restlängen werden automatisch angelegt oder mit vorhandenen gleich langen Resten zusammengefasst.</t>
         </is>
       </c>
       <c r="I75" s="86" t="n"/>
@@ -5835,7 +5835,7 @@
       </c>
       <c r="H76" s="94" t="inlineStr">
         <is>
-          <t>Werkzeugaufnahme fortgesetzt: Kategorien Schweißen MAG/MIG und Schweißen E-Hand vollständig erfasst.</t>
+          <t>Material-Entnahme mit realen Zuschnitten aus der Werkstatt getestet und zwei Fehler bei der Restberechnung behoben.</t>
         </is>
       </c>
       <c r="I76" s="86" t="n"/>
@@ -5876,7 +5876,7 @@
       </c>
       <c r="H77" s="67" t="inlineStr">
         <is>
-          <t>Kategorien Spannen und Fixieren sowie Nachbearbeitung erfasst und mit den Mitarbeitern auf Vollständigkeit geprüft.</t>
+          <t>System einem Mitarbeiter gezeigt, Rückmeldungen aufgenommen und die Bedienung an zwei Stellen vereinfacht.</t>
         </is>
       </c>
       <c r="I77" s="86" t="n"/>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="H80" s="67" t="inlineStr">
         <is>
-          <t>Kategorien Anreißen und Messen sowie persönliche Schutzausrüstung für drei Personen zusammengestellt.</t>
+          <t>Kurzanleitung für die Bedienung des Lagerbestand-Systems geschrieben und an den Arbeitsplatz gelegt.</t>
         </is>
       </c>
       <c r="I80" s="86" t="n"/>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="H81" s="67" t="inlineStr">
         <is>
-          <t>Kategorien Sicherheit und Umgebung, Verbrauchsmaterial sowie 5S-Möbel ergänzt. Damit sind alle neun Werkzeugkategorien A bis I erfasst.</t>
+          <t>Schwachstellen des Excel-Systems zusammengetragen (Bindung an einen Rechner, kein Mehrbenutzerbetrieb) und die Neuentwicklung als eigenständige Web-Anwendung mit dem Betreuer besprochen. Architektur in drei Schichten festgelegt und mit KI-Unterstützung aufgesetzt.</t>
         </is>
       </c>
       <c r="I81" s="86" t="n"/>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="H82" s="67" t="inlineStr">
         <is>
-          <t>Marktrecherche zu den Werkzeugen begonnen und Richtpreise je Position gesammelt.</t>
+          <t>Datenmodell aus den Excel-Blättern übernommen und die Kernfunktionen portiert: Artikel verwalten, Buchungen, Verlauf und die Material-Entnahme mit Resteverwaltung. 86 reale Artikel-Datensätze und 50 Artikelgruppen übernommen und die Übernahme kontrolliert.</t>
         </is>
       </c>
       <c r="I82" s="86" t="n"/>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="H83" s="67" t="inlineStr">
         <is>
-          <t>Marktrecherche abgeschlossen und je Kaufteil drei Preisstufen gegenübergestellt.</t>
+          <t>Anwendung als Hintergrunddienst mit täglichem Backup eingerichtet und zusätzlich in der Cloud bereitgestellt. Lasttest mit 100 gleichzeitigen Schreibzugriffen durchgeführt und die Bedienung dokumentiert.</t>
         </is>
       </c>
       <c r="I83" s="86" t="n"/>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="H84" s="67" t="inlineStr">
         <is>
-          <t>Mit dem digitalen Lagerbestand-System begonnen: Aufbau der Excel-Arbeitsmappe festgelegt und die Artikelliste mit Barcode, Bezeichnung, Profil, Maß, Material und Bestand angelegt.</t>
+          <t>Aufgabenstellung zum Schweißarbeitsplatz erhalten. Bestehenden Platz besichtigt, fotografiert und die verfügbare Fläche aufgemessen (rund 29 m²).</t>
         </is>
       </c>
       <c r="I84" s="86" t="n"/>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="H102" s="61" t="inlineStr">
         <is>
-          <t>Ergonomische Grundmaße für den Arbeitsplatz zusammengetragen (Arbeitshöhe, Greifräume, Beleuchtung) und mit den Normvorgaben abgeglichen.</t>
+          <t>Verwendete Schweißverfahren mit dem Betreuer besprochen (MAG/MIG und E-Hand) und die Unterschiede für die spätere Ausstattung festgehalten.</t>
         </is>
       </c>
       <c r="I102" s="86" t="n"/>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="H103" s="67" t="inlineStr">
         <is>
-          <t>Erstes Layout-Konzept für den Platz gezeichnet und die Wege zwischen Tisch, Maschine und Materialablage geprüft.</t>
+          <t>Aufnahme der vorhandenen Werkzeuge am Schweißplatz begonnen und nach Verwendungszweck gruppiert.</t>
         </is>
       </c>
       <c r="I103" s="86" t="n"/>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="H104" s="67" t="inlineStr">
         <is>
-          <t>Zweites Tabellenblatt für das Verlaufsprotokoll aufgebaut: jede Buchung wird mit Zeitstempel, Buchungsart und Mengenänderung festgehalten.</t>
+          <t>Werkzeugaufnahme fortgesetzt: Kategorien Schweißen MAG/MIG und Schweißen E-Hand vollständig erfasst.</t>
         </is>
       </c>
       <c r="I104" s="86" t="n"/>
@@ -6683,7 +6683,7 @@
       </c>
       <c r="H105" s="67" t="inlineStr">
         <is>
-          <t>Zwei weitere Layout-Varianten entwickelt und die drei Konzepte nebeneinandergestellt.</t>
+          <t>Kategorien Spannen und Fixieren sowie Nachbearbeitung erfasst und mit den Mitarbeitern auf Vollständigkeit geprüft.</t>
         </is>
       </c>
       <c r="I105" s="86" t="n"/>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="H109" s="94" t="inlineStr">
         <is>
-          <t>Nutzwertanalyse für die Werkbank-Ausführung aufgestellt: Kriterien festgelegt und gewichtet.</t>
+          <t>Kategorien Anreißen und Messen sowie persönliche Schutzausrüstung für drei Personen zusammengestellt.</t>
         </is>
       </c>
       <c r="I109" s="86" t="n"/>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="H110" s="94" t="inlineStr">
         <is>
-          <t>Erste VBA-Makros geschrieben: Ein- und Ausbuchen über ein Eingabefeld, Menge abfragen und Bestand fortschreiben.</t>
+          <t>Kategorien Sicherheit und Umgebung, Verbrauchsmaterial sowie 5S-Möbel ergänzt. Damit sind alle neun Werkzeugkategorien A bis I erfasst.</t>
         </is>
       </c>
       <c r="I110" s="86" t="n"/>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="H111" s="94" t="inlineStr">
         <is>
-          <t>Nutzwertanalyse für das Layout-Konzept gerechnet und die Ergebnisse ausgewertet.</t>
+          <t>Marktrecherche zu den Werkzeugen begonnen und Richtpreise je Position gesammelt.</t>
         </is>
       </c>
       <c r="I111" s="86" t="n"/>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="H112" s="94" t="inlineStr">
         <is>
-          <t>Kostenschätzung je Variante erstellt und der Nutzwertanalyse gegenübergestellt.</t>
+          <t>Marktrecherche abgeschlossen und je Kaufteil drei Preisstufen gegenübergestellt.</t>
         </is>
       </c>
       <c r="I112" s="86" t="n"/>
@@ -6989,7 +6989,7 @@
       </c>
       <c r="H113" s="67" t="inlineStr">
         <is>
-          <t>Barcode-Suche umgesetzt: Der eingescannte Code springt zum Artikel und zeigt alle Felder im Dashboard an.</t>
+          <t>Ergonomische Grundmaße für den Arbeitsplatz zusammengetragen (Arbeitshöhe, Greifräume, Beleuchtung) und mit den Normvorgaben abgeglichen.</t>
         </is>
       </c>
       <c r="I113" s="86" t="n"/>
@@ -7092,7 +7092,7 @@
       </c>
       <c r="H116" s="94" t="inlineStr">
         <is>
-          <t>Aufgabenstellung zum neuen Schweißtisch erhalten. Anforderungen mit dem Betreuer gesammelt: Größe, Spannmöglichkeiten, Fahrbarkeit.</t>
+          <t>Erstes Layout-Konzept für den Platz gezeichnet und die Wege zwischen Tisch, Maschine und Materialablage geprüft.</t>
         </is>
       </c>
       <c r="I116" s="86" t="n"/>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="H117" s="94" t="inlineStr">
         <is>
-          <t>Vorhandenen Tisch vermessen und die Schwachstellen im Betrieb aufgenommen.</t>
+          <t>Zwei weitere Layout-Varianten entwickelt und die drei Konzepte nebeneinandergestellt.</t>
         </is>
       </c>
       <c r="I117" s="86" t="n"/>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="H118" s="94" t="inlineStr">
         <is>
-          <t>Dashboard als Bedienoberfläche gestaltet: Scannfunktionen links, Suchergebnis in der Mitte, Exportbereich rechts.</t>
+          <t>Nutzwertanalyse für die Werkbank-Ausführung aufgestellt: Kriterien festgelegt und gewichtet.</t>
         </is>
       </c>
       <c r="I118" s="86" t="n"/>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="H120" s="94" t="inlineStr">
         <is>
-          <t>Recherche zu Schweißtisch-Konzepten und Spannsystemen durchgeführt, Beispiele gesammelt und bewertet.</t>
+          <t>Nutzwertanalyse für das Layout-Konzept gerechnet und die Ergebnisse ausgewertet.</t>
         </is>
       </c>
       <c r="I120" s="86" t="n"/>
@@ -7357,7 +7357,7 @@
       </c>
       <c r="H123" s="94" t="inlineStr">
         <is>
-          <t>Erste Handskizzen für den neuen Tisch angefertigt und mit dem Betreuer besprochen.</t>
+          <t>Kostenschätzung je Variante erstellt und der Nutzwertanalyse gegenübergestellt.</t>
         </is>
       </c>
       <c r="I123" s="86" t="n"/>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="H124" s="67" t="inlineStr">
         <is>
-          <t>Automatische Färbung des Bestands nach Soll- und Ist-Wert eingebaut, damit knapper Bestand sofort auffällt.</t>
+          <t>Aufgabenstellung zum neuen Schweißtisch erhalten. Anforderungen mit dem Betreuer gesammelt: Größe, Spannmöglichkeiten, Fahrbarkeit.</t>
         </is>
       </c>
       <c r="I124" s="86" t="n"/>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="H125" s="67" t="inlineStr">
         <is>
-          <t>Grundkonzept festgelegt: ausziehbarer Tisch mit Lochplatten-Spannsystem auf fahrbarem Untergestell.</t>
+          <t>Vorhandenen Tisch vermessen und die Schwachstellen im Betrieb aufgenommen.</t>
         </is>
       </c>
       <c r="I125" s="86" t="n"/>
@@ -7480,7 +7480,7 @@
       </c>
       <c r="H126" s="67" t="inlineStr">
         <is>
-          <t>Marktrecherche zu Lochplatten durchgeführt, Angebote verglichen und das D16-Raster ausgewählt.</t>
+          <t>Recherche zu Schweißtisch-Konzepten und Spannsystemen durchgeführt, Beispiele gesammelt und bewertet.</t>
         </is>
       </c>
       <c r="I126" s="86" t="n"/>
@@ -7521,7 +7521,7 @@
       </c>
       <c r="H127" s="67" t="inlineStr">
         <is>
-          <t>Eigene Eingabemaske für das Anlegen neuer Artikel als UserForm erstellt und mit der Artikelliste verbunden.</t>
+          <t>Erste Handskizzen für den neuen Tisch angefertigt und mit dem Betreuer besprochen.</t>
         </is>
       </c>
       <c r="I127" s="86" t="n"/>
@@ -7977,7 +7977,7 @@
       </c>
       <c r="H146" s="94" t="inlineStr">
         <is>
-          <t>Mit der CAD-Konstruktion begonnen: Tischplatte mit Lochraster aufgebaut.</t>
+          <t>Grundkonzept festgelegt: ausziehbarer Tisch mit Lochplatten-Spannsystem auf fahrbarem Untergestell.</t>
         </is>
       </c>
       <c r="I146" s="86" t="n"/>
@@ -8018,7 +8018,7 @@
       </c>
       <c r="H147" s="94" t="inlineStr">
         <is>
-          <t>Oberteil konstruiert: Träger und Profile modelliert und die Teilenummern vergeben.</t>
+          <t>Marktrecherche zu Lochplatten durchgeführt, Angebote verglichen und das D16-Raster ausgewählt.</t>
         </is>
       </c>
       <c r="I147" s="86" t="n"/>
@@ -8059,7 +8059,7 @@
       </c>
       <c r="H148" s="94" t="inlineStr">
         <is>
-          <t>Weitere Eingabemasken für Bearbeiten und Löschen ergänzt und eine Sicherheitsabfrage vor dem Löschen eingebaut.</t>
+          <t>Mit der CAD-Konstruktion begonnen: Tischplatte mit Lochraster aufgebaut.</t>
         </is>
       </c>
       <c r="I148" s="86" t="n"/>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="H149" s="94" t="inlineStr">
         <is>
-          <t>Unterteil konstruiert: Beine, Streben und Fußplatten aufgebaut.</t>
+          <t>Oberteil konstruiert: Träger und Profile modelliert und die Teilenummern vergeben.</t>
         </is>
       </c>
       <c r="I149" s="86" t="n"/>
@@ -8203,7 +8203,7 @@
       </c>
       <c r="H152" s="94" t="inlineStr">
         <is>
-          <t>Erweiterungssystem als Teleskop-Rahmen konstruiert, beidseitig ausziehbar.</t>
+          <t>Unterteil konstruiert: Beine, Streben und Fußplatten aufgebaut.</t>
         </is>
       </c>
       <c r="I152" s="86" t="n"/>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="H153" s="67" t="inlineStr">
         <is>
-          <t>Filterfunktion über Bezeichnung, Profil, Maß und Materialgruppe umgesetzt und getestet.</t>
+          <t>Erweiterungssystem als Teleskop-Rahmen konstruiert, beidseitig ausziehbar.</t>
         </is>
       </c>
       <c r="I153" s="86" t="n"/>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="H159" s="94" t="inlineStr">
         <is>
-          <t>Export auf Knopfdruck umgesetzt: ausgewählte Blätter als Excel- oder PDF-Datei in einen festen Zielordner speichern.</t>
+          <t>Erste Zeichnungsblätter abgeleitet und bemaßt.</t>
         </is>
       </c>
       <c r="I159" s="86" t="n"/>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="H160" s="94" t="inlineStr">
         <is>
-          <t>Aufgabenstellung zum Schweißmaschinenwagen erhalten. Vorhandenen Wagen im Betrieb fotografiert und den Zustand aufgenommen.</t>
+          <t>Weitere Einzelteilzeichnungen erstellt und die Schriftfelder ausgefüllt.</t>
         </is>
       </c>
       <c r="I160" s="86" t="n"/>
@@ -8550,7 +8550,7 @@
       </c>
       <c r="H161" s="94" t="inlineStr">
         <is>
-          <t>Schweißgerät und Gasflasche vor Ort aufgemessen und die Maße in einer Handskizze festgehalten.</t>
+          <t>Stücklisten der Baugruppen erstellt und die Zukaufteile gekennzeichnet.</t>
         </is>
       </c>
       <c r="I161" s="86" t="n"/>
@@ -8591,7 +8591,7 @@
       </c>
       <c r="H162" s="94" t="inlineStr">
         <is>
-          <t>Versand der Bestandsliste per E-Mail ergänzt und mit Testdaten geprüft.</t>
+          <t>Aufgabenstellung zum Schweißmaschinenwagen erhalten. Vorhandenen Wagen im Betrieb fotografiert und den Zustand aufgenommen.</t>
         </is>
       </c>
       <c r="I162" s="86" t="n"/>
@@ -8632,7 +8632,7 @@
       </c>
       <c r="H163" s="94" t="inlineStr">
         <is>
-          <t>Vereinfachte CAD-Platzhalter für Gerät und Flasche erstellt, um den Bauraum abzubilden.</t>
+          <t>Schweißgerät und Gasflasche vor Ort aufgemessen und die Maße in einer Handskizze festgehalten.</t>
         </is>
       </c>
       <c r="I163" s="86" t="n"/>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="H166" s="94" t="inlineStr">
         <is>
-          <t>Anforderungsliste aufgestellt: was der Wagen tragen und was er können muss.</t>
+          <t>Vereinfachte CAD-Platzhalter für Gerät und Flasche erstellt, um den Bauraum abzubilden.</t>
         </is>
       </c>
       <c r="I166" s="86" t="n"/>
@@ -8776,7 +8776,7 @@
       </c>
       <c r="H167" s="94" t="inlineStr">
         <is>
-          <t>Einstellungsblatt angelegt, damit Zielordner, Empfängeradresse und Schwellenwerte ohne Eingriff in den Code änderbar sind.</t>
+          <t>Anforderungsliste aufgestellt: was der Wagen tragen und was er können muss.</t>
         </is>
       </c>
       <c r="I167" s="86" t="n"/>
@@ -8899,7 +8899,7 @@
       </c>
       <c r="H170" s="94" t="inlineStr">
         <is>
-          <t>Tablet-Modus entwickelt: Vollbild-Oberfläche ohne Excel-Bedienelemente, damit das System direkt in der Werkstatt bedienbar ist.</t>
+          <t>Zwei erste Entwürfe im CAD aufgebaut und gegenübergestellt.</t>
         </is>
       </c>
       <c r="I170" s="86" t="n"/>
@@ -9316,7 +9316,7 @@
       </c>
       <c r="H188" s="94" t="inlineStr">
         <is>
-          <t>Zwei erste Entwürfe im CAD aufgebaut und gegenübergestellt.</t>
+          <t>Maße und Ergonomie festgelegt, Gewicht des beladenen Wagens grob abgeschätzt.</t>
         </is>
       </c>
       <c r="I188" s="86" t="n"/>
@@ -9357,7 +9357,7 @@
       </c>
       <c r="H189" s="94" t="inlineStr">
         <is>
-          <t>Maße und Ergonomie festgelegt, Gewicht des beladenen Wagens grob abgeschätzt.</t>
+          <t>Kompletten Neubau als Variante A konstruiert und einen Belegungsplan mit 16 Werkzeugpositionen erstellt.</t>
         </is>
       </c>
       <c r="I189" s="86" t="n"/>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="H190" s="94" t="inlineStr">
         <is>
-          <t>Schwachstellen des Excel-Systems zusammengetragen: Bindung an einen Rechner, kein Mehrbenutzerbetrieb, Abhängigkeit von einer Person.</t>
+          <t>Beim Maßabgleich festgestellt, dass das geplante Gerätefach zu niedrig für die vorhandene Maschine ist.</t>
         </is>
       </c>
       <c r="I190" s="86" t="n"/>
@@ -9439,7 +9439,7 @@
       </c>
       <c r="H191" s="94" t="inlineStr">
         <is>
-          <t>Kompletten Neubau als Variante A konstruiert und einen Belegungsplan mit 16 Werkzeugpositionen erstellt.</t>
+          <t>Als Variante B ein Aufsatzgestell entworfen, das über den vorhandenen Wagen fährt.</t>
         </is>
       </c>
       <c r="I191" s="86" t="n"/>
@@ -9480,7 +9480,7 @@
       </c>
       <c r="H192" s="94" t="inlineStr">
         <is>
-          <t>Beim Maßabgleich festgestellt, dass das geplante Gerätefach zu niedrig für die vorhandene Maschine ist.</t>
+          <t>Variante B überarbeitet, sodass die Gasflasche innerhalb der Aufstandsfläche steht.</t>
         </is>
       </c>
       <c r="I192" s="86" t="n"/>
@@ -9583,7 +9583,7 @@
       </c>
       <c r="H195" s="94" t="inlineStr">
         <is>
-          <t>Neuentwicklung als eigenständige Web-Anwendung mit dem Betreuer besprochen und die Architektur in drei Schichten festgelegt.</t>
+          <t>Vorzugsvariante festgelegt: modularer Aufbau in vier Etagen.</t>
         </is>
       </c>
       <c r="I195" s="86" t="n"/>
@@ -9706,7 +9706,7 @@
       </c>
       <c r="H198" s="94" t="inlineStr">
         <is>
-          <t>Datenmodell aus den Excel-Blättern abgeleitet und als Datenbanktabellen umgesetzt.</t>
+          <t>Werkzeugbedarf für das Drehen zusammengestellt.</t>
         </is>
       </c>
       <c r="I198" s="86" t="n"/>
@@ -9848,7 +9848,7 @@
       </c>
       <c r="H202" s="94" t="inlineStr">
         <is>
-          <t>Werkzeugbedarf für das Drehen zusammengestellt.</t>
+          <t>Werkzeugbedarf für das Fräsen sowie die Spann- und Aufspannmittel erfasst.</t>
         </is>
       </c>
       <c r="I202" s="86" t="n"/>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="H203" s="94" t="inlineStr">
         <is>
-          <t>Werkzeugbedarf für das Fräsen sowie die Spann- und Aufspannmittel erfasst.</t>
+          <t>Mess- und Prüfmittel sowie Nacharbeit und Hilfsmittel ergänzt. Damit sind alle sechs Gruppen erfasst.</t>
         </is>
       </c>
       <c r="I203" s="86" t="n"/>
@@ -9930,7 +9930,7 @@
       </c>
       <c r="H204" s="67" t="inlineStr">
         <is>
-          <t>Grundfunktionen portiert: Artikel anlegen, suchen, bearbeiten und löschen.</t>
+          <t>Mengen je Position festgelegt und begründet, welche Werkzeuge dreifach beschafft werden müssen.</t>
         </is>
       </c>
       <c r="I204" s="86" t="n"/>
@@ -9971,7 +9971,7 @@
       </c>
       <c r="H205" s="99" t="inlineStr">
         <is>
-          <t>Mess- und Prüfmittel sowie Nacharbeit und Hilfsmittel ergänzt. Damit sind alle sechs Gruppen erfasst.</t>
+          <t>Preise recherchiert und die Werkzeugliste mit 35 Positionen bepreist.</t>
         </is>
       </c>
       <c r="I205" s="86" t="n"/>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="H206" s="67" t="inlineStr">
         <is>
-          <t>Mengen je Position festgelegt und begründet, welche Werkzeuge dreifach beschafft werden müssen.</t>
+          <t>Kosten nach Kategorien ausgewertet und die teuersten Positionen herausgearbeitet.</t>
         </is>
       </c>
       <c r="I206" s="86" t="n"/>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="H209" s="67" t="inlineStr">
         <is>
-          <t>Buchungslogik und Verlaufsprotokoll übertragen und gegen das Excel-Original geprüft.</t>
+          <t>5S-Ordnung ausgearbeitet und die Werkzeuge den Zonen A, B und C zugeordnet.</t>
         </is>
       </c>
       <c r="I209" s="86" t="n"/>
@@ -10156,7 +10156,7 @@
       </c>
       <c r="H210" s="67" t="inlineStr">
         <is>
-          <t>Preise recherchiert und die Werkzeugliste mit 35 Positionen bepreist.</t>
+          <t>Grundmaße der Werkbank festgelegt und mit den Ergonomienormen abgeglichen.</t>
         </is>
       </c>
       <c r="I210" s="86" t="n"/>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="H211" s="67" t="inlineStr">
         <is>
-          <t>Kosten nach Kategorien ausgewertet und die teuersten Positionen herausgearbeitet.</t>
+          <t>Vier Bauvarianten skizziert und in 3D dargestellt: Aluprofil, Stahl-Standard, Systemmodule und Eigenbau.</t>
         </is>
       </c>
       <c r="I211" s="86" t="n"/>
@@ -10238,7 +10238,7 @@
       </c>
       <c r="H212" s="67" t="inlineStr">
         <is>
-          <t>Material-Entnahme mit Resteverwaltung in die neue Anwendung übernommen und mit denselben Beispielen nachgerechnet.</t>
+          <t>Vier Layout-Konzepte entwickelt und die Vor- und Nachteile gegenübergestellt.</t>
         </is>
       </c>
       <c r="I212" s="86" t="n"/>
@@ -10279,7 +10279,7 @@
       </c>
       <c r="H213" s="67" t="inlineStr">
         <is>
-          <t>5S-Ordnung ausgearbeitet und die Werkzeuge den Zonen A, B und C zugeordnet.</t>
+          <t>Werkstatt-Grundriss maßstäblich gezeichnet und die Freiräume an den Maschinen geprüft.</t>
         </is>
       </c>
       <c r="I213" s="86" t="n"/>
@@ -10696,7 +10696,7 @@
       </c>
       <c r="H231" s="61" t="inlineStr">
         <is>
-          <t>Aufgabenstellung zum Rostschutz für die Schienenprofile erhalten. Lagerbedingungen der Profile im Betrieb aufgenommen und fotografiert.</t>
+          <t>Nutzwertanalyse aufgestellt: sieben Kriterien festgelegt und gewichtet.</t>
         </is>
       </c>
       <c r="I231" s="86" t="n"/>
@@ -10737,7 +10737,7 @@
       </c>
       <c r="H232" s="67" t="inlineStr">
         <is>
-          <t>86 reale Artikel-Datensätze und 50 Artikelgruppen aus dem Altsystem übernommen und die Übernahme kontrolliert.</t>
+          <t>Aufgabenstellung zum Rostschutz für die Schienenprofile erhalten. Lagerbedingungen der Profile im Betrieb aufgenommen und fotografiert.</t>
         </is>
       </c>
       <c r="I232" s="86" t="n"/>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="H235" s="67" t="inlineStr">
         <is>
-          <t>Papierkorb und Löschabfrage eingebaut, um Bedienfehler abzufangen.</t>
+          <t>Verfahren gegenübergestellt und nach Wirksamkeit, Aufwand und Kosten bewertet.</t>
         </is>
       </c>
       <c r="I235" s="86" t="n"/>
@@ -10963,7 +10963,7 @@
       </c>
       <c r="H238" s="67" t="inlineStr">
         <is>
-          <t>Verfahren gegenübergestellt und nach Wirksamkeit, Aufwand und Kosten bewertet.</t>
+          <t>Konzept für eine geschlossene Lagerbox mit VCI-Schutz entworfen und die benötigten Maße aufgenommen.</t>
         </is>
       </c>
       <c r="I238" s="86" t="n"/>
@@ -11004,7 +11004,7 @@
       </c>
       <c r="H239" s="67" t="inlineStr">
         <is>
-          <t>Konzept für eine geschlossene Lagerbox mit VCI-Schutz entworfen und die benötigten Maße aufgenommen.</t>
+          <t>Lagerbox im CAD konstruiert und die Aufteilung für die verschiedenen Profillängen festgelegt.</t>
         </is>
       </c>
       <c r="I239" s="86" t="n"/>
@@ -11045,7 +11045,7 @@
       </c>
       <c r="H240" s="67" t="inlineStr">
         <is>
-          <t>Oberfläche überarbeitet: Suche, Filter und Bestandsanzeige übersichtlicher angeordnet.</t>
+          <t>Material- und Kostenaufstellung für die Schutzbox erstellt.</t>
         </is>
       </c>
       <c r="I240" s="86" t="n"/>
@@ -11086,7 +11086,7 @@
       </c>
       <c r="H241" s="67" t="inlineStr">
         <is>
-          <t>Lagerbox im CAD konstruiert und die Aufteilung für die verschiedenen Profillängen festgelegt.</t>
+          <t>Zeitersparnis durch den Wegfall des Nacharbeitens abgeschätzt und der Investition gegenübergestellt.</t>
         </is>
       </c>
       <c r="I241" s="86" t="n"/>
@@ -11127,7 +11127,7 @@
       </c>
       <c r="H242" s="67" t="inlineStr">
         <is>
-          <t>Material- und Kostenaufstellung für die Schutzbox erstellt.</t>
+          <t>Arbeitsanweisung für die Einlagerung und Entnahme der Schienenprofile entworfen.</t>
         </is>
       </c>
       <c r="I242" s="86" t="n"/>

--- a/hochschule/Hassine_3399727_Tätigkeitsnachweis.xlsx
+++ b/hochschule/Hassine_3399727_Tätigkeitsnachweis.xlsx
@@ -4459,7 +4459,7 @@
         <v>91</v>
       </c>
       <c r="E16" s="39" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="F16" s="40" t="s">
         <v>92</v>
@@ -4527,7 +4527,7 @@
         <v>91</v>
       </c>
       <c r="E18" s="49" t="n">
-        <v>8.25</v>
+        <v>9.25</v>
       </c>
       <c r="F18" s="50" t="s">
         <v>92</v>
@@ -4561,7 +4561,7 @@
         <v>91</v>
       </c>
       <c r="E19" s="49" t="n">
-        <v>9.25</v>
+        <v>9.75</v>
       </c>
       <c r="F19" s="50" t="s">
         <v>92</v>
@@ -4595,7 +4595,7 @@
         <v>91</v>
       </c>
       <c r="E20" s="49" t="n">
-        <v>7.75</v>
+        <v>9.75</v>
       </c>
       <c r="F20" s="50" t="s">
         <v>92</v>
@@ -4685,7 +4685,7 @@
         <v>91</v>
       </c>
       <c r="E23" s="49" t="n">
-        <v>8.75</v>
+        <v>9.25</v>
       </c>
       <c r="F23" s="50" t="s">
         <v>92</v>
@@ -4719,7 +4719,7 @@
         <v>91</v>
       </c>
       <c r="E24" s="49" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="F24" s="50" t="s">
         <v>92</v>
@@ -4753,7 +4753,7 @@
         <v>91</v>
       </c>
       <c r="E25" s="49" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F25" s="50" t="s">
         <v>92</v>
@@ -4787,7 +4787,7 @@
         <v>91</v>
       </c>
       <c r="E26" s="49" t="n">
-        <v>8.6</v>
+        <v>9.5</v>
       </c>
       <c r="F26" s="50" t="s">
         <v>92</v>
@@ -4821,7 +4821,7 @@
         <v>91</v>
       </c>
       <c r="E27" s="49" t="n">
-        <v>9.05</v>
+        <v>9.5</v>
       </c>
       <c r="F27" s="50" t="s">
         <v>92</v>
@@ -4911,7 +4911,7 @@
         <v>91</v>
       </c>
       <c r="E30" s="49" t="n">
-        <v>8.3</v>
+        <v>9.75</v>
       </c>
       <c r="F30" s="50" t="s">
         <v>92</v>
@@ -4945,7 +4945,7 @@
         <v>91</v>
       </c>
       <c r="E31" s="49" t="n">
-        <v>7.55</v>
+        <v>9.25</v>
       </c>
       <c r="F31" s="50" t="s">
         <v>92</v>
@@ -4979,7 +4979,7 @@
         <v>106</v>
       </c>
       <c r="E32" s="49" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="F32" s="50" t="s">
         <v>92</v>
@@ -5013,7 +5013,7 @@
         <v>91</v>
       </c>
       <c r="E33" s="49" t="n">
-        <v>8.8</v>
+        <v>9.25</v>
       </c>
       <c r="F33" s="50" t="s">
         <v>92</v>
@@ -5135,7 +5135,7 @@
         <v>91</v>
       </c>
       <c r="E37" s="49" t="n">
-        <v>9.2</v>
+        <v>9.75</v>
       </c>
       <c r="F37" s="50" t="s">
         <v>92</v>
@@ -5168,7 +5168,7 @@
         <v>91</v>
       </c>
       <c r="E38" s="49" t="n">
-        <v>8.45</v>
+        <v>10</v>
       </c>
       <c r="F38" s="50" t="s">
         <v>92</v>
@@ -5234,7 +5234,7 @@
         <v>91</v>
       </c>
       <c r="E40" s="49" t="n">
-        <v>8.95</v>
+        <v>9</v>
       </c>
       <c r="F40" s="50" t="s">
         <v>92</v>
@@ -5636,7 +5636,7 @@
         <v>91</v>
       </c>
       <c r="E59" s="39" t="n">
-        <v>7.85</v>
+        <v>10</v>
       </c>
       <c r="F59" s="40" t="s">
         <v>92</v>
@@ -5669,7 +5669,7 @@
         <v>91</v>
       </c>
       <c r="E60" s="49" t="n">
-        <v>8.2</v>
+        <v>9.5</v>
       </c>
       <c r="F60" s="50" t="s">
         <v>92</v>
@@ -5702,7 +5702,7 @@
         <v>106</v>
       </c>
       <c r="E61" s="49" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="F61" s="76" t="s">
         <v>92</v>
@@ -5735,7 +5735,7 @@
         <v>91</v>
       </c>
       <c r="E62" s="49" t="n">
-        <v>9.45</v>
+        <v>10.25</v>
       </c>
       <c r="F62" s="76" t="s">
         <v>92</v>
@@ -5884,7 +5884,7 @@
         <v>91</v>
       </c>
       <c r="E67" s="49" t="n">
-        <v>8.1</v>
+        <v>9.25</v>
       </c>
       <c r="F67" s="76" t="s">
         <v>92</v>
@@ -5917,7 +5917,7 @@
         <v>106</v>
       </c>
       <c r="E68" s="49" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="F68" s="76" t="s">
         <v>92</v>
@@ -5950,7 +5950,7 @@
         <v>91</v>
       </c>
       <c r="E69" s="49" t="n">
-        <v>8.7</v>
+        <v>9.5</v>
       </c>
       <c r="F69" s="76" t="s">
         <v>92</v>
@@ -5983,7 +5983,7 @@
         <v>91</v>
       </c>
       <c r="E70" s="49" t="n">
-        <v>9.3</v>
+        <v>10</v>
       </c>
       <c r="F70" s="76" t="s">
         <v>92</v>
@@ -6070,7 +6070,7 @@
         <v>91</v>
       </c>
       <c r="E73" s="49" t="n">
-        <v>8.05</v>
+        <v>10</v>
       </c>
       <c r="F73" s="76" t="s">
         <v>92</v>
@@ -6103,7 +6103,7 @@
         <v>91</v>
       </c>
       <c r="E74" s="49" t="n">
-        <v>8.55</v>
+        <v>9.5</v>
       </c>
       <c r="F74" s="76" t="s">
         <v>92</v>
@@ -6136,7 +6136,7 @@
         <v>106</v>
       </c>
       <c r="E75" s="49" t="n">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="F75" s="76" t="s">
         <v>92</v>
@@ -6169,7 +6169,7 @@
         <v>91</v>
       </c>
       <c r="E76" s="49" t="n">
-        <v>9.15</v>
+        <v>9.25</v>
       </c>
       <c r="F76" s="76" t="s">
         <v>92</v>
@@ -6202,7 +6202,7 @@
         <v>91</v>
       </c>
       <c r="E77" s="49" t="n">
-        <v>7.95</v>
+        <v>10.25</v>
       </c>
       <c r="F77" s="76" t="s">
         <v>92</v>
@@ -6289,7 +6289,7 @@
         <v>91</v>
       </c>
       <c r="E80" s="49" t="n">
-        <v>8.35</v>
+        <v>9.75</v>
       </c>
       <c r="F80" s="76" t="s">
         <v>92</v>
@@ -6322,7 +6322,7 @@
         <v>91</v>
       </c>
       <c r="E81" s="49" t="n">
-        <v>9.35</v>
+        <v>9.75</v>
       </c>
       <c r="F81" s="76" t="s">
         <v>92</v>
@@ -6355,7 +6355,7 @@
         <v>106</v>
       </c>
       <c r="E82" s="49" t="n">
-        <v>5</v>
+        <v>5.75</v>
       </c>
       <c r="F82" s="76" t="s">
         <v>92</v>
@@ -6388,7 +6388,7 @@
         <v>91</v>
       </c>
       <c r="E83" s="49" t="n">
-        <v>8.65</v>
+        <v>10</v>
       </c>
       <c r="F83" s="76" t="s">
         <v>92</v>
@@ -6421,7 +6421,7 @@
         <v>91</v>
       </c>
       <c r="E84" s="49" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="F84" s="76" t="s">
         <v>92</v>
@@ -6790,7 +6790,7 @@
         <v>91</v>
       </c>
       <c r="E102" s="39" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="F102" s="78" t="s">
         <v>92</v>
@@ -6823,7 +6823,7 @@
         <v>91</v>
       </c>
       <c r="E103" s="49" t="n">
-        <v>8.25</v>
+        <v>10</v>
       </c>
       <c r="F103" s="76" t="s">
         <v>92</v>
@@ -6856,7 +6856,7 @@
         <v>106</v>
       </c>
       <c r="E104" s="49" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="F104" s="76" t="s">
         <v>92</v>
@@ -6889,7 +6889,7 @@
         <v>91</v>
       </c>
       <c r="E105" s="49" t="n">
-        <v>9.25</v>
+        <v>9.75</v>
       </c>
       <c r="F105" s="76" t="s">
         <v>92</v>
@@ -7007,7 +7007,7 @@
         <v>91</v>
       </c>
       <c r="E109" s="49" t="n">
-        <v>7.75</v>
+        <v>10.25</v>
       </c>
       <c r="F109" s="76" t="s">
         <v>92</v>
@@ -7040,7 +7040,7 @@
         <v>91</v>
       </c>
       <c r="E110" s="49" t="n">
-        <v>8.75</v>
+        <v>9.25</v>
       </c>
       <c r="F110" s="76" t="s">
         <v>92</v>
@@ -7073,7 +7073,7 @@
         <v>106</v>
       </c>
       <c r="E111" s="49" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="F111" s="76" t="s">
         <v>92</v>
@@ -7139,7 +7139,7 @@
         <v>91</v>
       </c>
       <c r="E113" s="49" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F113" s="76" t="s">
         <v>92</v>
@@ -7226,7 +7226,7 @@
         <v>91</v>
       </c>
       <c r="E116" s="49" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="F116" s="76" t="s">
         <v>92</v>
@@ -7259,7 +7259,7 @@
         <v>91</v>
       </c>
       <c r="E117" s="49" t="n">
-        <v>9.05</v>
+        <v>9.5</v>
       </c>
       <c r="F117" s="76" t="s">
         <v>92</v>
@@ -7292,7 +7292,7 @@
         <v>106</v>
       </c>
       <c r="E118" s="49" t="n">
-        <v>5.55</v>
+        <v>5</v>
       </c>
       <c r="F118" s="76" t="s">
         <v>92</v>
@@ -7356,7 +7356,7 @@
         <v>91</v>
       </c>
       <c r="E120" s="49" t="n">
-        <v>8.3</v>
+        <v>9.25</v>
       </c>
       <c r="F120" s="76" t="s">
         <v>92</v>
@@ -7443,7 +7443,7 @@
         <v>91</v>
       </c>
       <c r="E123" s="49" t="n">
-        <v>7.55</v>
+        <v>10.25</v>
       </c>
       <c r="F123" s="76" t="s">
         <v>92</v>
@@ -7476,7 +7476,7 @@
         <v>91</v>
       </c>
       <c r="E124" s="49" t="n">
-        <v>8.8</v>
+        <v>9.75</v>
       </c>
       <c r="F124" s="76" t="s">
         <v>92</v>
@@ -7509,7 +7509,7 @@
         <v>106</v>
       </c>
       <c r="E125" s="49" t="n">
-        <v>4.9</v>
+        <v>5.25</v>
       </c>
       <c r="F125" s="76" t="s">
         <v>92</v>
@@ -7542,7 +7542,7 @@
         <v>91</v>
       </c>
       <c r="E126" s="49" t="n">
-        <v>9.2</v>
+        <v>9.75</v>
       </c>
       <c r="F126" s="76" t="s">
         <v>92</v>
@@ -7575,7 +7575,7 @@
         <v>91</v>
       </c>
       <c r="E127" s="49" t="n">
-        <v>8.45</v>
+        <v>10</v>
       </c>
       <c r="F127" s="76" t="s">
         <v>92</v>
@@ -7975,7 +7975,7 @@
         <v>91</v>
       </c>
       <c r="E146" s="49" t="n">
-        <v>8.95</v>
+        <v>9.5</v>
       </c>
       <c r="F146" s="76" t="s">
         <v>92</v>
@@ -8008,7 +8008,7 @@
         <v>106</v>
       </c>
       <c r="E147" s="49" t="n">
-        <v>5.4</v>
+        <v>5.75</v>
       </c>
       <c r="F147" s="76" t="s">
         <v>92</v>
@@ -8041,7 +8041,7 @@
         <v>91</v>
       </c>
       <c r="E148" s="49" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="F148" s="76" t="s">
         <v>92</v>
@@ -8074,7 +8074,7 @@
         <v>91</v>
       </c>
       <c r="E149" s="49" t="n">
-        <v>7.85</v>
+        <v>10</v>
       </c>
       <c r="F149" s="76" t="s">
         <v>92</v>
@@ -8161,7 +8161,7 @@
         <v>91</v>
       </c>
       <c r="E152" s="49" t="n">
-        <v>8.2</v>
+        <v>8.25</v>
       </c>
       <c r="F152" s="76" t="s">
         <v>92</v>
@@ -8194,7 +8194,7 @@
         <v>91</v>
       </c>
       <c r="E153" s="49" t="n">
-        <v>9.45</v>
+        <v>7.25</v>
       </c>
       <c r="F153" s="76" t="s">
         <v>92</v>
@@ -8227,7 +8227,7 @@
         <v>106</v>
       </c>
       <c r="E154" s="49" t="n">
-        <v>5.15</v>
+        <v>6</v>
       </c>
       <c r="F154" s="76" t="s">
         <v>92</v>
@@ -8291,7 +8291,7 @@
         <v>91</v>
       </c>
       <c r="E156" s="49" t="n">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="F156" s="76" t="s">
         <v>92</v>
@@ -8378,7 +8378,7 @@
         <v>91</v>
       </c>
       <c r="E159" s="49" t="n">
-        <v>8.7</v>
+        <v>8</v>
       </c>
       <c r="F159" s="76" t="s">
         <v>92</v>
@@ -8411,7 +8411,7 @@
         <v>91</v>
       </c>
       <c r="E160" s="49" t="n">
-        <v>9.3</v>
+        <v>8</v>
       </c>
       <c r="F160" s="76" t="s">
         <v>92</v>
@@ -8444,7 +8444,7 @@
         <v>106</v>
       </c>
       <c r="E161" s="49" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="F161" s="76" t="s">
         <v>92</v>
@@ -8477,7 +8477,7 @@
         <v>91</v>
       </c>
       <c r="E162" s="49" t="n">
-        <v>8.05</v>
+        <v>7.5</v>
       </c>
       <c r="F162" s="76" t="s">
         <v>92</v>
@@ -8510,7 +8510,7 @@
         <v>91</v>
       </c>
       <c r="E163" s="49" t="n">
-        <v>8.55</v>
+        <v>7.25</v>
       </c>
       <c r="F163" s="76" t="s">
         <v>92</v>
@@ -8597,7 +8597,7 @@
         <v>91</v>
       </c>
       <c r="E166" s="49" t="n">
-        <v>9.15</v>
+        <v>8.25</v>
       </c>
       <c r="F166" s="76" t="s">
         <v>92</v>
@@ -8630,7 +8630,7 @@
         <v>91</v>
       </c>
       <c r="E167" s="49" t="n">
-        <v>7.95</v>
+        <v>7.75</v>
       </c>
       <c r="F167" s="76" t="s">
         <v>92</v>
@@ -8663,7 +8663,7 @@
         <v>106</v>
       </c>
       <c r="E168" s="49" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="F168" s="76" t="s">
         <v>92</v>
@@ -8696,7 +8696,7 @@
         <v>91</v>
       </c>
       <c r="E169" s="49" t="n">
-        <v>8.35</v>
+        <v>7.75</v>
       </c>
       <c r="F169" s="76" t="s">
         <v>92</v>
@@ -8729,7 +8729,7 @@
         <v>91</v>
       </c>
       <c r="E170" s="49" t="n">
-        <v>9.35</v>
+        <v>8</v>
       </c>
       <c r="F170" s="76" t="s">
         <v>92</v>
@@ -9098,7 +9098,7 @@
         <v>91</v>
       </c>
       <c r="E188" s="39" t="n">
-        <v>8.65</v>
+        <v>7.5</v>
       </c>
       <c r="F188" s="78" t="s">
         <v>92</v>
@@ -9131,7 +9131,7 @@
         <v>91</v>
       </c>
       <c r="E189" s="49" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="F189" s="76" t="s">
         <v>92</v>
@@ -9164,7 +9164,7 @@
         <v>106</v>
       </c>
       <c r="E190" s="49" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="F190" s="76" t="s">
         <v>92</v>
@@ -9197,7 +9197,7 @@
         <v>91</v>
       </c>
       <c r="E191" s="49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F191" s="76" t="s">
         <v>92</v>
@@ -9317,7 +9317,7 @@
         <v>91</v>
       </c>
       <c r="E195" s="49" t="n">
-        <v>9.25</v>
+        <v>7.25</v>
       </c>
       <c r="F195" s="76" t="s">
         <v>92</v>
@@ -9383,7 +9383,7 @@
         <v>106</v>
       </c>
       <c r="E197" s="49" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="F197" s="76" t="s">
         <v>92</v>
@@ -9416,7 +9416,7 @@
         <v>91</v>
       </c>
       <c r="E198" s="49" t="n">
-        <v>8.75</v>
+        <v>6.75</v>
       </c>
       <c r="F198" s="76" t="s">
         <v>92</v>
@@ -9534,7 +9534,7 @@
         <v>91</v>
       </c>
       <c r="E202" s="49" t="n">
-        <v>9.5</v>
+        <v>6.75</v>
       </c>
       <c r="F202" s="76" t="s">
         <v>92</v>
@@ -9567,7 +9567,7 @@
         <v>91</v>
       </c>
       <c r="E203" s="49" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="F203" s="76" t="s">
         <v>92</v>
@@ -9600,7 +9600,7 @@
         <v>91</v>
       </c>
       <c r="E204" s="49" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="F204" s="76" t="s">
         <v>92</v>
@@ -9633,7 +9633,7 @@
         <v>91</v>
       </c>
       <c r="E205" s="49" t="n">
-        <v>9.05</v>
+        <v>7</v>
       </c>
       <c r="F205" s="76" t="s">
         <v>92</v>
@@ -9666,7 +9666,7 @@
         <v>91</v>
       </c>
       <c r="E206" s="49" t="n">
-        <v>8.3</v>
+        <v>6.5</v>
       </c>
       <c r="F206" s="76" t="s">
         <v>92</v>
@@ -9753,7 +9753,7 @@
         <v>91</v>
       </c>
       <c r="E209" s="49" t="n">
-        <v>7.55</v>
+        <v>6.75</v>
       </c>
       <c r="F209" s="76" t="s">
         <v>92</v>
@@ -9786,7 +9786,7 @@
         <v>91</v>
       </c>
       <c r="E210" s="49" t="n">
-        <v>8.8</v>
+        <v>6.75</v>
       </c>
       <c r="F210" s="76" t="s">
         <v>92</v>
@@ -9819,7 +9819,7 @@
         <v>91</v>
       </c>
       <c r="E211" s="49" t="n">
-        <v>9.2</v>
+        <v>6.75</v>
       </c>
       <c r="F211" s="76" t="s">
         <v>92</v>
@@ -9852,7 +9852,7 @@
         <v>91</v>
       </c>
       <c r="E212" s="49" t="n">
-        <v>8.45</v>
+        <v>6.75</v>
       </c>
       <c r="F212" s="76" t="s">
         <v>92</v>
@@ -9885,7 +9885,7 @@
         <v>91</v>
       </c>
       <c r="E213" s="49" t="n">
-        <v>8.95</v>
+        <v>7</v>
       </c>
       <c r="F213" s="76" t="s">
         <v>92</v>
@@ -10254,7 +10254,7 @@
         <v>91</v>
       </c>
       <c r="E231" s="39" t="n">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="F231" s="78" t="s">
         <v>92</v>
@@ -10287,7 +10287,7 @@
         <v>91</v>
       </c>
       <c r="E232" s="49" t="n">
-        <v>7.85</v>
+        <v>6.5</v>
       </c>
       <c r="F232" s="76" t="s">
         <v>92</v>
@@ -10320,7 +10320,7 @@
         <v>91</v>
       </c>
       <c r="E233" s="49" t="n">
-        <v>8.2</v>
+        <v>7</v>
       </c>
       <c r="F233" s="76" t="s">
         <v>92</v>
@@ -10353,7 +10353,7 @@
         <v>91</v>
       </c>
       <c r="E234" s="49" t="n">
-        <v>9.45</v>
+        <v>6.75</v>
       </c>
       <c r="F234" s="76" t="s">
         <v>92</v>
@@ -10386,7 +10386,7 @@
         <v>91</v>
       </c>
       <c r="E235" s="49" t="n">
-        <v>8.1</v>
+        <v>6.75</v>
       </c>
       <c r="F235" s="76" t="s">
         <v>92</v>
@@ -10473,7 +10473,7 @@
         <v>91</v>
       </c>
       <c r="E238" s="49" t="n">
-        <v>8.7</v>
+        <v>6.75</v>
       </c>
       <c r="F238" s="76" t="s">
         <v>92</v>
@@ -10506,7 +10506,7 @@
         <v>91</v>
       </c>
       <c r="E239" s="49" t="n">
-        <v>9.3</v>
+        <v>6.75</v>
       </c>
       <c r="F239" s="76" t="s">
         <v>92</v>
@@ -10539,7 +10539,7 @@
         <v>91</v>
       </c>
       <c r="E240" s="49" t="n">
-        <v>8.05</v>
+        <v>7</v>
       </c>
       <c r="F240" s="76" t="s">
         <v>92</v>
@@ -10572,7 +10572,7 @@
         <v>91</v>
       </c>
       <c r="E241" s="49" t="n">
-        <v>8.55</v>
+        <v>6.5</v>
       </c>
       <c r="F241" s="76" t="s">
         <v>92</v>
@@ -10605,7 +10605,7 @@
         <v>91</v>
       </c>
       <c r="E242" s="49" t="n">
-        <v>9.15</v>
+        <v>6.75</v>
       </c>
       <c r="F242" s="76" t="s">
         <v>92</v>

--- a/hochschule/Hassine_3399727_Tätigkeitsnachweis.xlsx
+++ b/hochschule/Hassine_3399727_Tätigkeitsnachweis.xlsx
@@ -4413,12 +4413,10 @@
       </c>
       <c r="D32" s="65" t="inlineStr">
         <is>
-          <t>VA</t>
-        </is>
-      </c>
-      <c r="E32" s="119" t="n">
-        <v>5.5</v>
-      </c>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E32" s="119" t="n"/>
       <c r="F32" s="92" t="inlineStr">
         <is>
           <t>h</t>
@@ -4431,7 +4429,7 @@
       </c>
       <c r="H32" s="94" t="inlineStr">
         <is>
-          <t>Belegungsplan erstellt: jeder der 135 Sorten einen festen, beschrifteten Platz zugeordnet. Bezugsquellen recherchiert, Ergebnisse dem Betreuer vorgestellt und eine Arbeitsanweisung für die Materialentnahme entworfen.</t>
+          <t>Vorlesung PP 10:00-11:30 an der OTH, keine Anwesenheit im Betrieb</t>
         </is>
       </c>
       <c r="I32" s="86" t="n"/>
@@ -4683,12 +4681,10 @@
       </c>
       <c r="D39" s="65" t="inlineStr">
         <is>
-          <t>VA</t>
-        </is>
-      </c>
-      <c r="E39" s="119" t="n">
-        <v>5.5</v>
-      </c>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E39" s="119" t="n"/>
       <c r="F39" s="92" t="inlineStr">
         <is>
           <t>h</t>
@@ -4701,7 +4697,7 @@
       </c>
       <c r="H39" s="95" t="inlineStr">
         <is>
-          <t>Barcode-Suche umgesetzt: Der eingescannte Code springt zum Artikel und zeigt alle Felder im Dashboard an.</t>
+          <t>Vorlesung PP 10:00-11:30 an der OTH, keine Anwesenheit im Betrieb</t>
         </is>
       </c>
       <c r="I39" s="86" t="n"/>
@@ -4742,7 +4738,7 @@
       </c>
       <c r="H40" s="94" t="inlineStr">
         <is>
-          <t>Dashboard als Bedienoberfläche gestaltet: Scannfunktionen links, Suchergebnis in der Mitte, Exportbereich rechts.</t>
+          <t>Barcode-Suche umgesetzt: Der eingescannte Code springt zum Artikel und zeigt alle Felder im Dashboard an.</t>
         </is>
       </c>
       <c r="I40" s="86" t="n"/>
@@ -4783,7 +4779,7 @@
       </c>
       <c r="H41" s="67" t="inlineStr">
         <is>
-          <t>Automatische Färbung des Bestands nach Soll- und Ist-Wert eingebaut, damit knapper Bestand sofort auffällt.</t>
+          <t>Dashboard als Bedienoberfläche gestaltet: Scannfunktionen links, Suchergebnis in der Mitte, Exportbereich rechts.</t>
         </is>
       </c>
       <c r="I41" s="86" t="n"/>
@@ -5200,7 +5196,7 @@
       </c>
       <c r="H59" s="94" t="inlineStr">
         <is>
-          <t>Eigene Eingabemaske für das Anlegen neuer Artikel als UserForm erstellt und mit der Artikelliste verbunden.</t>
+          <t>Automatische Färbung des Bestands nach Soll- und Ist-Wert eingebaut, damit knapper Bestand sofort auffällt.</t>
         </is>
       </c>
       <c r="I59" s="86" t="n"/>
@@ -5241,7 +5237,7 @@
       </c>
       <c r="H60" s="94" t="inlineStr">
         <is>
-          <t>Weitere Eingabemasken für Bearbeiten und Löschen ergänzt und eine Sicherheitsabfrage vor dem Löschen eingebaut.</t>
+          <t>Eigene Eingabemaske für das Anlegen neuer Artikel als UserForm erstellt und mit der Artikelliste verbunden.</t>
         </is>
       </c>
       <c r="I60" s="86" t="n"/>
@@ -5264,12 +5260,10 @@
       </c>
       <c r="D61" s="65" t="inlineStr">
         <is>
-          <t>VA</t>
-        </is>
-      </c>
-      <c r="E61" s="119" t="n">
-        <v>5.5</v>
-      </c>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E61" s="119" t="n"/>
       <c r="F61" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -5282,7 +5276,7 @@
       </c>
       <c r="H61" s="94" t="inlineStr">
         <is>
-          <t>Filterfunktion über Bezeichnung, Profil, Maß und Materialgruppe umgesetzt und getestet.</t>
+          <t>Vorlesung PP 10:00-11:30 an der OTH, keine Anwesenheit im Betrieb</t>
         </is>
       </c>
       <c r="I61" s="86" t="n"/>
@@ -5323,7 +5317,7 @@
       </c>
       <c r="H62" s="94" t="inlineStr">
         <is>
-          <t>Export auf Knopfdruck umgesetzt: ausgewählte Blätter als Excel- oder PDF-Datei in einen festen Zielordner speichern.</t>
+          <t>Weitere Eingabemasken für Bearbeiten und Löschen ergänzt und eine Sicherheitsabfrage vor dem Löschen eingebaut.</t>
         </is>
       </c>
       <c r="I62" s="86" t="n"/>
@@ -5504,7 +5498,7 @@
       </c>
       <c r="H67" s="94" t="inlineStr">
         <is>
-          <t>Versand der Bestandsliste per E-Mail ergänzt und mit Testdaten geprüft.</t>
+          <t>Filterfunktion über Bezeichnung, Profil, Maß und Materialgruppe umgesetzt und getestet.</t>
         </is>
       </c>
       <c r="I67" s="86" t="n"/>
@@ -5527,12 +5521,10 @@
       </c>
       <c r="D68" s="65" t="inlineStr">
         <is>
-          <t>VA</t>
-        </is>
-      </c>
-      <c r="E68" s="119" t="n">
-        <v>5.25</v>
-      </c>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E68" s="119" t="n"/>
       <c r="F68" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -5545,7 +5537,7 @@
       </c>
       <c r="H68" s="94" t="inlineStr">
         <is>
-          <t>Einstellungsblatt angelegt, damit Zielordner, Empfängeradresse und Schwellenwerte ohne Eingriff in den Code änderbar sind.</t>
+          <t>Vorlesung PP 10:00-11:30 an der OTH, keine Anwesenheit im Betrieb</t>
         </is>
       </c>
       <c r="I68" s="86" t="n"/>
@@ -5586,7 +5578,7 @@
       </c>
       <c r="H69" s="94" t="inlineStr">
         <is>
-          <t>Tablet-Modus entwickelt: Vollbild-Oberfläche ohne Excel-Bedienelemente, damit das System direkt in der Werkstatt bedienbar ist.</t>
+          <t>Export auf Knopfdruck umgesetzt: ausgewählte Blätter als Excel- oder PDF-Datei in einen festen Zielordner speichern.</t>
         </is>
       </c>
       <c r="I69" s="86" t="n"/>
@@ -5627,7 +5619,7 @@
       </c>
       <c r="H70" s="67" t="inlineStr">
         <is>
-          <t>Entwicklermodus ergänzt, der die Excel-Oberfläche für Wartungsarbeiten wieder einblendet, und mit einem Kennwort geschützt.</t>
+          <t>Versand der Bestandsliste per E-Mail ergänzt und mit Testdaten geprüft.</t>
         </is>
       </c>
       <c r="I70" s="86" t="n"/>
@@ -5730,7 +5722,7 @@
       </c>
       <c r="H73" s="94" t="inlineStr">
         <is>
-          <t>Makros in Modulgruppen aufgeteilt und benannt, damit die Datei wartbar bleibt und Funktionen wiederverwendet werden können.</t>
+          <t>Einstellungsblatt angelegt, damit Zielordner, Empfängeradresse und Schwellenwerte ohne Eingriff in den Code änderbar sind.</t>
         </is>
       </c>
       <c r="I73" s="86" t="n"/>
@@ -5771,7 +5763,7 @@
       </c>
       <c r="H74" s="94" t="inlineStr">
         <is>
-          <t>Material-Entnahme-Logik entworfen: Beim Zuschnitt soll die Restlänge selbstständig eingebucht werden.</t>
+          <t>Tablet-Modus entwickelt: Vollbild-Oberfläche ohne Excel-Bedienelemente, damit das System direkt in der Werkstatt bedienbar ist.</t>
         </is>
       </c>
       <c r="I74" s="86" t="n"/>
@@ -5794,12 +5786,10 @@
       </c>
       <c r="D75" s="65" t="inlineStr">
         <is>
-          <t>VA</t>
-        </is>
-      </c>
-      <c r="E75" s="119" t="n">
-        <v>5.25</v>
-      </c>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E75" s="119" t="n"/>
       <c r="F75" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -5812,7 +5802,7 @@
       </c>
       <c r="H75" s="94" t="inlineStr">
         <is>
-          <t>Material-Entnahme umgesetzt: Restlängen werden automatisch angelegt oder mit vorhandenen gleich langen Resten zusammengefasst.</t>
+          <t>Vorlesung PP 10:00-11:30 an der OTH, keine Anwesenheit im Betrieb</t>
         </is>
       </c>
       <c r="I75" s="86" t="n"/>
@@ -5853,7 +5843,7 @@
       </c>
       <c r="H76" s="94" t="inlineStr">
         <is>
-          <t>Material-Entnahme mit realen Zuschnitten aus der Werkstatt getestet und zwei Fehler bei der Restberechnung behoben.</t>
+          <t>Entwicklermodus ergänzt, der die Excel-Oberfläche für Wartungsarbeiten wieder einblendet, und mit einem Kennwort geschützt.</t>
         </is>
       </c>
       <c r="I76" s="86" t="n"/>
@@ -5894,7 +5884,7 @@
       </c>
       <c r="H77" s="67" t="inlineStr">
         <is>
-          <t>System einem Mitarbeiter gezeigt, Rückmeldungen aufgenommen und die Bedienung an zwei Stellen vereinfacht.</t>
+          <t>Makros in Modulgruppen aufgeteilt und benannt, damit die Datei wartbar bleibt und Funktionen wiederverwendet werden können.</t>
         </is>
       </c>
       <c r="I77" s="86" t="n"/>
@@ -5997,7 +5987,7 @@
       </c>
       <c r="H80" s="67" t="inlineStr">
         <is>
-          <t>Kurzanleitung für die Bedienung des Lagerbestand-Systems geschrieben und an den Arbeitsplatz gelegt.</t>
+          <t>Material-Entnahme-Logik entworfen: Beim Zuschnitt soll die Restlänge selbstständig eingebucht werden.</t>
         </is>
       </c>
       <c r="I80" s="86" t="n"/>
@@ -6038,7 +6028,7 @@
       </c>
       <c r="H81" s="67" t="inlineStr">
         <is>
-          <t>Schwachstellen des Excel-Systems zusammengetragen (Bindung an einen Rechner, kein Mehrbenutzerbetrieb) und die Neuentwicklung als eigenständige Web-Anwendung mit dem Betreuer besprochen. Architektur in drei Schichten festgelegt und mit KI-Unterstützung aufgesetzt.</t>
+          <t>Material-Entnahme umgesetzt: Restlängen werden automatisch angelegt oder mit vorhandenen gleich langen Resten zusammengefasst.</t>
         </is>
       </c>
       <c r="I81" s="86" t="n"/>
@@ -6061,12 +6051,10 @@
       </c>
       <c r="D82" s="65" t="inlineStr">
         <is>
-          <t>VA</t>
-        </is>
-      </c>
-      <c r="E82" s="119" t="n">
-        <v>5.5</v>
-      </c>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E82" s="119" t="n"/>
       <c r="F82" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -6079,7 +6067,7 @@
       </c>
       <c r="H82" s="67" t="inlineStr">
         <is>
-          <t>Datenmodell aus den Excel-Blättern übernommen und die Kernfunktionen portiert: Artikel verwalten, Buchungen, Verlauf und die Material-Entnahme mit Resteverwaltung. 86 reale Artikel-Datensätze und 50 Artikelgruppen übernommen und die Übernahme kontrolliert.</t>
+          <t>Vorlesung PP 10:00-11:30 an der OTH, keine Anwesenheit im Betrieb</t>
         </is>
       </c>
       <c r="I82" s="86" t="n"/>
@@ -6120,7 +6108,7 @@
       </c>
       <c r="H83" s="67" t="inlineStr">
         <is>
-          <t>Anwendung als Hintergrunddienst mit täglichem Backup eingerichtet und zusätzlich in der Cloud bereitgestellt. Lasttest mit 100 gleichzeitigen Schreibzugriffen durchgeführt und die Bedienung dokumentiert.</t>
+          <t>Material-Entnahme mit realen Zuschnitten aus der Werkstatt getestet und zwei Fehler bei der Restberechnung behoben.</t>
         </is>
       </c>
       <c r="I83" s="86" t="n"/>
@@ -6161,7 +6149,7 @@
       </c>
       <c r="H84" s="67" t="inlineStr">
         <is>
-          <t>Aufgabenstellung zum Schweißarbeitsplatz erhalten. Bestehenden Platz besichtigt, fotografiert und die verfügbare Fläche aufgemessen (rund 29 m²).</t>
+          <t>Schwachstellen des Excel-Systems zusammengetragen (Bindung an einen Rechner, kein Mehrbenutzerbetrieb) und die Neuentwicklung als eigenständige Web-Anwendung mit dem Betreuer besprochen. Architektur in drei Schichten festgelegt und mit KI-Unterstützung aufgesetzt.</t>
         </is>
       </c>
       <c r="I84" s="86" t="n"/>
@@ -6578,7 +6566,7 @@
       </c>
       <c r="H102" s="61" t="inlineStr">
         <is>
-          <t>Verwendete Schweißverfahren mit dem Betreuer besprochen (MAG/MIG und E-Hand) und die Unterschiede für die spätere Ausstattung festgehalten.</t>
+          <t>Datenmodell aus den Excel-Blättern übernommen und die Kernfunktionen portiert: Artikel verwalten, Buchungen, Verlauf und die Material-Entnahme mit Resteverwaltung. 86 reale Artikel-Datensätze und 50 Artikelgruppen übernommen und die Übernahme kontrolliert.</t>
         </is>
       </c>
       <c r="I102" s="86" t="n"/>
@@ -6619,7 +6607,7 @@
       </c>
       <c r="H103" s="67" t="inlineStr">
         <is>
-          <t>Aufnahme der vorhandenen Werkzeuge am Schweißplatz begonnen und nach Verwendungszweck gruppiert.</t>
+          <t>Anwendung als Hintergrunddienst mit täglichem Backup eingerichtet und zusätzlich in der Cloud bereitgestellt. Lasttest mit 100 gleichzeitigen Schreibzugriffen durchgeführt und die Bedienung dokumentiert.</t>
         </is>
       </c>
       <c r="I103" s="86" t="n"/>
@@ -6658,7 +6646,7 @@
       </c>
       <c r="H104" s="67" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00-11:30 und Praktikum Regelungstechnik 15:30-17:00 an der OTH, dazwischen keine Anwesenheit im Betrieb</t>
+          <t>Vorlesung PP 10:00-11:30 und Praktikum Regelungstechnik 15:30-17:00 an der OTH, keine Anwesenheit im Betrieb</t>
         </is>
       </c>
       <c r="I104" s="86" t="n"/>
@@ -6699,7 +6687,7 @@
       </c>
       <c r="H105" s="67" t="inlineStr">
         <is>
-          <t>Werkzeugaufnahme fortgesetzt: Kategorien Schweißen MAG/MIG und Schweißen E-Hand vollständig erfasst.</t>
+          <t>Aufgabenstellung zum Schweißarbeitsplatz erhalten. Bestehenden Platz besichtigt, fotografiert und die verfügbare Fläche aufgemessen (rund 29 m²).</t>
         </is>
       </c>
       <c r="I105" s="86" t="n"/>
@@ -6841,7 +6829,7 @@
       </c>
       <c r="H109" s="94" t="inlineStr">
         <is>
-          <t>Kategorien Spannen und Fixieren sowie Nachbearbeitung erfasst und mit den Mitarbeitern auf Vollständigkeit geprüft.</t>
+          <t>Verwendete Schweißverfahren mit dem Betreuer besprochen (MAG/MIG und E-Hand) und die Unterschiede für die spätere Ausstattung festgehalten.</t>
         </is>
       </c>
       <c r="I109" s="86" t="n"/>
@@ -6882,7 +6870,7 @@
       </c>
       <c r="H110" s="94" t="inlineStr">
         <is>
-          <t>Kategorien Anreißen und Messen sowie persönliche Schutzausrüstung für drei Personen zusammengestellt.</t>
+          <t>Aufnahme der vorhandenen Werkzeuge am Schweißplatz begonnen und nach Verwendungszweck gruppiert.</t>
         </is>
       </c>
       <c r="I110" s="86" t="n"/>
@@ -6905,12 +6893,10 @@
       </c>
       <c r="D111" s="65" t="inlineStr">
         <is>
-          <t>VA</t>
-        </is>
-      </c>
-      <c r="E111" s="119" t="n">
-        <v>5.5</v>
-      </c>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E111" s="119" t="n"/>
       <c r="F111" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -6923,7 +6909,7 @@
       </c>
       <c r="H111" s="94" t="inlineStr">
         <is>
-          <t>Kategorien Sicherheit und Umgebung, Verbrauchsmaterial sowie 5S-Möbel ergänzt. Damit sind alle neun Werkzeugkategorien A bis I erfasst.</t>
+          <t>Vorlesung PP 10:00-11:30 an der OTH, keine Anwesenheit im Betrieb</t>
         </is>
       </c>
       <c r="I111" s="86" t="n"/>
@@ -6964,7 +6950,7 @@
       </c>
       <c r="H112" s="94" t="inlineStr">
         <is>
-          <t>Marktrecherche zu den Werkzeugen begonnen und Richtpreise je Position gesammelt.</t>
+          <t>Werkzeugaufnahme fortgesetzt: Kategorien Schweißen MAG/MIG und Schweißen E-Hand vollständig erfasst.</t>
         </is>
       </c>
       <c r="I112" s="86" t="n"/>
@@ -7005,7 +6991,7 @@
       </c>
       <c r="H113" s="67" t="inlineStr">
         <is>
-          <t>Marktrecherche abgeschlossen und je Kaufteil drei Preisstufen gegenübergestellt.</t>
+          <t>Kategorien Spannen und Fixieren sowie Nachbearbeitung erfasst und mit den Mitarbeitern auf Vollständigkeit geprüft.</t>
         </is>
       </c>
       <c r="I113" s="86" t="n"/>
@@ -7108,7 +7094,7 @@
       </c>
       <c r="H116" s="94" t="inlineStr">
         <is>
-          <t>Ergonomische Grundmaße für den Arbeitsplatz zusammengetragen (Arbeitshöhe, Greifräume, Beleuchtung) und mit den Normvorgaben abgeglichen.</t>
+          <t>Kategorien Anreißen und Messen sowie persönliche Schutzausrüstung für drei Personen zusammengestellt.</t>
         </is>
       </c>
       <c r="I116" s="86" t="n"/>
@@ -7149,7 +7135,7 @@
       </c>
       <c r="H117" s="94" t="inlineStr">
         <is>
-          <t>Erstes Layout-Konzept für den Platz gezeichnet und die Wege zwischen Tisch, Maschine und Materialablage geprüft.</t>
+          <t>Kategorien Sicherheit und Umgebung, Verbrauchsmaterial sowie 5S-Möbel ergänzt. Damit sind alle neun Werkzeugkategorien A bis I erfasst.</t>
         </is>
       </c>
       <c r="I117" s="86" t="n"/>
@@ -7172,12 +7158,10 @@
       </c>
       <c r="D118" s="65" t="inlineStr">
         <is>
-          <t>VA</t>
-        </is>
-      </c>
-      <c r="E118" s="119" t="n">
-        <v>5.25</v>
-      </c>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E118" s="119" t="n"/>
       <c r="F118" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -7190,7 +7174,7 @@
       </c>
       <c r="H118" s="94" t="inlineStr">
         <is>
-          <t>Zwei weitere Layout-Varianten entwickelt und die drei Konzepte nebeneinandergestellt.</t>
+          <t>Vorlesung PP 10:00-11:30 an der OTH, keine Anwesenheit im Betrieb</t>
         </is>
       </c>
       <c r="I118" s="86" t="n"/>
@@ -7270,7 +7254,7 @@
       </c>
       <c r="H120" s="94" t="inlineStr">
         <is>
-          <t>Nutzwertanalyse für die Werkbank-Ausführung aufgestellt: Kriterien festgelegt und gewichtet.</t>
+          <t>Marktrecherche zu den Werkzeugen begonnen und Richtpreise je Position gesammelt.</t>
         </is>
       </c>
       <c r="I120" s="86" t="n"/>
@@ -7373,7 +7357,7 @@
       </c>
       <c r="H123" s="94" t="inlineStr">
         <is>
-          <t>Nutzwertanalyse für das Layout-Konzept gerechnet und die Ergebnisse ausgewertet.</t>
+          <t>Marktrecherche abgeschlossen und je Kaufteil drei Preisstufen gegenübergestellt.</t>
         </is>
       </c>
       <c r="I123" s="86" t="n"/>
@@ -7414,7 +7398,7 @@
       </c>
       <c r="H124" s="67" t="inlineStr">
         <is>
-          <t>Aufgabenstellung zum neuen Schweißtisch erhalten. Anforderungen mit dem Betreuer gesammelt: Größe, Spannmöglichkeiten, Fahrbarkeit.</t>
+          <t>Ergonomische Grundmaße für den Arbeitsplatz zusammengetragen (Arbeitshöhe, Greifräume, Beleuchtung) und mit den Normvorgaben abgeglichen.</t>
         </is>
       </c>
       <c r="I124" s="86" t="n"/>
@@ -7453,7 +7437,7 @@
       </c>
       <c r="H125" s="67" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00-11:30 und Praktikum Regelungstechnik 15:30-17:00 an der OTH, dazwischen keine Anwesenheit im Betrieb</t>
+          <t>Vorlesung PP 10:00-11:30 und Praktikum Regelungstechnik 15:30-17:00 an der OTH, keine Anwesenheit im Betrieb</t>
         </is>
       </c>
       <c r="I125" s="86" t="n"/>
@@ -7494,7 +7478,7 @@
       </c>
       <c r="H126" s="67" t="inlineStr">
         <is>
-          <t>Vorhandenen Tisch vermessen und die Schwachstellen im Betrieb aufgenommen.</t>
+          <t>Erstes Layout-Konzept für den Platz gezeichnet und die Wege zwischen Tisch, Maschine und Materialablage geprüft.</t>
         </is>
       </c>
       <c r="I126" s="86" t="n"/>
@@ -7535,7 +7519,7 @@
       </c>
       <c r="H127" s="67" t="inlineStr">
         <is>
-          <t>Recherche zu Schweißtisch-Konzepten und Spannsystemen durchgeführt, Beispiele gesammelt und bewertet.</t>
+          <t>Zwei weitere Layout-Varianten entwickelt und die drei Konzepte nebeneinandergestellt.</t>
         </is>
       </c>
       <c r="I127" s="86" t="n"/>
@@ -7991,7 +7975,7 @@
       </c>
       <c r="H146" s="94" t="inlineStr">
         <is>
-          <t>Erste Handskizzen für den neuen Tisch angefertigt und mit dem Betreuer besprochen.</t>
+          <t>Aufgabenstellung zum neuen Schweißtisch erhalten. Anforderungen mit dem Betreuer gesammelt: Größe, Spannmöglichkeiten, Fahrbarkeit.</t>
         </is>
       </c>
       <c r="I146" s="86" t="n"/>
@@ -8030,7 +8014,7 @@
       </c>
       <c r="H147" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00-11:30 und Praktikum Regelungstechnik 15:30-17:00 an der OTH, dazwischen keine Anwesenheit im Betrieb</t>
+          <t>Vorlesung PP 10:00-11:30 und Praktikum Regelungstechnik 15:30-17:00 an der OTH, keine Anwesenheit im Betrieb</t>
         </is>
       </c>
       <c r="I147" s="86" t="n"/>
@@ -8071,7 +8055,7 @@
       </c>
       <c r="H148" s="94" t="inlineStr">
         <is>
-          <t>Grundkonzept festgelegt: ausziehbarer Tisch mit Lochplatten-Spannsystem auf fahrbarem Untergestell.</t>
+          <t>Vorhandenen Tisch vermessen und die Schwachstellen im Betrieb aufgenommen.</t>
         </is>
       </c>
       <c r="I148" s="86" t="n"/>
@@ -8112,7 +8096,7 @@
       </c>
       <c r="H149" s="94" t="inlineStr">
         <is>
-          <t>Marktrecherche zu Lochplatten durchgeführt, Angebote verglichen und das D16-Raster ausgewählt.</t>
+          <t>Recherche zu Schweißtisch-Konzepten und Spannsystemen durchgeführt, Beispiele gesammelt und bewertet.</t>
         </is>
       </c>
       <c r="I149" s="86" t="n"/>
@@ -8215,7 +8199,7 @@
       </c>
       <c r="H152" s="94" t="inlineStr">
         <is>
-          <t>Mit der CAD-Konstruktion begonnen: Tischplatte mit Lochraster aufgebaut.</t>
+          <t>Erste Handskizzen für den neuen Tisch angefertigt und mit dem Betreuer besprochen.</t>
         </is>
       </c>
       <c r="I152" s="86" t="n"/>
@@ -8256,7 +8240,7 @@
       </c>
       <c r="H153" s="67" t="inlineStr">
         <is>
-          <t>Oberteil konstruiert: Träger und Profile modelliert und die Teilenummern vergeben.</t>
+          <t>Grundkonzept festgelegt: ausziehbarer Tisch mit Lochplatten-Spannsystem auf fahrbarem Untergestell.</t>
         </is>
       </c>
       <c r="I153" s="86" t="n"/>
@@ -8279,12 +8263,10 @@
       </c>
       <c r="D154" s="65" t="inlineStr">
         <is>
-          <t>VA</t>
-        </is>
-      </c>
-      <c r="E154" s="119" t="n">
-        <v>5.25</v>
-      </c>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E154" s="119" t="n"/>
       <c r="F154" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -8297,7 +8279,7 @@
       </c>
       <c r="H154" s="94" t="inlineStr">
         <is>
-          <t>Unterteil konstruiert: Beine, Streben und Fußplatten aufgebaut.</t>
+          <t>Vorlesung PP 10:00-11:30 an der OTH, keine Anwesenheit im Betrieb</t>
         </is>
       </c>
       <c r="I154" s="86" t="n"/>
@@ -8377,7 +8359,7 @@
       </c>
       <c r="H156" s="67" t="inlineStr">
         <is>
-          <t>Erweiterungssystem als Teleskop-Rahmen konstruiert, beidseitig ausziehbar.</t>
+          <t>Marktrecherche zu Lochplatten durchgeführt, Angebote verglichen und das D16-Raster ausgewählt.</t>
         </is>
       </c>
       <c r="I156" s="86" t="n"/>
@@ -8480,7 +8462,7 @@
       </c>
       <c r="H159" s="94" t="inlineStr">
         <is>
-          <t>Baugruppen zum Gesamtzusammenbau zusammengeführt und die Struktur geordnet.</t>
+          <t>Mit der CAD-Konstruktion begonnen: Tischplatte mit Lochraster aufgebaut.</t>
         </is>
       </c>
       <c r="I159" s="86" t="n"/>
@@ -8521,7 +8503,7 @@
       </c>
       <c r="H160" s="94" t="inlineStr">
         <is>
-          <t>Kollisionen und Verfahrwege im Modell geprüft und die Führungen angepasst.</t>
+          <t>Oberteil konstruiert: Träger und Profile modelliert und die Teilenummern vergeben.</t>
         </is>
       </c>
       <c r="I160" s="86" t="n"/>
@@ -8544,12 +8526,10 @@
       </c>
       <c r="D161" s="65" t="inlineStr">
         <is>
-          <t>VA</t>
-        </is>
-      </c>
-      <c r="E161" s="119" t="n">
-        <v>5</v>
-      </c>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E161" s="119" t="n"/>
       <c r="F161" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -8562,7 +8542,7 @@
       </c>
       <c r="H161" s="94" t="inlineStr">
         <is>
-          <t>Erste Zeichnungsblätter abgeleitet und bemaßt.</t>
+          <t>Vorlesung PP 10:00-11:30 an der OTH, keine Anwesenheit im Betrieb</t>
         </is>
       </c>
       <c r="I161" s="86" t="n"/>
@@ -8603,7 +8583,7 @@
       </c>
       <c r="H162" s="94" t="inlineStr">
         <is>
-          <t>Weitere Einzelteilzeichnungen erstellt und die Schriftfelder ausgefüllt.</t>
+          <t>Unterteil konstruiert: Beine, Streben und Fußplatten aufgebaut.</t>
         </is>
       </c>
       <c r="I162" s="86" t="n"/>
@@ -8644,7 +8624,7 @@
       </c>
       <c r="H163" s="94" t="inlineStr">
         <is>
-          <t>Aufgabenstellung zum Schweißmaschinenwagen erhalten. Vorhandenen Wagen im Betrieb fotografiert und den Zustand aufgenommen.</t>
+          <t>Erweiterungssystem als Teleskop-Rahmen konstruiert, beidseitig ausziehbar.</t>
         </is>
       </c>
       <c r="I163" s="86" t="n"/>
@@ -8747,7 +8727,7 @@
       </c>
       <c r="H166" s="94" t="inlineStr">
         <is>
-          <t>Schweißgerät und Gasflasche vor Ort aufgemessen und die Maße in einer Handskizze festgehalten.</t>
+          <t>Baugruppen zum Gesamtzusammenbau zusammengeführt und die Struktur geordnet.</t>
         </is>
       </c>
       <c r="I166" s="86" t="n"/>
@@ -8788,7 +8768,7 @@
       </c>
       <c r="H167" s="94" t="inlineStr">
         <is>
-          <t>Vereinfachte CAD-Platzhalter für Gerät und Flasche erstellt, um den Bauraum abzubilden.</t>
+          <t>Kollisionen und Verfahrwege im Modell geprüft und die Führungen angepasst.</t>
         </is>
       </c>
       <c r="I167" s="86" t="n"/>
@@ -8811,12 +8791,10 @@
       </c>
       <c r="D168" s="65" t="inlineStr">
         <is>
-          <t>VA</t>
-        </is>
-      </c>
-      <c r="E168" s="119" t="n">
-        <v>5</v>
-      </c>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E168" s="119" t="n"/>
       <c r="F168" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -8829,7 +8807,7 @@
       </c>
       <c r="H168" s="94" t="inlineStr">
         <is>
-          <t>Anforderungsliste aufgestellt: was der Wagen tragen und was er können muss.</t>
+          <t>Vorlesung PP 10:00-11:30 an der OTH, keine Anwesenheit im Betrieb</t>
         </is>
       </c>
       <c r="I168" s="86" t="n"/>
@@ -8870,7 +8848,7 @@
       </c>
       <c r="H169" s="67" t="inlineStr">
         <is>
-          <t>Anforderungsliste auf 14 nummerierte Punkte gebracht und mit dem Betreuer abgestimmt.</t>
+          <t>Aufgabenstellung zum Schweißmaschinenwagen erhalten. Vorhandenen Wagen im Betrieb fotografiert und den Zustand aufgenommen.</t>
         </is>
       </c>
       <c r="I169" s="86" t="n"/>
@@ -8911,7 +8889,7 @@
       </c>
       <c r="H170" s="94" t="inlineStr">
         <is>
-          <t>Referenzprojekte recherchiert und fünf Designrichtungen für den Wagen gesammelt.</t>
+          <t>Schweißgerät und Gasflasche vor Ort aufgemessen und die Maße in einer Handskizze festgehalten.</t>
         </is>
       </c>
       <c r="I170" s="86" t="n"/>
@@ -9328,7 +9306,7 @@
       </c>
       <c r="H188" s="94" t="inlineStr">
         <is>
-          <t>Zwei erste Entwürfe im CAD aufgebaut und gegenübergestellt.</t>
+          <t>Vereinfachte CAD-Platzhalter für Gerät und Flasche erstellt, um den Bauraum abzubilden.</t>
         </is>
       </c>
       <c r="I188" s="86" t="n"/>
@@ -9369,7 +9347,7 @@
       </c>
       <c r="H189" s="94" t="inlineStr">
         <is>
-          <t>Maße und Ergonomie festgelegt, Gewicht des beladenen Wagens grob abgeschätzt.</t>
+          <t>Anforderungsliste aufgestellt: was der Wagen tragen und was er können muss.</t>
         </is>
       </c>
       <c r="I189" s="86" t="n"/>
@@ -9392,12 +9370,10 @@
       </c>
       <c r="D190" s="65" t="inlineStr">
         <is>
-          <t>VA</t>
-        </is>
-      </c>
-      <c r="E190" s="119" t="n">
-        <v>5.25</v>
-      </c>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E190" s="119" t="n"/>
       <c r="F190" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -9410,7 +9386,7 @@
       </c>
       <c r="H190" s="94" t="inlineStr">
         <is>
-          <t>Kompletten Neubau als Variante A konstruiert und einen Belegungsplan mit 16 Werkzeugpositionen erstellt.</t>
+          <t>Vorlesung PP 10:00-11:30 an der OTH, keine Anwesenheit im Betrieb</t>
         </is>
       </c>
       <c r="I190" s="86" t="n"/>
@@ -9451,7 +9427,7 @@
       </c>
       <c r="H191" s="94" t="inlineStr">
         <is>
-          <t>Beim Maßabgleich festgestellt, dass das geplante Gerätefach zu niedrig für die vorhandene Maschine ist.</t>
+          <t>Anforderungsliste auf 14 nummerierte Punkte gebracht und mit dem Betreuer abgestimmt.</t>
         </is>
       </c>
       <c r="I191" s="86" t="n"/>
@@ -9492,7 +9468,7 @@
       </c>
       <c r="H192" s="94" t="inlineStr">
         <is>
-          <t>Als Variante B ein Aufsatzgestell entworfen, das über den vorhandenen Wagen fährt.</t>
+          <t>Referenzprojekte recherchiert und fünf Designrichtungen für den Wagen gesammelt.</t>
         </is>
       </c>
       <c r="I192" s="86" t="n"/>
@@ -9595,7 +9571,7 @@
       </c>
       <c r="H195" s="94" t="inlineStr">
         <is>
-          <t>Variante B überarbeitet, sodass die Gasflasche innerhalb der Aufstandsfläche steht.</t>
+          <t>Zwei erste Entwürfe im CAD aufgebaut und gegenübergestellt.</t>
         </is>
       </c>
       <c r="I195" s="86" t="n"/>
@@ -9636,7 +9612,7 @@
       </c>
       <c r="H196" s="94" t="inlineStr">
         <is>
-          <t>Vorzugsvariante festgelegt: modularer Aufbau in vier Etagen.</t>
+          <t>Maße und Ergonomie festgelegt, Gewicht des beladenen Wagens grob abgeschätzt.</t>
         </is>
       </c>
       <c r="I196" s="86" t="n"/>
@@ -9677,7 +9653,7 @@
       </c>
       <c r="H197" s="94" t="inlineStr">
         <is>
-          <t>Aufgabenstellung zum Zerspanarbeitsplatz erhalten und die Rahmenbedingungen aufgenommen (Drehen und Fräsen, drei Personen, eine Schicht).</t>
+          <t>Kompletten Neubau als Variante A konstruiert und einen Belegungsplan mit 16 Werkzeugpositionen erstellt.</t>
         </is>
       </c>
       <c r="I197" s="86" t="n"/>
@@ -9718,7 +9694,7 @@
       </c>
       <c r="H198" s="94" t="inlineStr">
         <is>
-          <t>Bestehenden Platz besichtigt, Maschinen und vorhandene Ausstattung fotografiert.</t>
+          <t>Beim Maßabgleich festgestellt, dass das geplante Gerätefach zu niedrig für die vorhandene Maschine ist.</t>
         </is>
       </c>
       <c r="I198" s="86" t="n"/>
@@ -9860,7 +9836,7 @@
       </c>
       <c r="H202" s="94" t="inlineStr">
         <is>
-          <t>Werkzeugbedarf für das Drehen zusammengestellt.</t>
+          <t>Als Variante B ein Aufsatzgestell entworfen, das über den vorhandenen Wagen fährt.</t>
         </is>
       </c>
       <c r="I202" s="86" t="n"/>
@@ -9901,7 +9877,7 @@
       </c>
       <c r="H203" s="94" t="inlineStr">
         <is>
-          <t>Werkzeugbedarf für das Fräsen sowie die Spann- und Aufspannmittel erfasst.</t>
+          <t>Aufgabenstellung zum Zerspanarbeitsplatz erhalten und die Rahmenbedingungen aufgenommen (Drehen und Fräsen, drei Personen, eine Schicht).</t>
         </is>
       </c>
       <c r="I203" s="86" t="n"/>
@@ -9942,7 +9918,7 @@
       </c>
       <c r="H204" s="67" t="inlineStr">
         <is>
-          <t>Mess- und Prüfmittel sowie Nacharbeit und Hilfsmittel ergänzt. Damit sind alle sechs Gruppen erfasst.</t>
+          <t>Bestehenden Platz besichtigt, Maschinen und vorhandene Ausstattung fotografiert.</t>
         </is>
       </c>
       <c r="I204" s="86" t="n"/>
@@ -9965,11 +9941,11 @@
       </c>
       <c r="D205" s="65" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="E205" s="119" t="n">
-        <v>7.25</v>
+        <v>4.25</v>
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
@@ -9978,12 +9954,12 @@
       </c>
       <c r="G205" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H205" s="99" t="inlineStr">
         <is>
-          <t>Mengen je Position festgelegt und begründet, welche Werkzeuge dreifach beschafft werden müssen.</t>
+          <t>Prüfung PRM an der OTH bis 10:00. Werkzeugbedarf für das Drehen zusammengestellt.</t>
         </is>
       </c>
       <c r="I205" s="86" t="n"/>
@@ -10010,7 +9986,7 @@
         </is>
       </c>
       <c r="E206" s="119" t="n">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
@@ -10024,7 +10000,7 @@
       </c>
       <c r="H206" s="67" t="inlineStr">
         <is>
-          <t>Preise recherchiert und die Werkzeugliste mit 35 Positionen bepreist.</t>
+          <t>Werkzeugbedarf für das Fräsen sowie die Spann- und Aufspannmittel erfasst.</t>
         </is>
       </c>
       <c r="I206" s="86" t="n"/>
@@ -10113,7 +10089,7 @@
         </is>
       </c>
       <c r="E209" s="119" t="n">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
@@ -10127,7 +10103,7 @@
       </c>
       <c r="H209" s="67" t="inlineStr">
         <is>
-          <t>Kosten nach Kategorien ausgewertet und die teuersten Positionen herausgearbeitet.</t>
+          <t>Mess- und Prüfmittel sowie Nacharbeit und Hilfsmittel ergänzt. Damit sind alle sechs Gruppen erfasst.</t>
         </is>
       </c>
       <c r="I209" s="86" t="n"/>
@@ -10154,7 +10130,7 @@
         </is>
       </c>
       <c r="E210" s="119" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
@@ -10168,7 +10144,7 @@
       </c>
       <c r="H210" s="67" t="inlineStr">
         <is>
-          <t>5S-Ordnung ausgearbeitet und die Werkzeuge den Zonen A, B und C zugeordnet.</t>
+          <t>Mengen je Position festgelegt und begründet, welche Werkzeuge dreifach beschafft werden müssen.</t>
         </is>
       </c>
       <c r="I210" s="86" t="n"/>
@@ -10195,7 +10171,7 @@
         </is>
       </c>
       <c r="E211" s="119" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
@@ -10209,7 +10185,7 @@
       </c>
       <c r="H211" s="67" t="inlineStr">
         <is>
-          <t>Grundmaße der Werkbank festgelegt und mit den Ergonomienormen abgeglichen.</t>
+          <t>Preise recherchiert und die Werkzeugliste mit 35 Positionen bepreist.</t>
         </is>
       </c>
       <c r="I211" s="86" t="n"/>
@@ -10250,7 +10226,7 @@
       </c>
       <c r="H212" s="67" t="inlineStr">
         <is>
-          <t>Vier Bauvarianten skizziert und in 3D dargestellt: Aluprofil, Stahl-Standard, Systemmodule und Eigenbau.</t>
+          <t>Kosten nach Kategorien ausgewertet und die teuersten Positionen herausgearbeitet.</t>
         </is>
       </c>
       <c r="I212" s="86" t="n"/>
@@ -10273,11 +10249,11 @@
       </c>
       <c r="D213" s="65" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="E213" s="119" t="n">
-        <v>7.25</v>
+        <v>4</v>
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
@@ -10286,12 +10262,12 @@
       </c>
       <c r="G213" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H213" s="67" t="inlineStr">
         <is>
-          <t>Vier Layout-Konzepte entwickelt und die Vor- und Nachteile gegenübergestellt.</t>
+          <t>Prüfung DA an der OTH bis 10:00. 5S-Ordnung ausgearbeitet und die Werkzeuge den Zonen A, B und C zugeordnet.</t>
         </is>
       </c>
       <c r="I213" s="86" t="n"/>
@@ -10690,11 +10666,11 @@
       </c>
       <c r="D231" s="59" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="E231" s="118" t="n">
-        <v>6.75</v>
+        <v>4.25</v>
       </c>
       <c r="F231" s="6" t="inlineStr">
         <is>
@@ -10703,12 +10679,12 @@
       </c>
       <c r="G231" s="8" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H231" s="61" t="inlineStr">
         <is>
-          <t>Werkstatt-Grundriss maßstäblich gezeichnet und die Freiräume an den Maschinen geprüft.</t>
+          <t>Prüfung GAT an der OTH bis 10:00. Grundmaße der Werkbank festgelegt und mit den Ergonomienormen abgeglichen.</t>
         </is>
       </c>
       <c r="I231" s="86" t="n"/>
@@ -10735,7 +10711,7 @@
         </is>
       </c>
       <c r="E232" s="119" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
@@ -10749,7 +10725,7 @@
       </c>
       <c r="H232" s="67" t="inlineStr">
         <is>
-          <t>Aufgabenstellung zum Rostschutz für die Schienenprofile erhalten. Lagerbedingungen der Profile im Betrieb aufgenommen und fotografiert.</t>
+          <t>Vier Bauvarianten skizziert und in 3D dargestellt: Aluprofil, Stahl-Standard, Systemmodule und Eigenbau.</t>
         </is>
       </c>
       <c r="I232" s="86" t="n"/>
@@ -10790,7 +10766,7 @@
       </c>
       <c r="H233" s="67" t="inlineStr">
         <is>
-          <t>Bestehende Rostschäden begutachtet und die Ursachen mit den Mitarbeitern besprochen (Feuchtigkeit, Kondenswasser, Lagerdauer).</t>
+          <t>Aufgabenstellung zum Rostschutz für die Schienenprofile erhalten. Lagerbedingungen der Profile im Betrieb aufgenommen und fotografiert.</t>
         </is>
       </c>
       <c r="I233" s="86" t="n"/>
@@ -10817,7 +10793,7 @@
         </is>
       </c>
       <c r="E234" s="119" t="n">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
@@ -10831,7 +10807,7 @@
       </c>
       <c r="H234" s="67" t="inlineStr">
         <is>
-          <t>Recherche zu Korrosionsschutzverfahren durchgeführt: Ölen, Wachsen, VCI-Folie und trockene Lagerung verglichen.</t>
+          <t>Bestehende Rostschäden begutachtet und die Ursachen mit den Mitarbeitern besprochen (Feuchtigkeit, Kondenswasser, Lagerdauer).</t>
         </is>
       </c>
       <c r="I234" s="86" t="n"/>
@@ -10858,7 +10834,7 @@
         </is>
       </c>
       <c r="E235" s="119" t="n">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
@@ -10872,7 +10848,7 @@
       </c>
       <c r="H235" s="67" t="inlineStr">
         <is>
-          <t>Verfahren gegenübergestellt und nach Wirksamkeit, Aufwand und Kosten bewertet.</t>
+          <t>Recherche zu Korrosionsschutzverfahren durchgeführt: Ölen, Wachsen, VCI-Folie und trockene Lagerung verglichen.</t>
         </is>
       </c>
       <c r="I235" s="86" t="n"/>
@@ -10961,7 +10937,7 @@
         </is>
       </c>
       <c r="E238" s="119" t="n">
-        <v>6.5</v>
+        <v>7.25</v>
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
@@ -10975,7 +10951,7 @@
       </c>
       <c r="H238" s="67" t="inlineStr">
         <is>
-          <t>Konzept für eine geschlossene Lagerbox mit VCI-Schutz entworfen und die benötigten Maße aufgenommen.</t>
+          <t>Verfahren gegenübergestellt und nach Wirksamkeit, Aufwand und Kosten bewertet.</t>
         </is>
       </c>
       <c r="I238" s="86" t="n"/>
@@ -10998,11 +10974,11 @@
       </c>
       <c r="D239" s="65" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="E239" s="119" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="F239" s="2" t="inlineStr">
         <is>
@@ -11011,12 +10987,12 @@
       </c>
       <c r="G239" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H239" s="67" t="inlineStr">
         <is>
-          <t>Lagerbox im CAD konstruiert und die Aufteilung für die verschiedenen Profillängen festgelegt.</t>
+          <t>Prüfung SWV an der OTH bis 10:00. Konzept für eine geschlossene Lagerbox mit VCI-Schutz entworfen und die benötigten Maße aufgenommen.</t>
         </is>
       </c>
       <c r="I239" s="86" t="n"/>
@@ -11043,7 +11019,7 @@
         </is>
       </c>
       <c r="E240" s="119" t="n">
-        <v>7.25</v>
+        <v>7.5</v>
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
@@ -11057,7 +11033,7 @@
       </c>
       <c r="H240" s="67" t="inlineStr">
         <is>
-          <t>Material- und Kostenaufstellung für die Schutzbox erstellt.</t>
+          <t>Lagerbox im CAD konstruiert und die Aufteilung für die verschiedenen Profillängen festgelegt.</t>
         </is>
       </c>
       <c r="I240" s="86" t="n"/>
@@ -11084,7 +11060,7 @@
         </is>
       </c>
       <c r="E241" s="119" t="n">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="F241" s="2" t="inlineStr">
         <is>
@@ -11098,7 +11074,7 @@
       </c>
       <c r="H241" s="67" t="inlineStr">
         <is>
-          <t>Zeitersparnis durch den Wegfall des Nacharbeitens abgeschätzt und der Investition gegenübergestellt.</t>
+          <t>Material- und Kostenaufstellung für die Schutzbox erstellt.</t>
         </is>
       </c>
       <c r="I241" s="86" t="n"/>
@@ -11139,7 +11115,7 @@
       </c>
       <c r="H242" s="67" t="inlineStr">
         <is>
-          <t>Arbeitsanweisung für die Einlagerung und Entnahme der Schienenprofile entworfen.</t>
+          <t>Zeitersparnis durch den Wegfall des Nacharbeitens abgeschätzt und der Investition gegenübergestellt.</t>
         </is>
       </c>
       <c r="I242" s="86" t="n"/>

--- a/hochschule/Hassine_3399727_Tätigkeitsnachweis.xlsx
+++ b/hochschule/Hassine_3399727_Tätigkeitsnachweis.xlsx
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="E16" s="118" t="n">
-        <v>8.25</v>
+        <v>8.5</v>
       </c>
       <c r="F16" s="91" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="E18" s="119" t="n">
-        <v>8</v>
+        <v>8.25</v>
       </c>
       <c r="F18" s="92" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="E23" s="119" t="n">
-        <v>8</v>
+        <v>8.25</v>
       </c>
       <c r="F23" s="92" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="E24" s="119" t="n">
-        <v>8.25</v>
+        <v>8.5</v>
       </c>
       <c r="F24" s="92" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         </is>
       </c>
       <c r="E25" s="119" t="n">
-        <v>8.25</v>
+        <v>8.5</v>
       </c>
       <c r="F25" s="92" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         </is>
       </c>
       <c r="E27" s="119" t="n">
-        <v>8.25</v>
+        <v>8.5</v>
       </c>
       <c r="F27" s="92" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="E31" s="119" t="n">
-        <v>8</v>
+        <v>8.25</v>
       </c>
       <c r="F31" s="92" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="E33" s="119" t="n">
-        <v>8</v>
+        <v>8.25</v>
       </c>
       <c r="F33" s="92" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         </is>
       </c>
       <c r="E38" s="119" t="n">
-        <v>8.25</v>
+        <v>8.5</v>
       </c>
       <c r="F38" s="92" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="E41" s="119" t="n">
-        <v>8.25</v>
+        <v>8.5</v>
       </c>
       <c r="F41" s="92" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         </is>
       </c>
       <c r="E60" s="119" t="n">
-        <v>8.25</v>
+        <v>8.5</v>
       </c>
       <c r="F60" s="92" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
         </is>
       </c>
       <c r="E67" s="119" t="n">
-        <v>8.25</v>
+        <v>8</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         </is>
       </c>
       <c r="E69" s="119" t="n">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         </is>
       </c>
       <c r="E70" s="119" t="n">
-        <v>8.5</v>
+        <v>8.25</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="E81" s="119" t="n">
-        <v>8.25</v>
+        <v>8</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         </is>
       </c>
       <c r="E83" s="119" t="n">
-        <v>8.5</v>
+        <v>8.25</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="E110" s="119" t="n">
-        <v>8.25</v>
+        <v>8</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         </is>
       </c>
       <c r="E112" s="119" t="n">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="E113" s="119" t="n">
-        <v>8.5</v>
+        <v>8.25</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -7080,7 +7080,7 @@
         </is>
       </c>
       <c r="E116" s="119" t="n">
-        <v>8.5</v>
+        <v>8.25</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         </is>
       </c>
       <c r="E117" s="119" t="n">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         </is>
       </c>
       <c r="E120" s="119" t="n">
-        <v>8.25</v>
+        <v>7.75</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -7384,7 +7384,7 @@
         </is>
       </c>
       <c r="E124" s="119" t="n">
-        <v>8.25</v>
+        <v>7.75</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         </is>
       </c>
       <c r="E126" s="119" t="n">
-        <v>8.25</v>
+        <v>7.75</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         </is>
       </c>
       <c r="E127" s="119" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="E146" s="119" t="n">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         </is>
       </c>
       <c r="E148" s="119" t="n">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         </is>
       </c>
       <c r="E149" s="119" t="n">
-        <v>8.25</v>
+        <v>8</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         </is>
       </c>
       <c r="E197" s="119" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         </is>
       </c>
       <c r="E205" s="119" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         </is>
       </c>
       <c r="E231" s="118" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="F231" s="6" t="inlineStr">
         <is>

--- a/hochschule/Hassine_3399727_Tätigkeitsnachweis.xlsx
+++ b/hochschule/Hassine_3399727_Tätigkeitsnachweis.xlsx
@@ -5260,10 +5260,12 @@
       </c>
       <c r="D61" s="65" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="E61" s="119" t="n"/>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="E61" s="119" t="n">
+        <v>3.75</v>
+      </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -5276,7 +5278,7 @@
       </c>
       <c r="H61" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00-11:30 an der OTH, keine Anwesenheit im Betrieb</t>
+          <t>Vorlesung PP bis 11:30, danach kurze Schicht im Betrieb. Weitere Eingabemasken für Bearbeiten und Löschen ergänzt und eine Sicherheitsabfrage vor dem Löschen eingebaut.</t>
         </is>
       </c>
       <c r="I61" s="86" t="n"/>
@@ -5317,7 +5319,7 @@
       </c>
       <c r="H62" s="94" t="inlineStr">
         <is>
-          <t>Weitere Eingabemasken für Bearbeiten und Löschen ergänzt und eine Sicherheitsabfrage vor dem Löschen eingebaut.</t>
+          <t>Filterfunktion über Bezeichnung, Profil, Maß und Materialgruppe umgesetzt und getestet.</t>
         </is>
       </c>
       <c r="I62" s="86" t="n"/>
@@ -5498,7 +5500,7 @@
       </c>
       <c r="H67" s="94" t="inlineStr">
         <is>
-          <t>Filterfunktion über Bezeichnung, Profil, Maß und Materialgruppe umgesetzt und getestet.</t>
+          <t>Export auf Knopfdruck umgesetzt: ausgewählte Blätter als Excel- oder PDF-Datei in einen festen Zielordner speichern.</t>
         </is>
       </c>
       <c r="I67" s="86" t="n"/>
@@ -5521,10 +5523,12 @@
       </c>
       <c r="D68" s="65" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="E68" s="119" t="n"/>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="E68" s="119" t="n">
+        <v>3.75</v>
+      </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -5537,7 +5541,7 @@
       </c>
       <c r="H68" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00-11:30 an der OTH, keine Anwesenheit im Betrieb</t>
+          <t>Vorlesung PP bis 11:30, danach kurze Schicht im Betrieb. Versand der Bestandsliste per E-Mail ergänzt und mit Testdaten geprüft.</t>
         </is>
       </c>
       <c r="I68" s="86" t="n"/>
@@ -5578,7 +5582,7 @@
       </c>
       <c r="H69" s="94" t="inlineStr">
         <is>
-          <t>Export auf Knopfdruck umgesetzt: ausgewählte Blätter als Excel- oder PDF-Datei in einen festen Zielordner speichern.</t>
+          <t>Einstellungsblatt angelegt, damit Zielordner, Empfängeradresse und Schwellenwerte ohne Eingriff in den Code änderbar sind.</t>
         </is>
       </c>
       <c r="I69" s="86" t="n"/>
@@ -5619,7 +5623,7 @@
       </c>
       <c r="H70" s="67" t="inlineStr">
         <is>
-          <t>Versand der Bestandsliste per E-Mail ergänzt und mit Testdaten geprüft.</t>
+          <t>Tablet-Modus entwickelt: Vollbild-Oberfläche ohne Excel-Bedienelemente, damit das System direkt in der Werkstatt bedienbar ist.</t>
         </is>
       </c>
       <c r="I70" s="86" t="n"/>
@@ -5722,7 +5726,7 @@
       </c>
       <c r="H73" s="94" t="inlineStr">
         <is>
-          <t>Einstellungsblatt angelegt, damit Zielordner, Empfängeradresse und Schwellenwerte ohne Eingriff in den Code änderbar sind.</t>
+          <t>Entwicklermodus ergänzt, der die Excel-Oberfläche für Wartungsarbeiten wieder einblendet, und mit einem Kennwort geschützt.</t>
         </is>
       </c>
       <c r="I73" s="86" t="n"/>
@@ -5763,7 +5767,7 @@
       </c>
       <c r="H74" s="94" t="inlineStr">
         <is>
-          <t>Tablet-Modus entwickelt: Vollbild-Oberfläche ohne Excel-Bedienelemente, damit das System direkt in der Werkstatt bedienbar ist.</t>
+          <t>Makros in Modulgruppen aufgeteilt und benannt, damit die Datei wartbar bleibt und Funktionen wiederverwendet werden können.</t>
         </is>
       </c>
       <c r="I74" s="86" t="n"/>
@@ -5843,7 +5847,7 @@
       </c>
       <c r="H76" s="94" t="inlineStr">
         <is>
-          <t>Entwicklermodus ergänzt, der die Excel-Oberfläche für Wartungsarbeiten wieder einblendet, und mit einem Kennwort geschützt.</t>
+          <t>Material-Entnahme-Logik entworfen: Beim Zuschnitt soll die Restlänge selbstständig eingebucht werden.</t>
         </is>
       </c>
       <c r="I76" s="86" t="n"/>
@@ -5884,7 +5888,7 @@
       </c>
       <c r="H77" s="67" t="inlineStr">
         <is>
-          <t>Makros in Modulgruppen aufgeteilt und benannt, damit die Datei wartbar bleibt und Funktionen wiederverwendet werden können.</t>
+          <t>Material-Entnahme umgesetzt: Restlängen werden automatisch angelegt oder mit vorhandenen gleich langen Resten zusammengefasst.</t>
         </is>
       </c>
       <c r="I77" s="86" t="n"/>
@@ -5987,7 +5991,7 @@
       </c>
       <c r="H80" s="67" t="inlineStr">
         <is>
-          <t>Material-Entnahme-Logik entworfen: Beim Zuschnitt soll die Restlänge selbstständig eingebucht werden.</t>
+          <t>Material-Entnahme mit realen Zuschnitten aus der Werkstatt getestet und zwei Fehler bei der Restberechnung behoben.</t>
         </is>
       </c>
       <c r="I80" s="86" t="n"/>
@@ -6028,7 +6032,7 @@
       </c>
       <c r="H81" s="67" t="inlineStr">
         <is>
-          <t>Material-Entnahme umgesetzt: Restlängen werden automatisch angelegt oder mit vorhandenen gleich langen Resten zusammengefasst.</t>
+          <t>System einem Mitarbeiter gezeigt, Rückmeldungen aufgenommen und die Bedienung an zwei Stellen vereinfacht.</t>
         </is>
       </c>
       <c r="I81" s="86" t="n"/>
@@ -6108,7 +6112,7 @@
       </c>
       <c r="H83" s="67" t="inlineStr">
         <is>
-          <t>Material-Entnahme mit realen Zuschnitten aus der Werkstatt getestet und zwei Fehler bei der Restberechnung behoben.</t>
+          <t>Schwachstellen des Excel-Systems zusammengetragen (Bindung an einen Rechner, kein Mehrbenutzerbetrieb) und die Neuentwicklung als eigenständige Web-Anwendung mit dem Betreuer besprochen. Architektur in drei Schichten festgelegt und mit KI-Unterstützung aufgesetzt.</t>
         </is>
       </c>
       <c r="I83" s="86" t="n"/>
@@ -6149,7 +6153,7 @@
       </c>
       <c r="H84" s="67" t="inlineStr">
         <is>
-          <t>Schwachstellen des Excel-Systems zusammengetragen (Bindung an einen Rechner, kein Mehrbenutzerbetrieb) und die Neuentwicklung als eigenständige Web-Anwendung mit dem Betreuer besprochen. Architektur in drei Schichten festgelegt und mit KI-Unterstützung aufgesetzt.</t>
+          <t>Datenmodell aus den Excel-Blättern übernommen und die Kernfunktionen portiert: Artikel verwalten, Buchungen, Verlauf und die Material-Entnahme mit Resteverwaltung. 86 reale Artikel-Datensätze und 50 Artikelgruppen übernommen und die Übernahme kontrolliert.</t>
         </is>
       </c>
       <c r="I84" s="86" t="n"/>
@@ -6566,7 +6570,7 @@
       </c>
       <c r="H102" s="61" t="inlineStr">
         <is>
-          <t>Datenmodell aus den Excel-Blättern übernommen und die Kernfunktionen portiert: Artikel verwalten, Buchungen, Verlauf und die Material-Entnahme mit Resteverwaltung. 86 reale Artikel-Datensätze und 50 Artikelgruppen übernommen und die Übernahme kontrolliert.</t>
+          <t>Anwendung als Hintergrunddienst mit täglichem Backup eingerichtet und zusätzlich in der Cloud bereitgestellt. Lasttest mit 100 gleichzeitigen Schreibzugriffen durchgeführt und die Bedienung dokumentiert.</t>
         </is>
       </c>
       <c r="I102" s="86" t="n"/>
@@ -6607,7 +6611,7 @@
       </c>
       <c r="H103" s="67" t="inlineStr">
         <is>
-          <t>Anwendung als Hintergrunddienst mit täglichem Backup eingerichtet und zusätzlich in der Cloud bereitgestellt. Lasttest mit 100 gleichzeitigen Schreibzugriffen durchgeführt und die Bedienung dokumentiert.</t>
+          <t>Aufgabenstellung zum Schweißarbeitsplatz erhalten. Bestehenden Platz besichtigt, fotografiert und die verfügbare Fläche aufgemessen (rund 29 m²).</t>
         </is>
       </c>
       <c r="I103" s="86" t="n"/>
@@ -6687,7 +6691,7 @@
       </c>
       <c r="H105" s="67" t="inlineStr">
         <is>
-          <t>Aufgabenstellung zum Schweißarbeitsplatz erhalten. Bestehenden Platz besichtigt, fotografiert und die verfügbare Fläche aufgemessen (rund 29 m²).</t>
+          <t>Verwendete Schweißverfahren mit dem Betreuer besprochen (MAG/MIG und E-Hand) und die Unterschiede für die spätere Ausstattung festgehalten.</t>
         </is>
       </c>
       <c r="I105" s="86" t="n"/>
@@ -6829,7 +6833,7 @@
       </c>
       <c r="H109" s="94" t="inlineStr">
         <is>
-          <t>Verwendete Schweißverfahren mit dem Betreuer besprochen (MAG/MIG und E-Hand) und die Unterschiede für die spätere Ausstattung festgehalten.</t>
+          <t>Aufnahme der vorhandenen Werkzeuge am Schweißplatz begonnen und nach Verwendungszweck gruppiert.</t>
         </is>
       </c>
       <c r="I109" s="86" t="n"/>
@@ -6870,7 +6874,7 @@
       </c>
       <c r="H110" s="94" t="inlineStr">
         <is>
-          <t>Aufnahme der vorhandenen Werkzeuge am Schweißplatz begonnen und nach Verwendungszweck gruppiert.</t>
+          <t>Werkzeugaufnahme fortgesetzt: Kategorien Schweißen MAG/MIG und Schweißen E-Hand vollständig erfasst.</t>
         </is>
       </c>
       <c r="I110" s="86" t="n"/>
@@ -6950,7 +6954,7 @@
       </c>
       <c r="H112" s="94" t="inlineStr">
         <is>
-          <t>Werkzeugaufnahme fortgesetzt: Kategorien Schweißen MAG/MIG und Schweißen E-Hand vollständig erfasst.</t>
+          <t>Kategorien Spannen und Fixieren sowie Nachbearbeitung erfasst und mit den Mitarbeitern auf Vollständigkeit geprüft.</t>
         </is>
       </c>
       <c r="I112" s="86" t="n"/>
@@ -6991,7 +6995,7 @@
       </c>
       <c r="H113" s="67" t="inlineStr">
         <is>
-          <t>Kategorien Spannen und Fixieren sowie Nachbearbeitung erfasst und mit den Mitarbeitern auf Vollständigkeit geprüft.</t>
+          <t>Kategorien Anreißen und Messen sowie persönliche Schutzausrüstung für drei Personen zusammengestellt.</t>
         </is>
       </c>
       <c r="I113" s="86" t="n"/>
@@ -7094,7 +7098,7 @@
       </c>
       <c r="H116" s="94" t="inlineStr">
         <is>
-          <t>Kategorien Anreißen und Messen sowie persönliche Schutzausrüstung für drei Personen zusammengestellt.</t>
+          <t>Kategorien Sicherheit und Umgebung, Verbrauchsmaterial sowie 5S-Möbel ergänzt. Damit sind alle neun Werkzeugkategorien A bis I erfasst.</t>
         </is>
       </c>
       <c r="I116" s="86" t="n"/>
@@ -7135,7 +7139,7 @@
       </c>
       <c r="H117" s="94" t="inlineStr">
         <is>
-          <t>Kategorien Sicherheit und Umgebung, Verbrauchsmaterial sowie 5S-Möbel ergänzt. Damit sind alle neun Werkzeugkategorien A bis I erfasst.</t>
+          <t>Marktrecherche zu den Werkzeugen begonnen und Richtpreise je Position gesammelt.</t>
         </is>
       </c>
       <c r="I117" s="86" t="n"/>
@@ -7158,10 +7162,12 @@
       </c>
       <c r="D118" s="65" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="E118" s="119" t="n"/>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="E118" s="119" t="n">
+        <v>3.75</v>
+      </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -7174,7 +7180,7 @@
       </c>
       <c r="H118" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00-11:30 an der OTH, keine Anwesenheit im Betrieb</t>
+          <t>Vorlesung PP bis 11:30, danach kurze Schicht im Betrieb. Marktrecherche abgeschlossen und je Kaufteil drei Preisstufen gegenübergestellt.</t>
         </is>
       </c>
       <c r="I118" s="86" t="n"/>
@@ -7254,7 +7260,7 @@
       </c>
       <c r="H120" s="94" t="inlineStr">
         <is>
-          <t>Marktrecherche zu den Werkzeugen begonnen und Richtpreise je Position gesammelt.</t>
+          <t>Ergonomische Grundmaße für den Arbeitsplatz zusammengetragen (Arbeitshöhe, Greifräume, Beleuchtung) und mit den Normvorgaben abgeglichen.</t>
         </is>
       </c>
       <c r="I120" s="86" t="n"/>
@@ -7357,7 +7363,7 @@
       </c>
       <c r="H123" s="94" t="inlineStr">
         <is>
-          <t>Marktrecherche abgeschlossen und je Kaufteil drei Preisstufen gegenübergestellt.</t>
+          <t>Erstes Layout-Konzept für den Platz gezeichnet und die Wege zwischen Tisch, Maschine und Materialablage geprüft.</t>
         </is>
       </c>
       <c r="I123" s="86" t="n"/>
@@ -7398,7 +7404,7 @@
       </c>
       <c r="H124" s="67" t="inlineStr">
         <is>
-          <t>Ergonomische Grundmaße für den Arbeitsplatz zusammengetragen (Arbeitshöhe, Greifräume, Beleuchtung) und mit den Normvorgaben abgeglichen.</t>
+          <t>Zwei weitere Layout-Varianten entwickelt und die drei Konzepte nebeneinandergestellt.</t>
         </is>
       </c>
       <c r="I124" s="86" t="n"/>
@@ -7478,7 +7484,7 @@
       </c>
       <c r="H126" s="67" t="inlineStr">
         <is>
-          <t>Erstes Layout-Konzept für den Platz gezeichnet und die Wege zwischen Tisch, Maschine und Materialablage geprüft.</t>
+          <t>Nutzwertanalyse für die Werkbank-Ausführung aufgestellt: Kriterien festgelegt und gewichtet.</t>
         </is>
       </c>
       <c r="I126" s="86" t="n"/>
@@ -7519,7 +7525,7 @@
       </c>
       <c r="H127" s="67" t="inlineStr">
         <is>
-          <t>Zwei weitere Layout-Varianten entwickelt und die drei Konzepte nebeneinandergestellt.</t>
+          <t>Aufgabenstellung zum neuen Schweißtisch erhalten. Anforderungen mit dem Betreuer gesammelt: Größe, Spannmöglichkeiten, Fahrbarkeit.</t>
         </is>
       </c>
       <c r="I127" s="86" t="n"/>
@@ -7975,7 +7981,7 @@
       </c>
       <c r="H146" s="94" t="inlineStr">
         <is>
-          <t>Aufgabenstellung zum neuen Schweißtisch erhalten. Anforderungen mit dem Betreuer gesammelt: Größe, Spannmöglichkeiten, Fahrbarkeit.</t>
+          <t>Vorhandenen Tisch vermessen und die Schwachstellen im Betrieb aufgenommen.</t>
         </is>
       </c>
       <c r="I146" s="86" t="n"/>
@@ -8055,7 +8061,7 @@
       </c>
       <c r="H148" s="94" t="inlineStr">
         <is>
-          <t>Vorhandenen Tisch vermessen und die Schwachstellen im Betrieb aufgenommen.</t>
+          <t>Recherche zu Schweißtisch-Konzepten und Spannsystemen durchgeführt, Beispiele gesammelt und bewertet.</t>
         </is>
       </c>
       <c r="I148" s="86" t="n"/>
@@ -8096,7 +8102,7 @@
       </c>
       <c r="H149" s="94" t="inlineStr">
         <is>
-          <t>Recherche zu Schweißtisch-Konzepten und Spannsystemen durchgeführt, Beispiele gesammelt und bewertet.</t>
+          <t>Erste Handskizzen für den neuen Tisch angefertigt und mit dem Betreuer besprochen.</t>
         </is>
       </c>
       <c r="I149" s="86" t="n"/>
@@ -8199,7 +8205,7 @@
       </c>
       <c r="H152" s="94" t="inlineStr">
         <is>
-          <t>Erste Handskizzen für den neuen Tisch angefertigt und mit dem Betreuer besprochen.</t>
+          <t>Grundkonzept festgelegt: ausziehbarer Tisch mit Lochplatten-Spannsystem auf fahrbarem Untergestell.</t>
         </is>
       </c>
       <c r="I152" s="86" t="n"/>
@@ -8240,7 +8246,7 @@
       </c>
       <c r="H153" s="67" t="inlineStr">
         <is>
-          <t>Grundkonzept festgelegt: ausziehbarer Tisch mit Lochplatten-Spannsystem auf fahrbarem Untergestell.</t>
+          <t>Marktrecherche zu Lochplatten durchgeführt, Angebote verglichen und das D16-Raster ausgewählt.</t>
         </is>
       </c>
       <c r="I153" s="86" t="n"/>
@@ -8263,10 +8269,12 @@
       </c>
       <c r="D154" s="65" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="E154" s="119" t="n"/>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="E154" s="119" t="n">
+        <v>3.75</v>
+      </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -8279,7 +8287,7 @@
       </c>
       <c r="H154" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00-11:30 an der OTH, keine Anwesenheit im Betrieb</t>
+          <t>Vorlesung PP bis 11:30, danach kurze Schicht im Betrieb. Mit der CAD-Konstruktion begonnen: Tischplatte mit Lochraster aufgebaut.</t>
         </is>
       </c>
       <c r="I154" s="86" t="n"/>
@@ -8359,7 +8367,7 @@
       </c>
       <c r="H156" s="67" t="inlineStr">
         <is>
-          <t>Marktrecherche zu Lochplatten durchgeführt, Angebote verglichen und das D16-Raster ausgewählt.</t>
+          <t>Oberteil konstruiert: Träger und Profile modelliert und die Teilenummern vergeben.</t>
         </is>
       </c>
       <c r="I156" s="86" t="n"/>
@@ -8462,7 +8470,7 @@
       </c>
       <c r="H159" s="94" t="inlineStr">
         <is>
-          <t>Mit der CAD-Konstruktion begonnen: Tischplatte mit Lochraster aufgebaut.</t>
+          <t>Unterteil konstruiert: Beine, Streben und Fußplatten aufgebaut.</t>
         </is>
       </c>
       <c r="I159" s="86" t="n"/>
@@ -8503,7 +8511,7 @@
       </c>
       <c r="H160" s="94" t="inlineStr">
         <is>
-          <t>Oberteil konstruiert: Träger und Profile modelliert und die Teilenummern vergeben.</t>
+          <t>Erweiterungssystem als Teleskop-Rahmen konstruiert, beidseitig ausziehbar.</t>
         </is>
       </c>
       <c r="I160" s="86" t="n"/>
@@ -8583,7 +8591,7 @@
       </c>
       <c r="H162" s="94" t="inlineStr">
         <is>
-          <t>Unterteil konstruiert: Beine, Streben und Fußplatten aufgebaut.</t>
+          <t>Baugruppen zum Gesamtzusammenbau zusammengeführt und die Struktur geordnet.</t>
         </is>
       </c>
       <c r="I162" s="86" t="n"/>
@@ -8624,7 +8632,7 @@
       </c>
       <c r="H163" s="94" t="inlineStr">
         <is>
-          <t>Erweiterungssystem als Teleskop-Rahmen konstruiert, beidseitig ausziehbar.</t>
+          <t>Kollisionen und Verfahrwege im Modell geprüft und die Führungen angepasst.</t>
         </is>
       </c>
       <c r="I163" s="86" t="n"/>
@@ -8727,7 +8735,7 @@
       </c>
       <c r="H166" s="94" t="inlineStr">
         <is>
-          <t>Baugruppen zum Gesamtzusammenbau zusammengeführt und die Struktur geordnet.</t>
+          <t>Erste Zeichnungsblätter abgeleitet und bemaßt.</t>
         </is>
       </c>
       <c r="I166" s="86" t="n"/>
@@ -8768,7 +8776,7 @@
       </c>
       <c r="H167" s="94" t="inlineStr">
         <is>
-          <t>Kollisionen und Verfahrwege im Modell geprüft und die Führungen angepasst.</t>
+          <t>Aufgabenstellung zum Schweißmaschinenwagen erhalten. Vorhandenen Wagen im Betrieb fotografiert und den Zustand aufgenommen.</t>
         </is>
       </c>
       <c r="I167" s="86" t="n"/>
@@ -8848,7 +8856,7 @@
       </c>
       <c r="H169" s="67" t="inlineStr">
         <is>
-          <t>Aufgabenstellung zum Schweißmaschinenwagen erhalten. Vorhandenen Wagen im Betrieb fotografiert und den Zustand aufgenommen.</t>
+          <t>Schweißgerät und Gasflasche vor Ort aufgemessen und die Maße in einer Handskizze festgehalten.</t>
         </is>
       </c>
       <c r="I169" s="86" t="n"/>
@@ -8889,7 +8897,7 @@
       </c>
       <c r="H170" s="94" t="inlineStr">
         <is>
-          <t>Schweißgerät und Gasflasche vor Ort aufgemessen und die Maße in einer Handskizze festgehalten.</t>
+          <t>Vereinfachte CAD-Platzhalter für Gerät und Flasche erstellt, um den Bauraum abzubilden.</t>
         </is>
       </c>
       <c r="I170" s="86" t="n"/>
@@ -9306,7 +9314,7 @@
       </c>
       <c r="H188" s="94" t="inlineStr">
         <is>
-          <t>Vereinfachte CAD-Platzhalter für Gerät und Flasche erstellt, um den Bauraum abzubilden.</t>
+          <t>Anforderungsliste aufgestellt: was der Wagen tragen und was er können muss.</t>
         </is>
       </c>
       <c r="I188" s="86" t="n"/>
@@ -9347,7 +9355,7 @@
       </c>
       <c r="H189" s="94" t="inlineStr">
         <is>
-          <t>Anforderungsliste aufgestellt: was der Wagen tragen und was er können muss.</t>
+          <t>Anforderungsliste auf 14 nummerierte Punkte gebracht und mit dem Betreuer abgestimmt.</t>
         </is>
       </c>
       <c r="I189" s="86" t="n"/>
@@ -9427,7 +9435,7 @@
       </c>
       <c r="H191" s="94" t="inlineStr">
         <is>
-          <t>Anforderungsliste auf 14 nummerierte Punkte gebracht und mit dem Betreuer abgestimmt.</t>
+          <t>Referenzprojekte recherchiert und fünf Designrichtungen für den Wagen gesammelt.</t>
         </is>
       </c>
       <c r="I191" s="86" t="n"/>
@@ -9468,7 +9476,7 @@
       </c>
       <c r="H192" s="94" t="inlineStr">
         <is>
-          <t>Referenzprojekte recherchiert und fünf Designrichtungen für den Wagen gesammelt.</t>
+          <t>Zwei erste Entwürfe im CAD aufgebaut und gegenübergestellt.</t>
         </is>
       </c>
       <c r="I192" s="86" t="n"/>
@@ -9571,7 +9579,7 @@
       </c>
       <c r="H195" s="94" t="inlineStr">
         <is>
-          <t>Zwei erste Entwürfe im CAD aufgebaut und gegenübergestellt.</t>
+          <t>Maße und Ergonomie festgelegt, Gewicht des beladenen Wagens grob abgeschätzt.</t>
         </is>
       </c>
       <c r="I195" s="86" t="n"/>
@@ -9612,7 +9620,7 @@
       </c>
       <c r="H196" s="94" t="inlineStr">
         <is>
-          <t>Maße und Ergonomie festgelegt, Gewicht des beladenen Wagens grob abgeschätzt.</t>
+          <t>Kompletten Neubau als Variante A konstruiert und einen Belegungsplan mit 16 Werkzeugpositionen erstellt.</t>
         </is>
       </c>
       <c r="I196" s="86" t="n"/>
@@ -9653,7 +9661,7 @@
       </c>
       <c r="H197" s="94" t="inlineStr">
         <is>
-          <t>Kompletten Neubau als Variante A konstruiert und einen Belegungsplan mit 16 Werkzeugpositionen erstellt.</t>
+          <t>Beim Maßabgleich festgestellt, dass das geplante Gerätefach zu niedrig für die vorhandene Maschine ist.</t>
         </is>
       </c>
       <c r="I197" s="86" t="n"/>
@@ -9694,7 +9702,7 @@
       </c>
       <c r="H198" s="94" t="inlineStr">
         <is>
-          <t>Beim Maßabgleich festgestellt, dass das geplante Gerätefach zu niedrig für die vorhandene Maschine ist.</t>
+          <t>Als Variante B ein Aufsatzgestell entworfen, das über den vorhandenen Wagen fährt.</t>
         </is>
       </c>
       <c r="I198" s="86" t="n"/>
@@ -9836,7 +9844,7 @@
       </c>
       <c r="H202" s="94" t="inlineStr">
         <is>
-          <t>Als Variante B ein Aufsatzgestell entworfen, das über den vorhandenen Wagen fährt.</t>
+          <t>Aufgabenstellung zum Zerspanarbeitsplatz erhalten und die Rahmenbedingungen aufgenommen (Drehen und Fräsen, drei Personen, eine Schicht).</t>
         </is>
       </c>
       <c r="I202" s="86" t="n"/>
@@ -9877,7 +9885,7 @@
       </c>
       <c r="H203" s="94" t="inlineStr">
         <is>
-          <t>Aufgabenstellung zum Zerspanarbeitsplatz erhalten und die Rahmenbedingungen aufgenommen (Drehen und Fräsen, drei Personen, eine Schicht).</t>
+          <t>Bestehenden Platz besichtigt, Maschinen und vorhandene Ausstattung fotografiert.</t>
         </is>
       </c>
       <c r="I203" s="86" t="n"/>
@@ -9918,7 +9926,7 @@
       </c>
       <c r="H204" s="67" t="inlineStr">
         <is>
-          <t>Bestehenden Platz besichtigt, Maschinen und vorhandene Ausstattung fotografiert.</t>
+          <t>Werkzeugbedarf für das Drehen zusammengestellt.</t>
         </is>
       </c>
       <c r="I204" s="86" t="n"/>
@@ -9959,7 +9967,7 @@
       </c>
       <c r="H205" s="99" t="inlineStr">
         <is>
-          <t>Prüfung PRM an der OTH bis 10:00. Werkzeugbedarf für das Drehen zusammengestellt.</t>
+          <t>Prüfung PRM an der OTH bis 10:00. Werkzeugbedarf für das Fräsen sowie die Spann- und Aufspannmittel erfasst.</t>
         </is>
       </c>
       <c r="I205" s="86" t="n"/>
@@ -10000,7 +10008,7 @@
       </c>
       <c r="H206" s="67" t="inlineStr">
         <is>
-          <t>Werkzeugbedarf für das Fräsen sowie die Spann- und Aufspannmittel erfasst.</t>
+          <t>Mess- und Prüfmittel sowie Nacharbeit und Hilfsmittel ergänzt. Damit sind alle sechs Gruppen erfasst.</t>
         </is>
       </c>
       <c r="I206" s="86" t="n"/>
@@ -10103,7 +10111,7 @@
       </c>
       <c r="H209" s="67" t="inlineStr">
         <is>
-          <t>Mess- und Prüfmittel sowie Nacharbeit und Hilfsmittel ergänzt. Damit sind alle sechs Gruppen erfasst.</t>
+          <t>Mengen je Position festgelegt und begründet, welche Werkzeuge dreifach beschafft werden müssen.</t>
         </is>
       </c>
       <c r="I209" s="86" t="n"/>
@@ -10144,7 +10152,7 @@
       </c>
       <c r="H210" s="67" t="inlineStr">
         <is>
-          <t>Mengen je Position festgelegt und begründet, welche Werkzeuge dreifach beschafft werden müssen.</t>
+          <t>Preise recherchiert und die Werkzeugliste mit 35 Positionen bepreist.</t>
         </is>
       </c>
       <c r="I210" s="86" t="n"/>
@@ -10185,7 +10193,7 @@
       </c>
       <c r="H211" s="67" t="inlineStr">
         <is>
-          <t>Preise recherchiert und die Werkzeugliste mit 35 Positionen bepreist.</t>
+          <t>Kosten nach Kategorien ausgewertet und die teuersten Positionen herausgearbeitet.</t>
         </is>
       </c>
       <c r="I211" s="86" t="n"/>
@@ -10226,7 +10234,7 @@
       </c>
       <c r="H212" s="67" t="inlineStr">
         <is>
-          <t>Kosten nach Kategorien ausgewertet und die teuersten Positionen herausgearbeitet.</t>
+          <t>5S-Ordnung ausgearbeitet und die Werkzeuge den Zonen A, B und C zugeordnet.</t>
         </is>
       </c>
       <c r="I212" s="86" t="n"/>
@@ -10267,7 +10275,7 @@
       </c>
       <c r="H213" s="67" t="inlineStr">
         <is>
-          <t>Prüfung DA an der OTH bis 10:00. 5S-Ordnung ausgearbeitet und die Werkzeuge den Zonen A, B und C zugeordnet.</t>
+          <t>Prüfung DA an der OTH bis 10:00. Grundmaße der Werkbank festgelegt und mit den Ergonomienormen abgeglichen.</t>
         </is>
       </c>
       <c r="I213" s="86" t="n"/>
@@ -10684,7 +10692,7 @@
       </c>
       <c r="H231" s="61" t="inlineStr">
         <is>
-          <t>Prüfung GAT an der OTH bis 10:00. Grundmaße der Werkbank festgelegt und mit den Ergonomienormen abgeglichen.</t>
+          <t>Prüfung GAT an der OTH bis 10:00. Vier Bauvarianten skizziert und in 3D dargestellt: Aluprofil, Stahl-Standard, Systemmodule und Eigenbau.</t>
         </is>
       </c>
       <c r="I231" s="86" t="n"/>
@@ -10725,7 +10733,7 @@
       </c>
       <c r="H232" s="67" t="inlineStr">
         <is>
-          <t>Vier Bauvarianten skizziert und in 3D dargestellt: Aluprofil, Stahl-Standard, Systemmodule und Eigenbau.</t>
+          <t>Vier Layout-Konzepte entwickelt und die Vor- und Nachteile gegenübergestellt.</t>
         </is>
       </c>
       <c r="I232" s="86" t="n"/>

--- a/hochschule/Hassine_3399727_Tätigkeitsnachweis.xlsx
+++ b/hochschule/Hassine_3399727_Tätigkeitsnachweis.xlsx
@@ -4413,10 +4413,12 @@
       </c>
       <c r="D32" s="65" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="E32" s="119" t="n"/>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="E32" s="119" t="n">
+        <v>4</v>
+      </c>
       <c r="F32" s="92" t="inlineStr">
         <is>
           <t>h</t>
@@ -4429,7 +4431,7 @@
       </c>
       <c r="H32" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00-11:30 an der OTH, keine Anwesenheit im Betrieb</t>
+          <t>Vorlesung PP bis 11:30, danach im Betrieb. Belegungsplan erstellt: jeder der 135 Sorten einen festen, beschrifteten Platz zugeordnet. Bezugsquellen recherchiert, Ergebnisse dem Betreuer vorgestellt und eine Arbeitsanweisung für die Materialentnahme entworfen.</t>
         </is>
       </c>
       <c r="I32" s="86" t="n"/>
@@ -4681,10 +4683,12 @@
       </c>
       <c r="D39" s="65" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="E39" s="119" t="n"/>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="E39" s="119" t="n">
+        <v>4</v>
+      </c>
       <c r="F39" s="92" t="inlineStr">
         <is>
           <t>h</t>
@@ -4697,7 +4701,7 @@
       </c>
       <c r="H39" s="95" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00-11:30 an der OTH, keine Anwesenheit im Betrieb</t>
+          <t>Vorlesung PP bis 11:30, danach im Betrieb. Barcode-Suche umgesetzt: Der eingescannte Code springt zum Artikel und zeigt alle Felder im Dashboard an.</t>
         </is>
       </c>
       <c r="I39" s="86" t="n"/>
@@ -4738,7 +4742,7 @@
       </c>
       <c r="H40" s="94" t="inlineStr">
         <is>
-          <t>Barcode-Suche umgesetzt: Der eingescannte Code springt zum Artikel und zeigt alle Felder im Dashboard an.</t>
+          <t>Dashboard als Bedienoberfläche gestaltet: Scannfunktionen links, Suchergebnis in der Mitte, Exportbereich rechts.</t>
         </is>
       </c>
       <c r="I40" s="86" t="n"/>
@@ -4779,7 +4783,7 @@
       </c>
       <c r="H41" s="67" t="inlineStr">
         <is>
-          <t>Dashboard als Bedienoberfläche gestaltet: Scannfunktionen links, Suchergebnis in der Mitte, Exportbereich rechts.</t>
+          <t>Automatische Färbung des Bestands nach Soll- und Ist-Wert eingebaut, damit knapper Bestand sofort auffällt.</t>
         </is>
       </c>
       <c r="I41" s="86" t="n"/>
@@ -5196,7 +5200,7 @@
       </c>
       <c r="H59" s="94" t="inlineStr">
         <is>
-          <t>Automatische Färbung des Bestands nach Soll- und Ist-Wert eingebaut, damit knapper Bestand sofort auffällt.</t>
+          <t>Eigene Eingabemaske für das Anlegen neuer Artikel als UserForm erstellt und mit der Artikelliste verbunden.</t>
         </is>
       </c>
       <c r="I59" s="86" t="n"/>
@@ -5237,7 +5241,7 @@
       </c>
       <c r="H60" s="94" t="inlineStr">
         <is>
-          <t>Eigene Eingabemaske für das Anlegen neuer Artikel als UserForm erstellt und mit der Artikelliste verbunden.</t>
+          <t>Weitere Eingabemasken für Bearbeiten und Löschen ergänzt und eine Sicherheitsabfrage vor dem Löschen eingebaut.</t>
         </is>
       </c>
       <c r="I60" s="86" t="n"/>
@@ -5264,7 +5268,7 @@
         </is>
       </c>
       <c r="E61" s="119" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -5278,7 +5282,7 @@
       </c>
       <c r="H61" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP bis 11:30, danach kurze Schicht im Betrieb. Weitere Eingabemasken für Bearbeiten und Löschen ergänzt und eine Sicherheitsabfrage vor dem Löschen eingebaut.</t>
+          <t>Vorlesung PP bis 11:30, danach im Betrieb. Filterfunktion über Bezeichnung, Profil, Maß und Materialgruppe umgesetzt und getestet.</t>
         </is>
       </c>
       <c r="I61" s="86" t="n"/>
@@ -5319,7 +5323,7 @@
       </c>
       <c r="H62" s="94" t="inlineStr">
         <is>
-          <t>Filterfunktion über Bezeichnung, Profil, Maß und Materialgruppe umgesetzt und getestet.</t>
+          <t>Export auf Knopfdruck umgesetzt: ausgewählte Blätter als Excel- oder PDF-Datei in einen festen Zielordner speichern.</t>
         </is>
       </c>
       <c r="I62" s="86" t="n"/>
@@ -5500,7 +5504,7 @@
       </c>
       <c r="H67" s="94" t="inlineStr">
         <is>
-          <t>Export auf Knopfdruck umgesetzt: ausgewählte Blätter als Excel- oder PDF-Datei in einen festen Zielordner speichern.</t>
+          <t>Versand der Bestandsliste per E-Mail ergänzt und mit Testdaten geprüft.</t>
         </is>
       </c>
       <c r="I67" s="86" t="n"/>
@@ -5527,7 +5531,7 @@
         </is>
       </c>
       <c r="E68" s="119" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -5541,7 +5545,7 @@
       </c>
       <c r="H68" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP bis 11:30, danach kurze Schicht im Betrieb. Versand der Bestandsliste per E-Mail ergänzt und mit Testdaten geprüft.</t>
+          <t>Vorlesung PP bis 11:30, danach im Betrieb. Einstellungsblatt angelegt, damit Zielordner, Empfängeradresse und Schwellenwerte ohne Eingriff in den Code änderbar sind.</t>
         </is>
       </c>
       <c r="I68" s="86" t="n"/>
@@ -5582,7 +5586,7 @@
       </c>
       <c r="H69" s="94" t="inlineStr">
         <is>
-          <t>Einstellungsblatt angelegt, damit Zielordner, Empfängeradresse und Schwellenwerte ohne Eingriff in den Code änderbar sind.</t>
+          <t>Tablet-Modus entwickelt: Vollbild-Oberfläche ohne Excel-Bedienelemente, damit das System direkt in der Werkstatt bedienbar ist.</t>
         </is>
       </c>
       <c r="I69" s="86" t="n"/>
@@ -5623,7 +5627,7 @@
       </c>
       <c r="H70" s="67" t="inlineStr">
         <is>
-          <t>Tablet-Modus entwickelt: Vollbild-Oberfläche ohne Excel-Bedienelemente, damit das System direkt in der Werkstatt bedienbar ist.</t>
+          <t>Entwicklermodus ergänzt, der die Excel-Oberfläche für Wartungsarbeiten wieder einblendet, und mit einem Kennwort geschützt.</t>
         </is>
       </c>
       <c r="I70" s="86" t="n"/>
@@ -5726,7 +5730,7 @@
       </c>
       <c r="H73" s="94" t="inlineStr">
         <is>
-          <t>Entwicklermodus ergänzt, der die Excel-Oberfläche für Wartungsarbeiten wieder einblendet, und mit einem Kennwort geschützt.</t>
+          <t>Makros in Modulgruppen aufgeteilt und benannt, damit die Datei wartbar bleibt und Funktionen wiederverwendet werden können.</t>
         </is>
       </c>
       <c r="I73" s="86" t="n"/>
@@ -5767,7 +5771,7 @@
       </c>
       <c r="H74" s="94" t="inlineStr">
         <is>
-          <t>Makros in Modulgruppen aufgeteilt und benannt, damit die Datei wartbar bleibt und Funktionen wiederverwendet werden können.</t>
+          <t>Material-Entnahme-Logik entworfen: Beim Zuschnitt soll die Restlänge selbstständig eingebucht werden.</t>
         </is>
       </c>
       <c r="I74" s="86" t="n"/>
@@ -5790,10 +5794,12 @@
       </c>
       <c r="D75" s="65" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="E75" s="119" t="n"/>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="E75" s="119" t="n">
+        <v>4</v>
+      </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -5806,7 +5812,7 @@
       </c>
       <c r="H75" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00-11:30 an der OTH, keine Anwesenheit im Betrieb</t>
+          <t>Vorlesung PP bis 11:30, danach im Betrieb. Material-Entnahme umgesetzt: Restlängen werden automatisch angelegt oder mit vorhandenen gleich langen Resten zusammengefasst.</t>
         </is>
       </c>
       <c r="I75" s="86" t="n"/>
@@ -5847,7 +5853,7 @@
       </c>
       <c r="H76" s="94" t="inlineStr">
         <is>
-          <t>Material-Entnahme-Logik entworfen: Beim Zuschnitt soll die Restlänge selbstständig eingebucht werden.</t>
+          <t>Material-Entnahme mit realen Zuschnitten aus der Werkstatt getestet und zwei Fehler bei der Restberechnung behoben.</t>
         </is>
       </c>
       <c r="I76" s="86" t="n"/>
@@ -5888,7 +5894,7 @@
       </c>
       <c r="H77" s="67" t="inlineStr">
         <is>
-          <t>Material-Entnahme umgesetzt: Restlängen werden automatisch angelegt oder mit vorhandenen gleich langen Resten zusammengefasst.</t>
+          <t>System einem Mitarbeiter gezeigt, Rückmeldungen aufgenommen und die Bedienung an zwei Stellen vereinfacht.</t>
         </is>
       </c>
       <c r="I77" s="86" t="n"/>
@@ -5991,7 +5997,7 @@
       </c>
       <c r="H80" s="67" t="inlineStr">
         <is>
-          <t>Material-Entnahme mit realen Zuschnitten aus der Werkstatt getestet und zwei Fehler bei der Restberechnung behoben.</t>
+          <t>Kurzanleitung für die Bedienung des Lagerbestand-Systems geschrieben und an den Arbeitsplatz gelegt.</t>
         </is>
       </c>
       <c r="I80" s="86" t="n"/>
@@ -6032,7 +6038,7 @@
       </c>
       <c r="H81" s="67" t="inlineStr">
         <is>
-          <t>System einem Mitarbeiter gezeigt, Rückmeldungen aufgenommen und die Bedienung an zwei Stellen vereinfacht.</t>
+          <t>Schwachstellen des Excel-Systems zusammengetragen (Bindung an einen Rechner, kein Mehrbenutzerbetrieb) und die Neuentwicklung als eigenständige Web-Anwendung mit dem Betreuer besprochen. Architektur in drei Schichten festgelegt und mit KI-Unterstützung aufgesetzt.</t>
         </is>
       </c>
       <c r="I81" s="86" t="n"/>
@@ -6055,10 +6061,12 @@
       </c>
       <c r="D82" s="65" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="E82" s="119" t="n"/>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="E82" s="119" t="n">
+        <v>4</v>
+      </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -6071,7 +6079,7 @@
       </c>
       <c r="H82" s="67" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00-11:30 an der OTH, keine Anwesenheit im Betrieb</t>
+          <t>Vorlesung PP bis 11:30, danach im Betrieb. Datenmodell aus den Excel-Blättern übernommen und die Kernfunktionen portiert: Artikel verwalten, Buchungen, Verlauf und die Material-Entnahme mit Resteverwaltung. 86 reale Artikel-Datensätze und 50 Artikelgruppen übernommen und die Übernahme kontrolliert.</t>
         </is>
       </c>
       <c r="I82" s="86" t="n"/>
@@ -6112,7 +6120,7 @@
       </c>
       <c r="H83" s="67" t="inlineStr">
         <is>
-          <t>Schwachstellen des Excel-Systems zusammengetragen (Bindung an einen Rechner, kein Mehrbenutzerbetrieb) und die Neuentwicklung als eigenständige Web-Anwendung mit dem Betreuer besprochen. Architektur in drei Schichten festgelegt und mit KI-Unterstützung aufgesetzt.</t>
+          <t>Anwendung als Hintergrunddienst mit täglichem Backup eingerichtet und zusätzlich in der Cloud bereitgestellt. Lasttest mit 100 gleichzeitigen Schreibzugriffen durchgeführt und die Bedienung dokumentiert.</t>
         </is>
       </c>
       <c r="I83" s="86" t="n"/>
@@ -6153,7 +6161,7 @@
       </c>
       <c r="H84" s="67" t="inlineStr">
         <is>
-          <t>Datenmodell aus den Excel-Blättern übernommen und die Kernfunktionen portiert: Artikel verwalten, Buchungen, Verlauf und die Material-Entnahme mit Resteverwaltung. 86 reale Artikel-Datensätze und 50 Artikelgruppen übernommen und die Übernahme kontrolliert.</t>
+          <t>Aufgabenstellung zum Schweißarbeitsplatz erhalten. Bestehenden Platz besichtigt, fotografiert und die verfügbare Fläche aufgemessen (rund 29 m²).</t>
         </is>
       </c>
       <c r="I84" s="86" t="n"/>
@@ -6570,7 +6578,7 @@
       </c>
       <c r="H102" s="61" t="inlineStr">
         <is>
-          <t>Anwendung als Hintergrunddienst mit täglichem Backup eingerichtet und zusätzlich in der Cloud bereitgestellt. Lasttest mit 100 gleichzeitigen Schreibzugriffen durchgeführt und die Bedienung dokumentiert.</t>
+          <t>Verwendete Schweißverfahren mit dem Betreuer besprochen (MAG/MIG und E-Hand) und die Unterschiede für die spätere Ausstattung festgehalten.</t>
         </is>
       </c>
       <c r="I102" s="86" t="n"/>
@@ -6611,7 +6619,7 @@
       </c>
       <c r="H103" s="67" t="inlineStr">
         <is>
-          <t>Aufgabenstellung zum Schweißarbeitsplatz erhalten. Bestehenden Platz besichtigt, fotografiert und die verfügbare Fläche aufgemessen (rund 29 m²).</t>
+          <t>Aufnahme der vorhandenen Werkzeuge am Schweißplatz begonnen und nach Verwendungszweck gruppiert.</t>
         </is>
       </c>
       <c r="I103" s="86" t="n"/>
@@ -6691,7 +6699,7 @@
       </c>
       <c r="H105" s="67" t="inlineStr">
         <is>
-          <t>Verwendete Schweißverfahren mit dem Betreuer besprochen (MAG/MIG und E-Hand) und die Unterschiede für die spätere Ausstattung festgehalten.</t>
+          <t>Werkzeugaufnahme fortgesetzt: Kategorien Schweißen MAG/MIG und Schweißen E-Hand vollständig erfasst.</t>
         </is>
       </c>
       <c r="I105" s="86" t="n"/>
@@ -6833,7 +6841,7 @@
       </c>
       <c r="H109" s="94" t="inlineStr">
         <is>
-          <t>Aufnahme der vorhandenen Werkzeuge am Schweißplatz begonnen und nach Verwendungszweck gruppiert.</t>
+          <t>Kategorien Spannen und Fixieren sowie Nachbearbeitung erfasst und mit den Mitarbeitern auf Vollständigkeit geprüft.</t>
         </is>
       </c>
       <c r="I109" s="86" t="n"/>
@@ -6874,7 +6882,7 @@
       </c>
       <c r="H110" s="94" t="inlineStr">
         <is>
-          <t>Werkzeugaufnahme fortgesetzt: Kategorien Schweißen MAG/MIG und Schweißen E-Hand vollständig erfasst.</t>
+          <t>Kategorien Anreißen und Messen sowie persönliche Schutzausrüstung für drei Personen zusammengestellt.</t>
         </is>
       </c>
       <c r="I110" s="86" t="n"/>
@@ -6897,10 +6905,12 @@
       </c>
       <c r="D111" s="65" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="E111" s="119" t="n"/>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="E111" s="119" t="n">
+        <v>4</v>
+      </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -6913,7 +6923,7 @@
       </c>
       <c r="H111" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00-11:30 an der OTH, keine Anwesenheit im Betrieb</t>
+          <t>Vorlesung PP bis 11:30, danach im Betrieb. Kategorien Sicherheit und Umgebung, Verbrauchsmaterial sowie 5S-Möbel ergänzt. Damit sind alle neun Werkzeugkategorien A bis I erfasst.</t>
         </is>
       </c>
       <c r="I111" s="86" t="n"/>
@@ -6954,7 +6964,7 @@
       </c>
       <c r="H112" s="94" t="inlineStr">
         <is>
-          <t>Kategorien Spannen und Fixieren sowie Nachbearbeitung erfasst und mit den Mitarbeitern auf Vollständigkeit geprüft.</t>
+          <t>Marktrecherche zu den Werkzeugen begonnen und Richtpreise je Position gesammelt.</t>
         </is>
       </c>
       <c r="I112" s="86" t="n"/>
@@ -6995,7 +7005,7 @@
       </c>
       <c r="H113" s="67" t="inlineStr">
         <is>
-          <t>Kategorien Anreißen und Messen sowie persönliche Schutzausrüstung für drei Personen zusammengestellt.</t>
+          <t>Marktrecherche abgeschlossen und je Kaufteil drei Preisstufen gegenübergestellt.</t>
         </is>
       </c>
       <c r="I113" s="86" t="n"/>
@@ -7098,7 +7108,7 @@
       </c>
       <c r="H116" s="94" t="inlineStr">
         <is>
-          <t>Kategorien Sicherheit und Umgebung, Verbrauchsmaterial sowie 5S-Möbel ergänzt. Damit sind alle neun Werkzeugkategorien A bis I erfasst.</t>
+          <t>Ergonomische Grundmaße für den Arbeitsplatz zusammengetragen (Arbeitshöhe, Greifräume, Beleuchtung) und mit den Normvorgaben abgeglichen.</t>
         </is>
       </c>
       <c r="I116" s="86" t="n"/>
@@ -7139,7 +7149,7 @@
       </c>
       <c r="H117" s="94" t="inlineStr">
         <is>
-          <t>Marktrecherche zu den Werkzeugen begonnen und Richtpreise je Position gesammelt.</t>
+          <t>Erstes Layout-Konzept für den Platz gezeichnet und die Wege zwischen Tisch, Maschine und Materialablage geprüft.</t>
         </is>
       </c>
       <c r="I117" s="86" t="n"/>
@@ -7166,7 +7176,7 @@
         </is>
       </c>
       <c r="E118" s="119" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -7180,7 +7190,7 @@
       </c>
       <c r="H118" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP bis 11:30, danach kurze Schicht im Betrieb. Marktrecherche abgeschlossen und je Kaufteil drei Preisstufen gegenübergestellt.</t>
+          <t>Vorlesung PP bis 11:30, danach im Betrieb. Zwei weitere Layout-Varianten entwickelt und die drei Konzepte nebeneinandergestellt.</t>
         </is>
       </c>
       <c r="I118" s="86" t="n"/>
@@ -7260,7 +7270,7 @@
       </c>
       <c r="H120" s="94" t="inlineStr">
         <is>
-          <t>Ergonomische Grundmaße für den Arbeitsplatz zusammengetragen (Arbeitshöhe, Greifräume, Beleuchtung) und mit den Normvorgaben abgeglichen.</t>
+          <t>Nutzwertanalyse für die Werkbank-Ausführung aufgestellt: Kriterien festgelegt und gewichtet.</t>
         </is>
       </c>
       <c r="I120" s="86" t="n"/>
@@ -7363,7 +7373,7 @@
       </c>
       <c r="H123" s="94" t="inlineStr">
         <is>
-          <t>Erstes Layout-Konzept für den Platz gezeichnet und die Wege zwischen Tisch, Maschine und Materialablage geprüft.</t>
+          <t>Nutzwertanalyse für das Layout-Konzept gerechnet und die Ergebnisse ausgewertet.</t>
         </is>
       </c>
       <c r="I123" s="86" t="n"/>
@@ -7404,7 +7414,7 @@
       </c>
       <c r="H124" s="67" t="inlineStr">
         <is>
-          <t>Zwei weitere Layout-Varianten entwickelt und die drei Konzepte nebeneinandergestellt.</t>
+          <t>Aufgabenstellung zum neuen Schweißtisch erhalten. Anforderungen mit dem Betreuer gesammelt: Größe, Spannmöglichkeiten, Fahrbarkeit.</t>
         </is>
       </c>
       <c r="I124" s="86" t="n"/>
@@ -7484,7 +7494,7 @@
       </c>
       <c r="H126" s="67" t="inlineStr">
         <is>
-          <t>Nutzwertanalyse für die Werkbank-Ausführung aufgestellt: Kriterien festgelegt und gewichtet.</t>
+          <t>Vorhandenen Tisch vermessen und die Schwachstellen im Betrieb aufgenommen.</t>
         </is>
       </c>
       <c r="I126" s="86" t="n"/>
@@ -7525,7 +7535,7 @@
       </c>
       <c r="H127" s="67" t="inlineStr">
         <is>
-          <t>Aufgabenstellung zum neuen Schweißtisch erhalten. Anforderungen mit dem Betreuer gesammelt: Größe, Spannmöglichkeiten, Fahrbarkeit.</t>
+          <t>Recherche zu Schweißtisch-Konzepten und Spannsystemen durchgeführt, Beispiele gesammelt und bewertet.</t>
         </is>
       </c>
       <c r="I127" s="86" t="n"/>
@@ -7981,7 +7991,7 @@
       </c>
       <c r="H146" s="94" t="inlineStr">
         <is>
-          <t>Vorhandenen Tisch vermessen und die Schwachstellen im Betrieb aufgenommen.</t>
+          <t>Erste Handskizzen für den neuen Tisch angefertigt und mit dem Betreuer besprochen.</t>
         </is>
       </c>
       <c r="I146" s="86" t="n"/>
@@ -8061,7 +8071,7 @@
       </c>
       <c r="H148" s="94" t="inlineStr">
         <is>
-          <t>Recherche zu Schweißtisch-Konzepten und Spannsystemen durchgeführt, Beispiele gesammelt und bewertet.</t>
+          <t>Grundkonzept festgelegt: ausziehbarer Tisch mit Lochplatten-Spannsystem auf fahrbarem Untergestell.</t>
         </is>
       </c>
       <c r="I148" s="86" t="n"/>
@@ -8102,7 +8112,7 @@
       </c>
       <c r="H149" s="94" t="inlineStr">
         <is>
-          <t>Erste Handskizzen für den neuen Tisch angefertigt und mit dem Betreuer besprochen.</t>
+          <t>Marktrecherche zu Lochplatten durchgeführt, Angebote verglichen und das D16-Raster ausgewählt.</t>
         </is>
       </c>
       <c r="I149" s="86" t="n"/>
@@ -8205,7 +8215,7 @@
       </c>
       <c r="H152" s="94" t="inlineStr">
         <is>
-          <t>Grundkonzept festgelegt: ausziehbarer Tisch mit Lochplatten-Spannsystem auf fahrbarem Untergestell.</t>
+          <t>Mit der CAD-Konstruktion begonnen: Tischplatte mit Lochraster aufgebaut.</t>
         </is>
       </c>
       <c r="I152" s="86" t="n"/>
@@ -8246,7 +8256,7 @@
       </c>
       <c r="H153" s="67" t="inlineStr">
         <is>
-          <t>Marktrecherche zu Lochplatten durchgeführt, Angebote verglichen und das D16-Raster ausgewählt.</t>
+          <t>Oberteil konstruiert: Träger und Profile modelliert und die Teilenummern vergeben.</t>
         </is>
       </c>
       <c r="I153" s="86" t="n"/>
@@ -8273,7 +8283,7 @@
         </is>
       </c>
       <c r="E154" s="119" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
@@ -8287,7 +8297,7 @@
       </c>
       <c r="H154" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP bis 11:30, danach kurze Schicht im Betrieb. Mit der CAD-Konstruktion begonnen: Tischplatte mit Lochraster aufgebaut.</t>
+          <t>Vorlesung PP bis 11:30, danach im Betrieb. Unterteil konstruiert: Beine, Streben und Fußplatten aufgebaut.</t>
         </is>
       </c>
       <c r="I154" s="86" t="n"/>
@@ -8367,7 +8377,7 @@
       </c>
       <c r="H156" s="67" t="inlineStr">
         <is>
-          <t>Oberteil konstruiert: Träger und Profile modelliert und die Teilenummern vergeben.</t>
+          <t>Erweiterungssystem als Teleskop-Rahmen konstruiert, beidseitig ausziehbar.</t>
         </is>
       </c>
       <c r="I156" s="86" t="n"/>
@@ -8470,7 +8480,7 @@
       </c>
       <c r="H159" s="94" t="inlineStr">
         <is>
-          <t>Unterteil konstruiert: Beine, Streben und Fußplatten aufgebaut.</t>
+          <t>Baugruppen zum Gesamtzusammenbau zusammengeführt und die Struktur geordnet.</t>
         </is>
       </c>
       <c r="I159" s="86" t="n"/>
@@ -8511,7 +8521,7 @@
       </c>
       <c r="H160" s="94" t="inlineStr">
         <is>
-          <t>Erweiterungssystem als Teleskop-Rahmen konstruiert, beidseitig ausziehbar.</t>
+          <t>Kollisionen und Verfahrwege im Modell geprüft und die Führungen angepasst.</t>
         </is>
       </c>
       <c r="I160" s="86" t="n"/>
@@ -8534,10 +8544,12 @@
       </c>
       <c r="D161" s="65" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="E161" s="119" t="n"/>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="E161" s="119" t="n">
+        <v>4</v>
+      </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -8550,7 +8562,7 @@
       </c>
       <c r="H161" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00-11:30 an der OTH, keine Anwesenheit im Betrieb</t>
+          <t>Vorlesung PP bis 11:30, danach im Betrieb. Erste Zeichnungsblätter abgeleitet und bemaßt.</t>
         </is>
       </c>
       <c r="I161" s="86" t="n"/>
@@ -8591,7 +8603,7 @@
       </c>
       <c r="H162" s="94" t="inlineStr">
         <is>
-          <t>Baugruppen zum Gesamtzusammenbau zusammengeführt und die Struktur geordnet.</t>
+          <t>Weitere Einzelteilzeichnungen erstellt und die Schriftfelder ausgefüllt.</t>
         </is>
       </c>
       <c r="I162" s="86" t="n"/>
@@ -8632,7 +8644,7 @@
       </c>
       <c r="H163" s="94" t="inlineStr">
         <is>
-          <t>Kollisionen und Verfahrwege im Modell geprüft und die Führungen angepasst.</t>
+          <t>Aufgabenstellung zum Schweißmaschinenwagen erhalten. Vorhandenen Wagen im Betrieb fotografiert und den Zustand aufgenommen.</t>
         </is>
       </c>
       <c r="I163" s="86" t="n"/>
@@ -8735,7 +8747,7 @@
       </c>
       <c r="H166" s="94" t="inlineStr">
         <is>
-          <t>Erste Zeichnungsblätter abgeleitet und bemaßt.</t>
+          <t>Schweißgerät und Gasflasche vor Ort aufgemessen und die Maße in einer Handskizze festgehalten.</t>
         </is>
       </c>
       <c r="I166" s="86" t="n"/>
@@ -8776,7 +8788,7 @@
       </c>
       <c r="H167" s="94" t="inlineStr">
         <is>
-          <t>Aufgabenstellung zum Schweißmaschinenwagen erhalten. Vorhandenen Wagen im Betrieb fotografiert und den Zustand aufgenommen.</t>
+          <t>Vereinfachte CAD-Platzhalter für Gerät und Flasche erstellt, um den Bauraum abzubilden.</t>
         </is>
       </c>
       <c r="I167" s="86" t="n"/>
@@ -8799,10 +8811,12 @@
       </c>
       <c r="D168" s="65" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="E168" s="119" t="n"/>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="E168" s="119" t="n">
+        <v>4</v>
+      </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -8815,7 +8829,7 @@
       </c>
       <c r="H168" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00-11:30 an der OTH, keine Anwesenheit im Betrieb</t>
+          <t>Vorlesung PP bis 11:30, danach im Betrieb. Anforderungsliste aufgestellt: was der Wagen tragen und was er können muss.</t>
         </is>
       </c>
       <c r="I168" s="86" t="n"/>
@@ -8856,7 +8870,7 @@
       </c>
       <c r="H169" s="67" t="inlineStr">
         <is>
-          <t>Schweißgerät und Gasflasche vor Ort aufgemessen und die Maße in einer Handskizze festgehalten.</t>
+          <t>Anforderungsliste auf 14 nummerierte Punkte gebracht und mit dem Betreuer abgestimmt.</t>
         </is>
       </c>
       <c r="I169" s="86" t="n"/>
@@ -8897,7 +8911,7 @@
       </c>
       <c r="H170" s="94" t="inlineStr">
         <is>
-          <t>Vereinfachte CAD-Platzhalter für Gerät und Flasche erstellt, um den Bauraum abzubilden.</t>
+          <t>Referenzprojekte recherchiert und fünf Designrichtungen für den Wagen gesammelt.</t>
         </is>
       </c>
       <c r="I170" s="86" t="n"/>
@@ -9314,7 +9328,7 @@
       </c>
       <c r="H188" s="94" t="inlineStr">
         <is>
-          <t>Anforderungsliste aufgestellt: was der Wagen tragen und was er können muss.</t>
+          <t>Zwei erste Entwürfe im CAD aufgebaut und gegenübergestellt.</t>
         </is>
       </c>
       <c r="I188" s="86" t="n"/>
@@ -9355,7 +9369,7 @@
       </c>
       <c r="H189" s="94" t="inlineStr">
         <is>
-          <t>Anforderungsliste auf 14 nummerierte Punkte gebracht und mit dem Betreuer abgestimmt.</t>
+          <t>Maße und Ergonomie festgelegt, Gewicht des beladenen Wagens grob abgeschätzt.</t>
         </is>
       </c>
       <c r="I189" s="86" t="n"/>
@@ -9378,10 +9392,12 @@
       </c>
       <c r="D190" s="65" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="E190" s="119" t="n"/>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="E190" s="119" t="n">
+        <v>4</v>
+      </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -9394,7 +9410,7 @@
       </c>
       <c r="H190" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00-11:30 an der OTH, keine Anwesenheit im Betrieb</t>
+          <t>Vorlesung PP bis 11:30, danach im Betrieb. Kompletten Neubau als Variante A konstruiert und einen Belegungsplan mit 16 Werkzeugpositionen erstellt.</t>
         </is>
       </c>
       <c r="I190" s="86" t="n"/>
@@ -9435,7 +9451,7 @@
       </c>
       <c r="H191" s="94" t="inlineStr">
         <is>
-          <t>Referenzprojekte recherchiert und fünf Designrichtungen für den Wagen gesammelt.</t>
+          <t>Beim Maßabgleich festgestellt, dass das geplante Gerätefach zu niedrig für die vorhandene Maschine ist.</t>
         </is>
       </c>
       <c r="I191" s="86" t="n"/>
@@ -9476,7 +9492,7 @@
       </c>
       <c r="H192" s="94" t="inlineStr">
         <is>
-          <t>Zwei erste Entwürfe im CAD aufgebaut und gegenübergestellt.</t>
+          <t>Als Variante B ein Aufsatzgestell entworfen, das über den vorhandenen Wagen fährt.</t>
         </is>
       </c>
       <c r="I192" s="86" t="n"/>
@@ -9579,7 +9595,7 @@
       </c>
       <c r="H195" s="94" t="inlineStr">
         <is>
-          <t>Maße und Ergonomie festgelegt, Gewicht des beladenen Wagens grob abgeschätzt.</t>
+          <t>Variante B überarbeitet, sodass die Gasflasche innerhalb der Aufstandsfläche steht.</t>
         </is>
       </c>
       <c r="I195" s="86" t="n"/>
@@ -9620,7 +9636,7 @@
       </c>
       <c r="H196" s="94" t="inlineStr">
         <is>
-          <t>Kompletten Neubau als Variante A konstruiert und einen Belegungsplan mit 16 Werkzeugpositionen erstellt.</t>
+          <t>Aufgabenstellung zum Zerspanarbeitsplatz erhalten und die Rahmenbedingungen aufgenommen (Drehen und Fräsen, drei Personen, eine Schicht).</t>
         </is>
       </c>
       <c r="I196" s="86" t="n"/>
@@ -9661,7 +9677,7 @@
       </c>
       <c r="H197" s="94" t="inlineStr">
         <is>
-          <t>Beim Maßabgleich festgestellt, dass das geplante Gerätefach zu niedrig für die vorhandene Maschine ist.</t>
+          <t>Bestehenden Platz besichtigt, Maschinen und vorhandene Ausstattung fotografiert.</t>
         </is>
       </c>
       <c r="I197" s="86" t="n"/>
@@ -9702,7 +9718,7 @@
       </c>
       <c r="H198" s="94" t="inlineStr">
         <is>
-          <t>Als Variante B ein Aufsatzgestell entworfen, das über den vorhandenen Wagen fährt.</t>
+          <t>Werkzeugbedarf für das Drehen zusammengestellt.</t>
         </is>
       </c>
       <c r="I198" s="86" t="n"/>
@@ -9844,7 +9860,7 @@
       </c>
       <c r="H202" s="94" t="inlineStr">
         <is>
-          <t>Aufgabenstellung zum Zerspanarbeitsplatz erhalten und die Rahmenbedingungen aufgenommen (Drehen und Fräsen, drei Personen, eine Schicht).</t>
+          <t>Werkzeugbedarf für das Fräsen sowie die Spann- und Aufspannmittel erfasst.</t>
         </is>
       </c>
       <c r="I202" s="86" t="n"/>
@@ -9885,7 +9901,7 @@
       </c>
       <c r="H203" s="94" t="inlineStr">
         <is>
-          <t>Bestehenden Platz besichtigt, Maschinen und vorhandene Ausstattung fotografiert.</t>
+          <t>Mess- und Prüfmittel sowie Nacharbeit und Hilfsmittel ergänzt. Damit sind alle sechs Gruppen erfasst.</t>
         </is>
       </c>
       <c r="I203" s="86" t="n"/>
@@ -9926,7 +9942,7 @@
       </c>
       <c r="H204" s="67" t="inlineStr">
         <is>
-          <t>Werkzeugbedarf für das Drehen zusammengestellt.</t>
+          <t>Mengen je Position festgelegt und begründet, welche Werkzeuge dreifach beschafft werden müssen.</t>
         </is>
       </c>
       <c r="I204" s="86" t="n"/>
@@ -9967,7 +9983,7 @@
       </c>
       <c r="H205" s="99" t="inlineStr">
         <is>
-          <t>Prüfung PRM an der OTH bis 10:00. Werkzeugbedarf für das Fräsen sowie die Spann- und Aufspannmittel erfasst.</t>
+          <t>Prüfung PRM an der OTH bis 10:00. Preise recherchiert und die Werkzeugliste mit 35 Positionen bepreist.</t>
         </is>
       </c>
       <c r="I205" s="86" t="n"/>
@@ -10008,7 +10024,7 @@
       </c>
       <c r="H206" s="67" t="inlineStr">
         <is>
-          <t>Mess- und Prüfmittel sowie Nacharbeit und Hilfsmittel ergänzt. Damit sind alle sechs Gruppen erfasst.</t>
+          <t>Kosten nach Kategorien ausgewertet und die teuersten Positionen herausgearbeitet.</t>
         </is>
       </c>
       <c r="I206" s="86" t="n"/>
@@ -10111,7 +10127,7 @@
       </c>
       <c r="H209" s="67" t="inlineStr">
         <is>
-          <t>Mengen je Position festgelegt und begründet, welche Werkzeuge dreifach beschafft werden müssen.</t>
+          <t>5S-Ordnung ausgearbeitet und die Werkzeuge den Zonen A, B und C zugeordnet.</t>
         </is>
       </c>
       <c r="I209" s="86" t="n"/>
@@ -10152,7 +10168,7 @@
       </c>
       <c r="H210" s="67" t="inlineStr">
         <is>
-          <t>Preise recherchiert und die Werkzeugliste mit 35 Positionen bepreist.</t>
+          <t>Grundmaße der Werkbank festgelegt und mit den Ergonomienormen abgeglichen.</t>
         </is>
       </c>
       <c r="I210" s="86" t="n"/>
@@ -10193,7 +10209,7 @@
       </c>
       <c r="H211" s="67" t="inlineStr">
         <is>
-          <t>Kosten nach Kategorien ausgewertet und die teuersten Positionen herausgearbeitet.</t>
+          <t>Vier Bauvarianten skizziert und in 3D dargestellt: Aluprofil, Stahl-Standard, Systemmodule und Eigenbau.</t>
         </is>
       </c>
       <c r="I211" s="86" t="n"/>
@@ -10234,7 +10250,7 @@
       </c>
       <c r="H212" s="67" t="inlineStr">
         <is>
-          <t>5S-Ordnung ausgearbeitet und die Werkzeuge den Zonen A, B und C zugeordnet.</t>
+          <t>Vier Layout-Konzepte entwickelt und die Vor- und Nachteile gegenübergestellt.</t>
         </is>
       </c>
       <c r="I212" s="86" t="n"/>
@@ -10275,7 +10291,7 @@
       </c>
       <c r="H213" s="67" t="inlineStr">
         <is>
-          <t>Prüfung DA an der OTH bis 10:00. Grundmaße der Werkbank festgelegt und mit den Ergonomienormen abgeglichen.</t>
+          <t>Prüfung DA an der OTH bis 10:00. Werkstatt-Grundriss maßstäblich gezeichnet und die Freiräume an den Maschinen geprüft.</t>
         </is>
       </c>
       <c r="I213" s="86" t="n"/>
@@ -10692,7 +10708,7 @@
       </c>
       <c r="H231" s="61" t="inlineStr">
         <is>
-          <t>Prüfung GAT an der OTH bis 10:00. Vier Bauvarianten skizziert und in 3D dargestellt: Aluprofil, Stahl-Standard, Systemmodule und Eigenbau.</t>
+          <t>Prüfung GAT an der OTH bis 10:00. Nutzwertanalyse aufgestellt: sieben Kriterien festgelegt und gewichtet.</t>
         </is>
       </c>
       <c r="I231" s="86" t="n"/>
@@ -10733,7 +10749,7 @@
       </c>
       <c r="H232" s="67" t="inlineStr">
         <is>
-          <t>Vier Layout-Konzepte entwickelt und die Vor- und Nachteile gegenübergestellt.</t>
+          <t>Aufgabenstellung zum Rostschutz für die Schienenprofile erhalten. Lagerbedingungen der Profile im Betrieb aufgenommen und fotografiert.</t>
         </is>
       </c>
       <c r="I232" s="86" t="n"/>
@@ -10774,7 +10790,7 @@
       </c>
       <c r="H233" s="67" t="inlineStr">
         <is>
-          <t>Aufgabenstellung zum Rostschutz für die Schienenprofile erhalten. Lagerbedingungen der Profile im Betrieb aufgenommen und fotografiert.</t>
+          <t>Bestehende Rostschäden begutachtet und die Ursachen mit den Mitarbeitern besprochen (Feuchtigkeit, Kondenswasser, Lagerdauer).</t>
         </is>
       </c>
       <c r="I233" s="86" t="n"/>
@@ -10815,7 +10831,7 @@
       </c>
       <c r="H234" s="67" t="inlineStr">
         <is>
-          <t>Bestehende Rostschäden begutachtet und die Ursachen mit den Mitarbeitern besprochen (Feuchtigkeit, Kondenswasser, Lagerdauer).</t>
+          <t>Recherche zu Korrosionsschutzverfahren durchgeführt: Ölen, Wachsen, VCI-Folie und trockene Lagerung verglichen.</t>
         </is>
       </c>
       <c r="I234" s="86" t="n"/>
@@ -10856,7 +10872,7 @@
       </c>
       <c r="H235" s="67" t="inlineStr">
         <is>
-          <t>Recherche zu Korrosionsschutzverfahren durchgeführt: Ölen, Wachsen, VCI-Folie und trockene Lagerung verglichen.</t>
+          <t>Verfahren gegenübergestellt und nach Wirksamkeit, Aufwand und Kosten bewertet.</t>
         </is>
       </c>
       <c r="I235" s="86" t="n"/>
@@ -10959,7 +10975,7 @@
       </c>
       <c r="H238" s="67" t="inlineStr">
         <is>
-          <t>Verfahren gegenübergestellt und nach Wirksamkeit, Aufwand und Kosten bewertet.</t>
+          <t>Konzept für eine geschlossene Lagerbox mit VCI-Schutz entworfen und die benötigten Maße aufgenommen.</t>
         </is>
       </c>
       <c r="I238" s="86" t="n"/>
@@ -11000,7 +11016,7 @@
       </c>
       <c r="H239" s="67" t="inlineStr">
         <is>
-          <t>Prüfung SWV an der OTH bis 10:00. Konzept für eine geschlossene Lagerbox mit VCI-Schutz entworfen und die benötigten Maße aufgenommen.</t>
+          <t>Prüfung SWV an der OTH bis 10:00. Lagerbox im CAD konstruiert und die Aufteilung für die verschiedenen Profillängen festgelegt.</t>
         </is>
       </c>
       <c r="I239" s="86" t="n"/>
@@ -11041,7 +11057,7 @@
       </c>
       <c r="H240" s="67" t="inlineStr">
         <is>
-          <t>Lagerbox im CAD konstruiert und die Aufteilung für die verschiedenen Profillängen festgelegt.</t>
+          <t>Material- und Kostenaufstellung für die Schutzbox erstellt.</t>
         </is>
       </c>
       <c r="I240" s="86" t="n"/>
@@ -11082,7 +11098,7 @@
       </c>
       <c r="H241" s="67" t="inlineStr">
         <is>
-          <t>Material- und Kostenaufstellung für die Schutzbox erstellt.</t>
+          <t>Zeitersparnis durch den Wegfall des Nacharbeitens abgeschätzt und der Investition gegenübergestellt.</t>
         </is>
       </c>
       <c r="I241" s="86" t="n"/>
@@ -11123,7 +11139,7 @@
       </c>
       <c r="H242" s="67" t="inlineStr">
         <is>
-          <t>Zeitersparnis durch den Wegfall des Nacharbeitens abgeschätzt und der Investition gegenübergestellt.</t>
+          <t>Arbeitsanweisung für die Einlagerung und Entnahme der Schienenprofile entworfen.</t>
         </is>
       </c>
       <c r="I242" s="86" t="n"/>

--- a/hochschule/Hassine_3399727_Tätigkeitsnachweis.xlsx
+++ b/hochschule/Hassine_3399727_Tätigkeitsnachweis.xlsx
@@ -2476,7 +2476,7 @@
       <c r="H14" s="100" t="n"/>
       <c r="I14" s="104" t="inlineStr">
         <is>
-          <t>Amine</t>
+          <t>Amin</t>
         </is>
       </c>
       <c r="J14" s="114" t="n"/>

--- a/hochschule/Hassine_3399727_Tätigkeitsnachweis.xlsx
+++ b/hochschule/Hassine_3399727_Tätigkeitsnachweis.xlsx
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="E16" s="118" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="F16" s="91" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="E17" s="119" t="n">
-        <v>8.25</v>
+        <v>9.75</v>
       </c>
       <c r="F17" s="92" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         </is>
       </c>
       <c r="E18" s="119" t="n">
-        <v>8.25</v>
+        <v>9.25</v>
       </c>
       <c r="F18" s="92" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         </is>
       </c>
       <c r="E19" s="119" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="F19" s="92" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="E20" s="119" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="F20" s="92" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="G21" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H21" s="67" t="n"/>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="G22" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H22" s="67" t="n"/>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="E23" s="119" t="n">
-        <v>8.25</v>
+        <v>9.25</v>
       </c>
       <c r="F23" s="92" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="E24" s="119" t="n">
-        <v>8.5</v>
+        <v>9.75</v>
       </c>
       <c r="F24" s="92" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         </is>
       </c>
       <c r="E25" s="119" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="F25" s="92" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="E26" s="119" t="n">
-        <v>8.25</v>
+        <v>9.5</v>
       </c>
       <c r="F26" s="92" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         </is>
       </c>
       <c r="E27" s="119" t="n">
-        <v>8.5</v>
+        <v>9.75</v>
       </c>
       <c r="F27" s="92" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
       </c>
       <c r="G28" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H28" s="67" t="n"/>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="G29" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H29" s="67" t="n"/>
@@ -4333,7 +4333,7 @@
         </is>
       </c>
       <c r="E30" s="119" t="n">
-        <v>8.5</v>
+        <v>7.25</v>
       </c>
       <c r="F30" s="92" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="E31" s="119" t="n">
-        <v>8.25</v>
+        <v>8</v>
       </c>
       <c r="F31" s="92" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         </is>
       </c>
       <c r="E32" s="119" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="F32" s="92" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="H32" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP bis 11:30, danach im Betrieb. Belegungsplan erstellt: jeder der 135 Sorten einen festen, beschrifteten Platz zugeordnet. Bezugsquellen recherchiert, Ergebnisse dem Betreuer vorgestellt und eine Arbeitsanweisung für die Materialentnahme entworfen.</t>
+          <t>Vorlesung PP 10:00-11:30 an der OTH, davor und danach im Betrieb. Belegungsplan erstellt: jeder der 135 Sorten einen festen, beschrifteten Platz zugeordnet. Bezugsquellen recherchiert, Ergebnisse dem Betreuer vorgestellt und eine Arbeitsanweisung für die Materialentnahme entworfen.</t>
         </is>
       </c>
       <c r="I32" s="86" t="n"/>
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="E33" s="119" t="n">
-        <v>8.25</v>
+        <v>7.5</v>
       </c>
       <c r="F33" s="92" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G34" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H34" s="67" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="G35" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H35" s="67" t="n"/>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="G36" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H36" s="67" t="n"/>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="E37" s="119" t="n">
-        <v>8.5</v>
+        <v>9.75</v>
       </c>
       <c r="F37" s="92" t="inlineStr">
         <is>
@@ -4646,7 +4646,7 @@
         </is>
       </c>
       <c r="E38" s="119" t="n">
-        <v>8.5</v>
+        <v>7.75</v>
       </c>
       <c r="F38" s="92" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="E39" s="119" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="F39" s="92" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="H39" s="95" t="inlineStr">
         <is>
-          <t>Vorlesung PP bis 11:30, danach im Betrieb. Barcode-Suche umgesetzt: Der eingescannte Code springt zum Artikel und zeigt alle Felder im Dashboard an.</t>
+          <t>Vorlesung PP 10:00-11:30 an der OTH, davor und danach im Betrieb. Barcode-Suche umgesetzt: Der eingescannte Code springt zum Artikel und zeigt alle Felder im Dashboard an.</t>
         </is>
       </c>
       <c r="I39" s="86" t="n"/>
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="E40" s="119" t="n">
-        <v>8.25</v>
+        <v>8</v>
       </c>
       <c r="F40" s="92" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="E41" s="119" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="F41" s="92" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
       </c>
       <c r="G42" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H42" s="67" t="n"/>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H43" s="74" t="n"/>
@@ -5186,7 +5186,7 @@
         </is>
       </c>
       <c r="E59" s="118" t="n">
-        <v>8.25</v>
+        <v>9.25</v>
       </c>
       <c r="F59" s="91" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         </is>
       </c>
       <c r="E60" s="119" t="n">
-        <v>8.5</v>
+        <v>7.25</v>
       </c>
       <c r="F60" s="92" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         </is>
       </c>
       <c r="E61" s="119" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="H61" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP bis 11:30, danach im Betrieb. Filterfunktion über Bezeichnung, Profil, Maß und Materialgruppe umgesetzt und getestet.</t>
+          <t>Vorlesung PP 10:00-11:30 an der OTH, davor und danach im Betrieb. Filterfunktion über Bezeichnung, Profil, Maß und Materialgruppe umgesetzt und getestet.</t>
         </is>
       </c>
       <c r="I61" s="86" t="n"/>
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="E62" s="119" t="n">
-        <v>8.25</v>
+        <v>7.25</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
       </c>
       <c r="G63" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H63" s="67" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="G64" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H64" s="67" t="n"/>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="G65" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H65" s="67" t="n"/>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="G66" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H66" s="94" t="inlineStr">
@@ -5490,7 +5490,7 @@
         </is>
       </c>
       <c r="E67" s="119" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         </is>
       </c>
       <c r="E68" s="119" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="H68" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP bis 11:30, danach im Betrieb. Einstellungsblatt angelegt, damit Zielordner, Empfängeradresse und Schwellenwerte ohne Eingriff in den Code änderbar sind.</t>
+          <t>Vorlesung PP 10:00-11:30 an der OTH, davor und danach im Betrieb. Einstellungsblatt angelegt, damit Zielordner, Empfängeradresse und Schwellenwerte ohne Eingriff in den Code änderbar sind.</t>
         </is>
       </c>
       <c r="I68" s="86" t="n"/>
@@ -5572,7 +5572,7 @@
         </is>
       </c>
       <c r="E69" s="119" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         </is>
       </c>
       <c r="E70" s="119" t="n">
-        <v>8.25</v>
+        <v>7.75</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
       </c>
       <c r="G71" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H71" s="67" t="n"/>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="G72" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H72" s="67" t="n"/>
@@ -5716,7 +5716,7 @@
         </is>
       </c>
       <c r="E73" s="119" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="E74" s="119" t="n">
-        <v>8</v>
+        <v>9.75</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="E75" s="119" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="H75" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP bis 11:30, danach im Betrieb. Material-Entnahme umgesetzt: Restlängen werden automatisch angelegt oder mit vorhandenen gleich langen Resten zusammengefasst.</t>
+          <t>Vorlesung PP 10:00-11:30 an der OTH, davor und danach im Betrieb. Material-Entnahme umgesetzt: Restlängen werden automatisch angelegt oder mit vorhandenen gleich langen Resten zusammengefasst.</t>
         </is>
       </c>
       <c r="I75" s="86" t="n"/>
@@ -5839,7 +5839,7 @@
         </is>
       </c>
       <c r="E76" s="119" t="n">
-        <v>8.25</v>
+        <v>7.25</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="E77" s="119" t="n">
-        <v>8.25</v>
+        <v>7.5</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="G78" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H78" s="67" t="n"/>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="G79" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H79" s="67" t="n"/>
@@ -5983,7 +5983,7 @@
         </is>
       </c>
       <c r="E80" s="119" t="n">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         </is>
       </c>
       <c r="E82" s="119" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="H82" s="67" t="inlineStr">
         <is>
-          <t>Vorlesung PP bis 11:30, danach im Betrieb. Datenmodell aus den Excel-Blättern übernommen und die Kernfunktionen portiert: Artikel verwalten, Buchungen, Verlauf und die Material-Entnahme mit Resteverwaltung. 86 reale Artikel-Datensätze und 50 Artikelgruppen übernommen und die Übernahme kontrolliert.</t>
+          <t>Vorlesung PP 10:00-11:30 an der OTH, davor und danach im Betrieb. Datenmodell aus den Excel-Blättern übernommen und die Kernfunktionen portiert: Artikel verwalten, Buchungen, Verlauf und die Material-Entnahme mit Resteverwaltung. 86 reale Artikel-Datensätze und 50 Artikelgruppen übernommen und die Übernahme kontrolliert.</t>
         </is>
       </c>
       <c r="I82" s="86" t="n"/>
@@ -6106,7 +6106,7 @@
         </is>
       </c>
       <c r="E83" s="119" t="n">
-        <v>8.25</v>
+        <v>7.5</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         </is>
       </c>
       <c r="E84" s="119" t="n">
-        <v>8</v>
+        <v>7.25</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="G85" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H85" s="67" t="n"/>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="G86" s="13" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H86" s="74" t="n"/>
@@ -6564,7 +6564,7 @@
         </is>
       </c>
       <c r="E102" s="118" t="n">
-        <v>8</v>
+        <v>9.25</v>
       </c>
       <c r="F102" s="6" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         </is>
       </c>
       <c r="E103" s="119" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -6642,10 +6642,12 @@
       </c>
       <c r="D104" s="65" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="E104" s="119" t="n"/>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="E104" s="119" t="n">
+        <v>2.5</v>
+      </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -6658,7 +6660,7 @@
       </c>
       <c r="H104" s="67" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00-11:30 und Praktikum Regelungstechnik 15:30-17:00 an der OTH, keine Anwesenheit im Betrieb</t>
+          <t>Vorlesung PP 10:00-11:30 und Praktikum Regelungstechnik 15:30-17:00 an der OTH, Vormittag im Betrieb. Werkzeugaufnahme fortgesetzt: Kategorien Schweißen MAG/MIG und Schweißen E-Hand vollständig erfasst.</t>
         </is>
       </c>
       <c r="I104" s="86" t="n"/>
@@ -6685,7 +6687,7 @@
         </is>
       </c>
       <c r="E105" s="119" t="n">
-        <v>8.25</v>
+        <v>7.75</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6699,7 +6701,7 @@
       </c>
       <c r="H105" s="67" t="inlineStr">
         <is>
-          <t>Werkzeugaufnahme fortgesetzt: Kategorien Schweißen MAG/MIG und Schweißen E-Hand vollständig erfasst.</t>
+          <t>Kategorien Spannen und Fixieren sowie Nachbearbeitung erfasst und mit den Mitarbeitern auf Vollständigkeit geprüft.</t>
         </is>
       </c>
       <c r="I105" s="86" t="n"/>
@@ -6733,7 +6735,7 @@
       </c>
       <c r="G106" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H106" s="67" t="inlineStr">
@@ -6768,7 +6770,7 @@
       </c>
       <c r="G107" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H107" s="67" t="n"/>
@@ -6799,7 +6801,7 @@
       </c>
       <c r="G108" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H108" s="67" t="n"/>
@@ -6827,7 +6829,7 @@
         </is>
       </c>
       <c r="E109" s="119" t="n">
-        <v>8.5</v>
+        <v>7.25</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6841,7 +6843,7 @@
       </c>
       <c r="H109" s="94" t="inlineStr">
         <is>
-          <t>Kategorien Spannen und Fixieren sowie Nachbearbeitung erfasst und mit den Mitarbeitern auf Vollständigkeit geprüft.</t>
+          <t>Kategorien Anreißen und Messen sowie persönliche Schutzausrüstung für drei Personen zusammengestellt.</t>
         </is>
       </c>
       <c r="I109" s="86" t="n"/>
@@ -6868,7 +6870,7 @@
         </is>
       </c>
       <c r="E110" s="119" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6882,7 +6884,7 @@
       </c>
       <c r="H110" s="94" t="inlineStr">
         <is>
-          <t>Kategorien Anreißen und Messen sowie persönliche Schutzausrüstung für drei Personen zusammengestellt.</t>
+          <t>Kategorien Sicherheit und Umgebung, Verbrauchsmaterial sowie 5S-Möbel ergänzt. Damit sind alle neun Werkzeugkategorien A bis I erfasst.</t>
         </is>
       </c>
       <c r="I110" s="86" t="n"/>
@@ -6909,7 +6911,7 @@
         </is>
       </c>
       <c r="E111" s="119" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6923,7 +6925,7 @@
       </c>
       <c r="H111" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP bis 11:30, danach im Betrieb. Kategorien Sicherheit und Umgebung, Verbrauchsmaterial sowie 5S-Möbel ergänzt. Damit sind alle neun Werkzeugkategorien A bis I erfasst.</t>
+          <t>Vorlesung PP 10:00-11:30 an der OTH, davor und danach im Betrieb. Marktrecherche zu den Werkzeugen begonnen und Richtpreise je Position gesammelt.</t>
         </is>
       </c>
       <c r="I111" s="86" t="n"/>
@@ -6950,7 +6952,7 @@
         </is>
       </c>
       <c r="E112" s="119" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6964,7 +6966,7 @@
       </c>
       <c r="H112" s="94" t="inlineStr">
         <is>
-          <t>Marktrecherche zu den Werkzeugen begonnen und Richtpreise je Position gesammelt.</t>
+          <t>Marktrecherche abgeschlossen und je Kaufteil drei Preisstufen gegenübergestellt.</t>
         </is>
       </c>
       <c r="I112" s="86" t="n"/>
@@ -6991,7 +6993,7 @@
         </is>
       </c>
       <c r="E113" s="119" t="n">
-        <v>8.25</v>
+        <v>7.75</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -7005,7 +7007,7 @@
       </c>
       <c r="H113" s="67" t="inlineStr">
         <is>
-          <t>Marktrecherche abgeschlossen und je Kaufteil drei Preisstufen gegenübergestellt.</t>
+          <t>Ergonomische Grundmaße für den Arbeitsplatz zusammengetragen (Arbeitshöhe, Greifräume, Beleuchtung) und mit den Normvorgaben abgeglichen.</t>
         </is>
       </c>
       <c r="I113" s="86" t="n"/>
@@ -7035,7 +7037,7 @@
       </c>
       <c r="G114" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H114" s="67" t="n"/>
@@ -7066,7 +7068,7 @@
       </c>
       <c r="G115" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H115" s="67" t="n"/>
@@ -7094,7 +7096,7 @@
         </is>
       </c>
       <c r="E116" s="119" t="n">
-        <v>8.25</v>
+        <v>9.75</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -7108,7 +7110,7 @@
       </c>
       <c r="H116" s="94" t="inlineStr">
         <is>
-          <t>Ergonomische Grundmaße für den Arbeitsplatz zusammengetragen (Arbeitshöhe, Greifräume, Beleuchtung) und mit den Normvorgaben abgeglichen.</t>
+          <t>Erstes Layout-Konzept für den Platz gezeichnet und die Wege zwischen Tisch, Maschine und Materialablage geprüft.</t>
         </is>
       </c>
       <c r="I116" s="86" t="n"/>
@@ -7135,7 +7137,7 @@
         </is>
       </c>
       <c r="E117" s="119" t="n">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -7149,7 +7151,7 @@
       </c>
       <c r="H117" s="94" t="inlineStr">
         <is>
-          <t>Erstes Layout-Konzept für den Platz gezeichnet und die Wege zwischen Tisch, Maschine und Materialablage geprüft.</t>
+          <t>Zwei weitere Layout-Varianten entwickelt und die drei Konzepte nebeneinandergestellt.</t>
         </is>
       </c>
       <c r="I117" s="86" t="n"/>
@@ -7176,7 +7178,7 @@
         </is>
       </c>
       <c r="E118" s="119" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -7190,7 +7192,7 @@
       </c>
       <c r="H118" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP bis 11:30, danach im Betrieb. Zwei weitere Layout-Varianten entwickelt und die drei Konzepte nebeneinandergestellt.</t>
+          <t>Vorlesung PP 10:00-11:30 an der OTH, davor und danach im Betrieb. Nutzwertanalyse für die Werkbank-Ausführung aufgestellt: Kriterien festgelegt und gewichtet.</t>
         </is>
       </c>
       <c r="I118" s="86" t="n"/>
@@ -7224,7 +7226,7 @@
       </c>
       <c r="G119" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H119" s="94" t="inlineStr">
@@ -7256,7 +7258,7 @@
         </is>
       </c>
       <c r="E120" s="119" t="n">
-        <v>7.75</v>
+        <v>7.25</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -7270,7 +7272,7 @@
       </c>
       <c r="H120" s="94" t="inlineStr">
         <is>
-          <t>Nutzwertanalyse für die Werkbank-Ausführung aufgestellt: Kriterien festgelegt und gewichtet.</t>
+          <t>Nutzwertanalyse für das Layout-Konzept gerechnet und die Ergebnisse ausgewertet.</t>
         </is>
       </c>
       <c r="I120" s="86" t="n"/>
@@ -7300,7 +7302,7 @@
       </c>
       <c r="G121" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H121" s="67" t="n"/>
@@ -7331,7 +7333,7 @@
       </c>
       <c r="G122" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H122" s="67" t="n"/>
@@ -7359,7 +7361,7 @@
         </is>
       </c>
       <c r="E123" s="119" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -7373,7 +7375,7 @@
       </c>
       <c r="H123" s="94" t="inlineStr">
         <is>
-          <t>Nutzwertanalyse für das Layout-Konzept gerechnet und die Ergebnisse ausgewertet.</t>
+          <t>Aufgabenstellung zum neuen Schweißtisch erhalten. Anforderungen mit dem Betreuer gesammelt: Größe, Spannmöglichkeiten, Fahrbarkeit.</t>
         </is>
       </c>
       <c r="I123" s="86" t="n"/>
@@ -7400,7 +7402,7 @@
         </is>
       </c>
       <c r="E124" s="119" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7414,7 +7416,7 @@
       </c>
       <c r="H124" s="67" t="inlineStr">
         <is>
-          <t>Aufgabenstellung zum neuen Schweißtisch erhalten. Anforderungen mit dem Betreuer gesammelt: Größe, Spannmöglichkeiten, Fahrbarkeit.</t>
+          <t>Vorhandenen Tisch vermessen und die Schwachstellen im Betrieb aufgenommen.</t>
         </is>
       </c>
       <c r="I124" s="86" t="n"/>
@@ -7437,10 +7439,12 @@
       </c>
       <c r="D125" s="65" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="E125" s="119" t="n"/>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="E125" s="119" t="n">
+        <v>2.5</v>
+      </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -7453,7 +7457,7 @@
       </c>
       <c r="H125" s="67" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00-11:30 und Praktikum Regelungstechnik 15:30-17:00 an der OTH, keine Anwesenheit im Betrieb</t>
+          <t>Vorlesung PP 10:00-11:30 und Praktikum Regelungstechnik 15:30-17:00 an der OTH, Vormittag im Betrieb. Recherche zu Schweißtisch-Konzepten und Spannsystemen durchgeführt, Beispiele gesammelt und bewertet.</t>
         </is>
       </c>
       <c r="I125" s="86" t="n"/>
@@ -7494,7 +7498,7 @@
       </c>
       <c r="H126" s="67" t="inlineStr">
         <is>
-          <t>Vorhandenen Tisch vermessen und die Schwachstellen im Betrieb aufgenommen.</t>
+          <t>Erste Handskizzen für den neuen Tisch angefertigt und mit dem Betreuer besprochen.</t>
         </is>
       </c>
       <c r="I126" s="86" t="n"/>
@@ -7521,7 +7525,7 @@
         </is>
       </c>
       <c r="E127" s="119" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7535,7 +7539,7 @@
       </c>
       <c r="H127" s="67" t="inlineStr">
         <is>
-          <t>Recherche zu Schweißtisch-Konzepten und Spannsystemen durchgeführt, Beispiele gesammelt und bewertet.</t>
+          <t>Grundkonzept festgelegt: ausziehbarer Tisch mit Lochplatten-Spannsystem auf fahrbarem Untergestell.</t>
         </is>
       </c>
       <c r="I127" s="86" t="n"/>
@@ -7565,7 +7569,7 @@
       </c>
       <c r="G128" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H128" s="67" t="n"/>
@@ -7596,7 +7600,7 @@
       </c>
       <c r="G129" s="13" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H129" s="74" t="n"/>
@@ -7945,7 +7949,7 @@
       </c>
       <c r="G145" s="8" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H145" s="94" t="inlineStr">
@@ -7977,7 +7981,7 @@
         </is>
       </c>
       <c r="E146" s="119" t="n">
-        <v>7.5</v>
+        <v>9.25</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -7991,7 +7995,7 @@
       </c>
       <c r="H146" s="94" t="inlineStr">
         <is>
-          <t>Erste Handskizzen für den neuen Tisch angefertigt und mit dem Betreuer besprochen.</t>
+          <t>Marktrecherche zu Lochplatten durchgeführt, Angebote verglichen und das D16-Raster ausgewählt.</t>
         </is>
       </c>
       <c r="I146" s="86" t="n"/>
@@ -8014,10 +8018,12 @@
       </c>
       <c r="D147" s="65" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="E147" s="119" t="n"/>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="E147" s="119" t="n">
+        <v>2.5</v>
+      </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
           <t>h</t>
@@ -8030,7 +8036,7 @@
       </c>
       <c r="H147" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00-11:30 und Praktikum Regelungstechnik 15:30-17:00 an der OTH, keine Anwesenheit im Betrieb</t>
+          <t>Vorlesung PP 10:00-11:30 und Praktikum Regelungstechnik 15:30-17:00 an der OTH, Vormittag im Betrieb. Mit der CAD-Konstruktion begonnen: Tischplatte mit Lochraster aufgebaut.</t>
         </is>
       </c>
       <c r="I147" s="86" t="n"/>
@@ -8057,7 +8063,7 @@
         </is>
       </c>
       <c r="E148" s="119" t="n">
-        <v>7.5</v>
+        <v>7.25</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -8071,7 +8077,7 @@
       </c>
       <c r="H148" s="94" t="inlineStr">
         <is>
-          <t>Grundkonzept festgelegt: ausziehbarer Tisch mit Lochplatten-Spannsystem auf fahrbarem Untergestell.</t>
+          <t>Oberteil konstruiert: Träger und Profile modelliert und die Teilenummern vergeben.</t>
         </is>
       </c>
       <c r="I148" s="86" t="n"/>
@@ -8098,7 +8104,7 @@
         </is>
       </c>
       <c r="E149" s="119" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
@@ -8112,7 +8118,7 @@
       </c>
       <c r="H149" s="94" t="inlineStr">
         <is>
-          <t>Marktrecherche zu Lochplatten durchgeführt, Angebote verglichen und das D16-Raster ausgewählt.</t>
+          <t>Unterteil konstruiert: Beine, Streben und Fußplatten aufgebaut.</t>
         </is>
       </c>
       <c r="I149" s="86" t="n"/>
@@ -8142,7 +8148,7 @@
       </c>
       <c r="G150" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H150" s="67" t="n"/>
@@ -8173,7 +8179,7 @@
       </c>
       <c r="G151" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H151" s="67" t="n"/>
@@ -8201,7 +8207,7 @@
         </is>
       </c>
       <c r="E152" s="119" t="n">
-        <v>8</v>
+        <v>7.25</v>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
@@ -8215,7 +8221,7 @@
       </c>
       <c r="H152" s="94" t="inlineStr">
         <is>
-          <t>Mit der CAD-Konstruktion begonnen: Tischplatte mit Lochraster aufgebaut.</t>
+          <t>Erweiterungssystem als Teleskop-Rahmen konstruiert, beidseitig ausziehbar.</t>
         </is>
       </c>
       <c r="I152" s="86" t="n"/>
@@ -8242,7 +8248,7 @@
         </is>
       </c>
       <c r="E153" s="119" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
@@ -8256,7 +8262,7 @@
       </c>
       <c r="H153" s="67" t="inlineStr">
         <is>
-          <t>Oberteil konstruiert: Träger und Profile modelliert und die Teilenummern vergeben.</t>
+          <t>Baugruppen zum Gesamtzusammenbau zusammengeführt und die Struktur geordnet.</t>
         </is>
       </c>
       <c r="I153" s="86" t="n"/>
@@ -8283,7 +8289,7 @@
         </is>
       </c>
       <c r="E154" s="119" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
@@ -8297,7 +8303,7 @@
       </c>
       <c r="H154" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP bis 11:30, danach im Betrieb. Unterteil konstruiert: Beine, Streben und Fußplatten aufgebaut.</t>
+          <t>Vorlesung PP 10:00-11:30 an der OTH, davor und danach im Betrieb. Kollisionen und Verfahrwege im Modell geprüft und die Führungen angepasst.</t>
         </is>
       </c>
       <c r="I154" s="86" t="n"/>
@@ -8331,7 +8337,7 @@
       </c>
       <c r="G155" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H155" s="94" t="inlineStr">
@@ -8363,7 +8369,7 @@
         </is>
       </c>
       <c r="E156" s="119" t="n">
-        <v>7.25</v>
+        <v>9.75</v>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
@@ -8377,7 +8383,7 @@
       </c>
       <c r="H156" s="67" t="inlineStr">
         <is>
-          <t>Erweiterungssystem als Teleskop-Rahmen konstruiert, beidseitig ausziehbar.</t>
+          <t>Erste Zeichnungsblätter abgeleitet und bemaßt.</t>
         </is>
       </c>
       <c r="I156" s="86" t="n"/>
@@ -8407,7 +8413,7 @@
       </c>
       <c r="G157" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H157" s="67" t="n"/>
@@ -8438,7 +8444,7 @@
       </c>
       <c r="G158" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H158" s="67" t="n"/>
@@ -8466,7 +8472,7 @@
         </is>
       </c>
       <c r="E159" s="119" t="n">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
@@ -8480,7 +8486,7 @@
       </c>
       <c r="H159" s="94" t="inlineStr">
         <is>
-          <t>Baugruppen zum Gesamtzusammenbau zusammengeführt und die Struktur geordnet.</t>
+          <t>Weitere Einzelteilzeichnungen erstellt und die Schriftfelder ausgefüllt.</t>
         </is>
       </c>
       <c r="I159" s="86" t="n"/>
@@ -8507,7 +8513,7 @@
         </is>
       </c>
       <c r="E160" s="119" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
@@ -8521,7 +8527,7 @@
       </c>
       <c r="H160" s="94" t="inlineStr">
         <is>
-          <t>Kollisionen und Verfahrwege im Modell geprüft und die Führungen angepasst.</t>
+          <t>Aufgabenstellung zum Schweißmaschinenwagen erhalten. Vorhandenen Wagen im Betrieb fotografiert und den Zustand aufgenommen.</t>
         </is>
       </c>
       <c r="I160" s="86" t="n"/>
@@ -8548,7 +8554,7 @@
         </is>
       </c>
       <c r="E161" s="119" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
@@ -8562,7 +8568,7 @@
       </c>
       <c r="H161" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP bis 11:30, danach im Betrieb. Erste Zeichnungsblätter abgeleitet und bemaßt.</t>
+          <t>Vorlesung PP 10:00-11:30 an der OTH, davor und danach im Betrieb. Schweißgerät und Gasflasche vor Ort aufgemessen und die Maße in einer Handskizze festgehalten.</t>
         </is>
       </c>
       <c r="I161" s="86" t="n"/>
@@ -8589,7 +8595,7 @@
         </is>
       </c>
       <c r="E162" s="119" t="n">
-        <v>7.25</v>
+        <v>9.25</v>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
@@ -8603,7 +8609,7 @@
       </c>
       <c r="H162" s="94" t="inlineStr">
         <is>
-          <t>Weitere Einzelteilzeichnungen erstellt und die Schriftfelder ausgefüllt.</t>
+          <t>Vereinfachte CAD-Platzhalter für Gerät und Flasche erstellt, um den Bauraum abzubilden.</t>
         </is>
       </c>
       <c r="I162" s="86" t="n"/>
@@ -8630,7 +8636,7 @@
         </is>
       </c>
       <c r="E163" s="119" t="n">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
@@ -8644,7 +8650,7 @@
       </c>
       <c r="H163" s="94" t="inlineStr">
         <is>
-          <t>Aufgabenstellung zum Schweißmaschinenwagen erhalten. Vorhandenen Wagen im Betrieb fotografiert und den Zustand aufgenommen.</t>
+          <t>Anforderungsliste aufgestellt: was der Wagen tragen und was er können muss.</t>
         </is>
       </c>
       <c r="I163" s="86" t="n"/>
@@ -8674,7 +8680,7 @@
       </c>
       <c r="G164" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H164" s="67" t="n"/>
@@ -8705,7 +8711,7 @@
       </c>
       <c r="G165" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H165" s="67" t="n"/>
@@ -8733,7 +8739,7 @@
         </is>
       </c>
       <c r="E166" s="119" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
@@ -8747,7 +8753,7 @@
       </c>
       <c r="H166" s="94" t="inlineStr">
         <is>
-          <t>Schweißgerät und Gasflasche vor Ort aufgemessen und die Maße in einer Handskizze festgehalten.</t>
+          <t>Anforderungsliste auf 14 nummerierte Punkte gebracht und mit dem Betreuer abgestimmt.</t>
         </is>
       </c>
       <c r="I166" s="86" t="n"/>
@@ -8774,7 +8780,7 @@
         </is>
       </c>
       <c r="E167" s="119" t="n">
-        <v>7.5</v>
+        <v>7.25</v>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
@@ -8788,7 +8794,7 @@
       </c>
       <c r="H167" s="94" t="inlineStr">
         <is>
-          <t>Vereinfachte CAD-Platzhalter für Gerät und Flasche erstellt, um den Bauraum abzubilden.</t>
+          <t>Referenzprojekte recherchiert und fünf Designrichtungen für den Wagen gesammelt.</t>
         </is>
       </c>
       <c r="I167" s="86" t="n"/>
@@ -8815,7 +8821,7 @@
         </is>
       </c>
       <c r="E168" s="119" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
@@ -8829,7 +8835,7 @@
       </c>
       <c r="H168" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP bis 11:30, danach im Betrieb. Anforderungsliste aufgestellt: was der Wagen tragen und was er können muss.</t>
+          <t>Vorlesung PP 10:00-11:30 an der OTH, davor und danach im Betrieb. Zwei erste Entwürfe im CAD aufgebaut und gegenübergestellt.</t>
         </is>
       </c>
       <c r="I168" s="86" t="n"/>
@@ -8856,7 +8862,7 @@
         </is>
       </c>
       <c r="E169" s="119" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
@@ -8870,7 +8876,7 @@
       </c>
       <c r="H169" s="67" t="inlineStr">
         <is>
-          <t>Anforderungsliste auf 14 nummerierte Punkte gebracht und mit dem Betreuer abgestimmt.</t>
+          <t>Maße und Ergonomie festgelegt, Gewicht des beladenen Wagens grob abgeschätzt.</t>
         </is>
       </c>
       <c r="I169" s="86" t="n"/>
@@ -8897,7 +8903,7 @@
         </is>
       </c>
       <c r="E170" s="119" t="n">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
@@ -8911,7 +8917,7 @@
       </c>
       <c r="H170" s="94" t="inlineStr">
         <is>
-          <t>Referenzprojekte recherchiert und fünf Designrichtungen für den Wagen gesammelt.</t>
+          <t>Kompletten Neubau als Variante A konstruiert und einen Belegungsplan mit 16 Werkzeugpositionen erstellt.</t>
         </is>
       </c>
       <c r="I170" s="86" t="n"/>
@@ -8941,7 +8947,7 @@
       </c>
       <c r="G171" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H171" s="67" t="n"/>
@@ -8972,7 +8978,7 @@
       </c>
       <c r="G172" s="13" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H172" s="74" t="n"/>
@@ -9314,7 +9320,7 @@
         </is>
       </c>
       <c r="E188" s="118" t="n">
-        <v>7.25</v>
+        <v>6.75</v>
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
@@ -9328,7 +9334,7 @@
       </c>
       <c r="H188" s="94" t="inlineStr">
         <is>
-          <t>Zwei erste Entwürfe im CAD aufgebaut und gegenübergestellt.</t>
+          <t>Beim Maßabgleich festgestellt, dass das geplante Gerätefach zu niedrig für die vorhandene Maschine ist.</t>
         </is>
       </c>
       <c r="I188" s="86" t="n"/>
@@ -9369,7 +9375,7 @@
       </c>
       <c r="H189" s="94" t="inlineStr">
         <is>
-          <t>Maße und Ergonomie festgelegt, Gewicht des beladenen Wagens grob abgeschätzt.</t>
+          <t>Als Variante B ein Aufsatzgestell entworfen, das über den vorhandenen Wagen fährt.</t>
         </is>
       </c>
       <c r="I189" s="86" t="n"/>
@@ -9396,7 +9402,7 @@
         </is>
       </c>
       <c r="E190" s="119" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
@@ -9410,7 +9416,7 @@
       </c>
       <c r="H190" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP bis 11:30, danach im Betrieb. Kompletten Neubau als Variante A konstruiert und einen Belegungsplan mit 16 Werkzeugpositionen erstellt.</t>
+          <t>Vorlesung PP 10:00-11:30 an der OTH, davor und danach im Betrieb. Variante B überarbeitet, sodass die Gasflasche innerhalb der Aufstandsfläche steht.</t>
         </is>
       </c>
       <c r="I190" s="86" t="n"/>
@@ -9437,7 +9443,7 @@
         </is>
       </c>
       <c r="E191" s="119" t="n">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
@@ -9451,7 +9457,7 @@
       </c>
       <c r="H191" s="94" t="inlineStr">
         <is>
-          <t>Beim Maßabgleich festgestellt, dass das geplante Gerätefach zu niedrig für die vorhandene Maschine ist.</t>
+          <t>Vorzugsvariante festgelegt: modularer Aufbau in vier Etagen.</t>
         </is>
       </c>
       <c r="I191" s="86" t="n"/>
@@ -9478,7 +9484,7 @@
         </is>
       </c>
       <c r="E192" s="119" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
@@ -9492,7 +9498,7 @@
       </c>
       <c r="H192" s="94" t="inlineStr">
         <is>
-          <t>Als Variante B ein Aufsatzgestell entworfen, das über den vorhandenen Wagen fährt.</t>
+          <t>Aufgabenstellung zum Zerspanarbeitsplatz erhalten und die Rahmenbedingungen aufgenommen (Drehen und Fräsen, drei Personen, eine Schicht).</t>
         </is>
       </c>
       <c r="I192" s="86" t="n"/>
@@ -9522,7 +9528,7 @@
       </c>
       <c r="G193" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H193" s="67" t="n"/>
@@ -9553,7 +9559,7 @@
       </c>
       <c r="G194" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H194" s="67" t="n"/>
@@ -9581,7 +9587,7 @@
         </is>
       </c>
       <c r="E195" s="119" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
@@ -9595,7 +9601,7 @@
       </c>
       <c r="H195" s="94" t="inlineStr">
         <is>
-          <t>Variante B überarbeitet, sodass die Gasflasche innerhalb der Aufstandsfläche steht.</t>
+          <t>Bestehenden Platz besichtigt, Maschinen und vorhandene Ausstattung fotografiert.</t>
         </is>
       </c>
       <c r="I195" s="86" t="n"/>
@@ -9622,7 +9628,7 @@
         </is>
       </c>
       <c r="E196" s="119" t="n">
-        <v>7.5</v>
+        <v>7.25</v>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
@@ -9636,7 +9642,7 @@
       </c>
       <c r="H196" s="94" t="inlineStr">
         <is>
-          <t>Aufgabenstellung zum Zerspanarbeitsplatz erhalten und die Rahmenbedingungen aufgenommen (Drehen und Fräsen, drei Personen, eine Schicht).</t>
+          <t>Werkzeugbedarf für das Drehen zusammengestellt.</t>
         </is>
       </c>
       <c r="I196" s="86" t="n"/>
@@ -9677,7 +9683,7 @@
       </c>
       <c r="H197" s="94" t="inlineStr">
         <is>
-          <t>Bestehenden Platz besichtigt, Maschinen und vorhandene Ausstattung fotografiert.</t>
+          <t>Im Anschluss Praktikum Regelungstechnik 15:30-17:00 an der OTH. Werkzeugbedarf für das Fräsen sowie die Spann- und Aufspannmittel erfasst.</t>
         </is>
       </c>
       <c r="I197" s="86" t="n"/>
@@ -9704,7 +9710,7 @@
         </is>
       </c>
       <c r="E198" s="119" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
@@ -9718,7 +9724,7 @@
       </c>
       <c r="H198" s="94" t="inlineStr">
         <is>
-          <t>Werkzeugbedarf für das Drehen zusammengestellt.</t>
+          <t>Mess- und Prüfmittel sowie Nacharbeit und Hilfsmittel ergänzt. Damit sind alle sechs Gruppen erfasst.</t>
         </is>
       </c>
       <c r="I198" s="86" t="n"/>
@@ -9752,7 +9758,7 @@
       </c>
       <c r="G199" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H199" s="98" t="inlineStr">
@@ -9787,7 +9793,7 @@
       </c>
       <c r="G200" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H200" s="67" t="n"/>
@@ -9818,7 +9824,7 @@
       </c>
       <c r="G201" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H201" s="67" t="n"/>
@@ -9846,7 +9852,7 @@
         </is>
       </c>
       <c r="E202" s="119" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
@@ -9860,7 +9866,7 @@
       </c>
       <c r="H202" s="94" t="inlineStr">
         <is>
-          <t>Werkzeugbedarf für das Fräsen sowie die Spann- und Aufspannmittel erfasst.</t>
+          <t>Mengen je Position festgelegt und begründet, welche Werkzeuge dreifach beschafft werden müssen.</t>
         </is>
       </c>
       <c r="I202" s="86" t="n"/>
@@ -9901,7 +9907,7 @@
       </c>
       <c r="H203" s="94" t="inlineStr">
         <is>
-          <t>Mess- und Prüfmittel sowie Nacharbeit und Hilfsmittel ergänzt. Damit sind alle sechs Gruppen erfasst.</t>
+          <t>Preise recherchiert und die Werkzeugliste mit 35 Positionen bepreist.</t>
         </is>
       </c>
       <c r="I203" s="86" t="n"/>
@@ -9942,7 +9948,7 @@
       </c>
       <c r="H204" s="67" t="inlineStr">
         <is>
-          <t>Mengen je Position festgelegt und begründet, welche Werkzeuge dreifach beschafft werden müssen.</t>
+          <t>Kosten nach Kategorien ausgewertet und die teuersten Positionen herausgearbeitet.</t>
         </is>
       </c>
       <c r="I204" s="86" t="n"/>
@@ -9983,7 +9989,7 @@
       </c>
       <c r="H205" s="99" t="inlineStr">
         <is>
-          <t>Prüfung PRM an der OTH bis 10:00. Preise recherchiert und die Werkzeugliste mit 35 Positionen bepreist.</t>
+          <t>Prüfung PRM an der OTH bis 10:00. 5S-Ordnung ausgearbeitet und die Werkzeuge den Zonen A, B und C zugeordnet.</t>
         </is>
       </c>
       <c r="I205" s="86" t="n"/>
@@ -10010,7 +10016,7 @@
         </is>
       </c>
       <c r="E206" s="119" t="n">
-        <v>7.25</v>
+        <v>7.5</v>
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
@@ -10024,7 +10030,7 @@
       </c>
       <c r="H206" s="67" t="inlineStr">
         <is>
-          <t>Kosten nach Kategorien ausgewertet und die teuersten Positionen herausgearbeitet.</t>
+          <t>Grundmaße der Werkbank festgelegt und mit den Ergonomienormen abgeglichen.</t>
         </is>
       </c>
       <c r="I206" s="86" t="n"/>
@@ -10054,7 +10060,7 @@
       </c>
       <c r="G207" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H207" s="67" t="n"/>
@@ -10085,7 +10091,7 @@
       </c>
       <c r="G208" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H208" s="67" t="n"/>
@@ -10113,7 +10119,7 @@
         </is>
       </c>
       <c r="E209" s="119" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
@@ -10127,7 +10133,7 @@
       </c>
       <c r="H209" s="67" t="inlineStr">
         <is>
-          <t>5S-Ordnung ausgearbeitet und die Werkzeuge den Zonen A, B und C zugeordnet.</t>
+          <t>Vier Bauvarianten skizziert und in 3D dargestellt: Aluprofil, Stahl-Standard, Systemmodule und Eigenbau.</t>
         </is>
       </c>
       <c r="I209" s="86" t="n"/>
@@ -10154,7 +10160,7 @@
         </is>
       </c>
       <c r="E210" s="119" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
@@ -10168,7 +10174,7 @@
       </c>
       <c r="H210" s="67" t="inlineStr">
         <is>
-          <t>Grundmaße der Werkbank festgelegt und mit den Ergonomienormen abgeglichen.</t>
+          <t>Vier Layout-Konzepte entwickelt und die Vor- und Nachteile gegenübergestellt.</t>
         </is>
       </c>
       <c r="I210" s="86" t="n"/>
@@ -10195,7 +10201,7 @@
         </is>
       </c>
       <c r="E211" s="119" t="n">
-        <v>7.5</v>
+        <v>7.25</v>
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
@@ -10209,7 +10215,7 @@
       </c>
       <c r="H211" s="67" t="inlineStr">
         <is>
-          <t>Vier Bauvarianten skizziert und in 3D dargestellt: Aluprofil, Stahl-Standard, Systemmodule und Eigenbau.</t>
+          <t>Werkstatt-Grundriss maßstäblich gezeichnet und die Freiräume an den Maschinen geprüft.</t>
         </is>
       </c>
       <c r="I211" s="86" t="n"/>
@@ -10250,7 +10256,7 @@
       </c>
       <c r="H212" s="67" t="inlineStr">
         <is>
-          <t>Vier Layout-Konzepte entwickelt und die Vor- und Nachteile gegenübergestellt.</t>
+          <t>Nutzwertanalyse aufgestellt: sieben Kriterien festgelegt und gewichtet.</t>
         </is>
       </c>
       <c r="I212" s="86" t="n"/>
@@ -10291,7 +10297,7 @@
       </c>
       <c r="H213" s="67" t="inlineStr">
         <is>
-          <t>Prüfung DA an der OTH bis 10:00. Werkstatt-Grundriss maßstäblich gezeichnet und die Freiräume an den Maschinen geprüft.</t>
+          <t>Prüfung DA an der OTH bis 10:00. Bewertungsmatrix gerechnet und die Rangfolge der vier Varianten ausgewertet.</t>
         </is>
       </c>
       <c r="I213" s="86" t="n"/>
@@ -10321,7 +10327,7 @@
       </c>
       <c r="G214" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H214" s="67" t="n"/>
@@ -10352,7 +10358,7 @@
       </c>
       <c r="G215" s="13" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H215" s="74" t="n"/>
@@ -10708,7 +10714,7 @@
       </c>
       <c r="H231" s="61" t="inlineStr">
         <is>
-          <t>Prüfung GAT an der OTH bis 10:00. Nutzwertanalyse aufgestellt: sieben Kriterien festgelegt und gewichtet.</t>
+          <t>Prüfung GAT an der OTH bis 10:00. Aufgabenstellung zum Rostschutz für die Schienenprofile erhalten. Lagerbedingungen der Profile im Betrieb aufgenommen und fotografiert.</t>
         </is>
       </c>
       <c r="I231" s="86" t="n"/>
@@ -10735,7 +10741,7 @@
         </is>
       </c>
       <c r="E232" s="119" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
@@ -10749,7 +10755,7 @@
       </c>
       <c r="H232" s="67" t="inlineStr">
         <is>
-          <t>Aufgabenstellung zum Rostschutz für die Schienenprofile erhalten. Lagerbedingungen der Profile im Betrieb aufgenommen und fotografiert.</t>
+          <t>Bestehende Rostschäden begutachtet und die Ursachen mit den Mitarbeitern besprochen (Feuchtigkeit, Kondenswasser, Lagerdauer).</t>
         </is>
       </c>
       <c r="I232" s="86" t="n"/>
@@ -10776,7 +10782,7 @@
         </is>
       </c>
       <c r="E233" s="119" t="n">
-        <v>7.25</v>
+        <v>6.75</v>
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
@@ -10790,7 +10796,7 @@
       </c>
       <c r="H233" s="67" t="inlineStr">
         <is>
-          <t>Bestehende Rostschäden begutachtet und die Ursachen mit den Mitarbeitern besprochen (Feuchtigkeit, Kondenswasser, Lagerdauer).</t>
+          <t>Recherche zu Korrosionsschutzverfahren durchgeführt: Ölen, Wachsen, VCI-Folie und trockene Lagerung verglichen.</t>
         </is>
       </c>
       <c r="I233" s="86" t="n"/>
@@ -10817,7 +10823,7 @@
         </is>
       </c>
       <c r="E234" s="119" t="n">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
@@ -10831,7 +10837,7 @@
       </c>
       <c r="H234" s="67" t="inlineStr">
         <is>
-          <t>Recherche zu Korrosionsschutzverfahren durchgeführt: Ölen, Wachsen, VCI-Folie und trockene Lagerung verglichen.</t>
+          <t>Verfahren gegenübergestellt und nach Wirksamkeit, Aufwand und Kosten bewertet.</t>
         </is>
       </c>
       <c r="I234" s="86" t="n"/>
@@ -10858,7 +10864,7 @@
         </is>
       </c>
       <c r="E235" s="119" t="n">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
@@ -10872,7 +10878,7 @@
       </c>
       <c r="H235" s="67" t="inlineStr">
         <is>
-          <t>Verfahren gegenübergestellt und nach Wirksamkeit, Aufwand und Kosten bewertet.</t>
+          <t>Konzept für eine geschlossene Lagerbox mit VCI-Schutz entworfen und die benötigten Maße aufgenommen.</t>
         </is>
       </c>
       <c r="I235" s="86" t="n"/>
@@ -10902,7 +10908,7 @@
       </c>
       <c r="G236" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H236" s="67" t="n"/>
@@ -10933,7 +10939,7 @@
       </c>
       <c r="G237" s="96" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="H237" s="67" t="n"/>
@@ -10961,7 +10967,7 @@
         </is>
       </c>
       <c r="E238" s="119" t="n">
-        <v>7.25</v>
+        <v>7</v>
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
@@ -10975,7 +10981,7 @@
       </c>
       <c r="H238" s="67" t="inlineStr">
         <is>
-          <t>Konzept für eine geschlossene Lagerbox mit VCI-Schutz entworfen und die benötigten Maße aufgenommen.</t>
+          <t>Lagerbox im CAD konstruiert und die Aufteilung für die verschiedenen Profillängen festgelegt.</t>
         </is>
       </c>
       <c r="I238" s="86" t="n"/>
@@ -11016,7 +11022,7 @@
       </c>
       <c r="H239" s="67" t="inlineStr">
         <is>
-          <t>Prüfung SWV an der OTH bis 10:00. Lagerbox im CAD konstruiert und die Aufteilung für die verschiedenen Profillängen festgelegt.</t>
+          <t>Prüfung SWV an der OTH bis 10:00. Material- und Kostenaufstellung für die Schutzbox erstellt.</t>
         </is>
       </c>
       <c r="I239" s="86" t="n"/>
@@ -11057,7 +11063,7 @@
       </c>
       <c r="H240" s="67" t="inlineStr">
         <is>
-          <t>Material- und Kostenaufstellung für die Schutzbox erstellt.</t>
+          <t>Zeitersparnis durch den Wegfall des Nacharbeitens abgeschätzt und der Investition gegenübergestellt.</t>
         </is>
       </c>
       <c r="I240" s="86" t="n"/>
@@ -11084,7 +11090,7 @@
         </is>
       </c>
       <c r="E241" s="119" t="n">
-        <v>6.5</v>
+        <v>7.25</v>
       </c>
       <c r="F241" s="2" t="inlineStr">
         <is>
@@ -11098,7 +11104,7 @@
       </c>
       <c r="H241" s="67" t="inlineStr">
         <is>
-          <t>Zeitersparnis durch den Wegfall des Nacharbeitens abgeschätzt und der Investition gegenübergestellt.</t>
+          <t>Arbeitsanweisung für die Einlagerung und Entnahme der Schienenprofile entworfen.</t>
         </is>
       </c>
       <c r="I241" s="86" t="n"/>
@@ -11139,7 +11145,7 @@
       </c>
       <c r="H242" s="67" t="inlineStr">
         <is>
-          <t>Arbeitsanweisung für die Einlagerung und Entnahme der Schienenprofile entworfen.</t>
+          <t>Rostschutz-Konzept zusammengeschrieben, dem Betreuer vorgestellt und die Praktikumsunterlagen abschließend sortiert.</t>
         </is>
       </c>
       <c r="I242" s="86" t="n"/>

--- a/hochschule/Hassine_3399727_Tätigkeitsnachweis.xlsx
+++ b/hochschule/Hassine_3399727_Tätigkeitsnachweis.xlsx
@@ -5527,11 +5527,11 @@
       </c>
       <c r="D68" s="65" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E68" s="119" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="G68" s="96" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nein</t>
         </is>
       </c>
       <c r="H68" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00-11:30 an der OTH, davor und danach im Betrieb. Einstellungsblatt angelegt, damit Zielordner, Empfängeradresse und Schwellenwerte ohne Eingriff in den Code änderbar sind.</t>
+          <t>Einstellungsblatt angelegt, damit Zielordner, Empfängeradresse und Schwellenwerte ohne Eingriff in den Code änderbar sind.</t>
         </is>
       </c>
       <c r="I68" s="86" t="n"/>
@@ -5572,7 +5572,7 @@
         </is>
       </c>
       <c r="E69" s="119" t="n">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         </is>
       </c>
       <c r="E70" s="119" t="n">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         </is>
       </c>
       <c r="E73" s="119" t="n">
-        <v>7.5</v>
+        <v>9.75</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="E74" s="119" t="n">
-        <v>9.75</v>
+        <v>7.25</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         </is>
       </c>
       <c r="E76" s="119" t="n">
-        <v>7.25</v>
+        <v>7.5</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="E77" s="119" t="n">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         </is>
       </c>
       <c r="E80" s="119" t="n">
-        <v>7.75</v>
+        <v>8</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         </is>
       </c>
       <c r="E81" s="119" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         </is>
       </c>
       <c r="E83" s="119" t="n">
-        <v>7.5</v>
+        <v>7.25</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         </is>
       </c>
       <c r="E84" s="119" t="n">
-        <v>7.25</v>
+        <v>7.5</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         </is>
       </c>
       <c r="E103" s="119" t="n">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         </is>
       </c>
       <c r="E105" s="119" t="n">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="H149" s="94" t="inlineStr">
         <is>
-          <t>Unterteil konstruiert: Beine, Streben und Fußplatten aufgebaut.</t>
+          <t>Unterteil konstruiert: Beine, Streben und Fußplatten aufgebaut – Vierkantrohr 80×80×3 in den Längen 1328, 750 und 500 mm als Zukaufteile, dazu vier gebohrte Fußplatten 120×120×10 als Eigenfertigung.</t>
         </is>
       </c>
       <c r="I149" s="86" t="n"/>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="H156" s="67" t="inlineStr">
         <is>
-          <t>Erste Zeichnungsblätter abgeleitet und bemaßt.</t>
+          <t>Erste Zeichnungsblätter abgeleitet und bemaßt: je Baugruppe ein Zeichnungsblatt und ein zugehöriges Stücklistenblatt, durchnummeriert nach dem Schema 000-005-XXX-1, etwa 000-005-104-1 für das Oberteil Basic.</t>
         </is>
       </c>
       <c r="I156" s="86" t="n"/>
@@ -9457,7 +9457,7 @@
       </c>
       <c r="H191" s="94" t="inlineStr">
         <is>
-          <t>Vorzugsvariante festgelegt: modularer Aufbau in vier Etagen.</t>
+          <t>Vorzugsvariante festgelegt: modularer Aufbau in vier Etagen. Der Vorteil liegt in der Modularität – jede Etage ist eine eigene Baugruppe, und die beiden Schubladenetagen sind identisch, sodass nur eine Konstruktion in doppelter Stückzahl gefertigt werden muss.</t>
         </is>
       </c>
       <c r="I191" s="86" t="n"/>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="H196" s="94" t="inlineStr">
         <is>
-          <t>Werkzeugbedarf für das Drehen zusammengestellt.</t>
+          <t>Werkzeugbedarf für das Drehen zusammengestellt: Drehmeißelsatz, Wendeschneidplatten mit Haltern, Bohrfutter mit HSS-Bohrersatz, Zentrierbohrer, Gewindeschneidzeug und mitlaufende Körnerspitze – je mit Zweck und Menge.</t>
         </is>
       </c>
       <c r="I196" s="86" t="n"/>

--- a/hochschule/Hassine_3399727_Tätigkeitsnachweis.xlsx
+++ b/hochschule/Hassine_3399727_Tätigkeitsnachweis.xlsx
@@ -3441,7 +3441,7 @@
     <dataValidation sqref="B26" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="B2:G2 I8:N8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Auswahlfehler" error="Es sind nur die vorgegebenen Eingaben zulässig_x000a_" promptTitle="Anrede" prompt="Bitte geben Sie die gewünschte Anrede ein." type="list">
+    <dataValidation sqref="B2:G2 I8:N8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Auswahlfehler" error="Es sind nur die vorgegebenen Eingaben zulässig&#10;" promptTitle="Anrede" prompt="Bitte geben Sie die gewünschte Anrede ein." type="list">
       <formula1>"Herr, Frau, divers"</formula1>
     </dataValidation>
   </dataValidations>
@@ -19229,7 +19229,7 @@
     <dataValidation sqref="G16:G43 G59:G86 G102:G129 G145:G172 G188:G215 G231:G258 G274:G301 G317:G344 G360:G387 G403:G430 G446:G473 G489:G516 G532:G559" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Korrekte EIngabe beachten" error="Bitte geben Sie nur &quot;ja&quot; oder &quot;nein&quot; ein." promptTitle="begleitende Lehrveranstaltung" prompt="Bitte geben Sie hier &quot;ja&quot; an, wenn Sie an diesem Tag eine begleitende Lehrveranstaltung besucht haben. Alle anderen Lehrveranstaltungen sind hier nicht zu berücksichtigen." type="list" errorStyle="information">
       <formula1>"ja, nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="E16:E43 E59:E86 E102:E129 E145:E172 E188:E215 E231:E258 E274:E301 E317:E344 E360:E387 E403:E430 E446:E473 E489:E516 E532:E559" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Eingabe beachten" error="Bitte beachten Sie das vorgegebene Eingabeformat_x000a_" promptTitle="Eingabe Arbeitszeit" prompt="Geben Sie bitte als Dezimalzahl ihre Arbeitszeit (Anwesenheitszeit) am genannten Tag ein. 7 Stunden und 30 Minuten &gt;&gt; 7,5 ._x000a_Sie können die Anwesenheitszeit auf die Viertelstunde aufrunden." type="decimal">
+    <dataValidation sqref="E16:E43 E59:E86 E102:E129 E145:E172 E188:E215 E231:E258 E274:E301 E317:E344 E360:E387 E403:E430 E446:E473 E489:E516 E532:E559" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Eingabe beachten" error="Bitte beachten Sie das vorgegebene Eingabeformat&#10;" promptTitle="Eingabe Arbeitszeit" prompt="Geben Sie bitte als Dezimalzahl ihre Arbeitszeit (Anwesenheitszeit) am genannten Tag ein. 7 Stunden und 30 Minuten &gt;&gt; 7,5 .&#10;Sie können die Anwesenheitszeit auf die Viertelstunde aufrunden." type="decimal">
       <formula1>0</formula1>
       <formula2>24</formula2>
     </dataValidation>
@@ -19237,11 +19237,18 @@
       <formula1>" 001 - Beschreibung nicht ausreichend, 002 - Stundenangabe nicht plausibel, 003 - keine Vorlesung angeboten, 004 - keine Vorlesung angeboten, 005 - Abwesenheit, 006 - keine relevante Tätigkeit, 999 - Sonstiges"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7086614173228347" right="0.7086614173228347" top="1.181102362204725" bottom="1.181102362204725" header="0.2755905511811024" footer="0.2755905511811024"/>
+  <pageMargins left="0.7086614173228347" right="0.7086614173228347" top="1.181102362204725" bottom="1.9" header="0.2755905511811024" footer="0.2755905511811024"/>
   <pageSetup orientation="portrait" paperSize="9" scale="69" fitToHeight="0"/>
   <headerFooter>
-    <oddHeader>&amp;L_x000a__x000a_&amp;C&amp;"-,Fett"Tätigkeitsbericht _x000a_Pflichtpraktikum&amp;R_x000a_&amp;D_x000a_&amp;P von &amp;N</oddHeader>
-    <oddFooter>&amp;L&amp;"-,Standard"_x000a__x000a_Bestätigung des Ausbildungsbetriebes: _x000a__x000a__x000a__x000a__________________        __________________________________x000a_Datum                                   Unterschrift und Firmenstempel</oddFooter>
+    <oddHeader>&amp;L
+&amp;C&amp;"-,Fett"Tätigkeitsbericht 
+Pflichtpraktikum&amp;R
+&amp;D
+&amp;P von &amp;N</oddHeader>
+    <oddFooter>&amp;L&amp;"-,Standard"
+Bestätigung des Ausbildungsbetriebes: 
+_________________        _________________________________
+Datum                                   Unterschrift und Firmenstempel</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/hochschule/Hassine_3399727_Tätigkeitsnachweis.xlsx
+++ b/hochschule/Hassine_3399727_Tätigkeitsnachweis.xlsx
@@ -2543,7 +2543,7 @@
       <c r="H17" s="28" t="n"/>
       <c r="I17" s="104" t="inlineStr">
         <is>
-          <t>⟨Position im Unternehmen⟩</t>
+          <t>Konstruktion und Arbeitsvorbereitung</t>
         </is>
       </c>
       <c r="J17" s="114" t="n"/>
@@ -2608,7 +2608,7 @@
       <c r="H20" s="100" t="n"/>
       <c r="I20" s="105" t="inlineStr">
         <is>
-          <t>⟨E-Mail Betreuer⟩</t>
+          <t>amin.halloul@mw-schmidt.de</t>
         </is>
       </c>
       <c r="J20" s="114" t="n"/>
@@ -2673,7 +2673,7 @@
       <c r="H23" s="100" t="n"/>
       <c r="I23" s="104" t="inlineStr">
         <is>
-          <t>⟨Telefon Betreuer⟩</t>
+          <t>09447/9909014</t>
         </is>
       </c>
       <c r="J23" s="114" t="n"/>
@@ -3447,6 +3447,7 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.787401575" bottom="0.787401575" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" scale="79" horizontalDpi="300"/>

--- a/hochschule/Hassine_3399727_Tätigkeitsnachweis.xlsx
+++ b/hochschule/Hassine_3399727_Tätigkeitsnachweis.xlsx
@@ -4414,7 +4414,7 @@
       </c>
       <c r="D32" s="65" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E32" s="119" t="n">
@@ -4427,12 +4427,12 @@
       </c>
       <c r="G32" s="96" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nein</t>
         </is>
       </c>
       <c r="H32" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00-11:30 an der OTH, davor und danach im Betrieb. Belegungsplan erstellt: jeder der 135 Sorten einen festen, beschrifteten Platz zugeordnet. Bezugsquellen recherchiert, Ergebnisse dem Betreuer vorgestellt und eine Arbeitsanweisung für die Materialentnahme entworfen.</t>
+          <t>Belegungsplan erstellt: jeder der 135 Sorten einen festen, beschrifteten Platz zugeordnet. Bezugsquellen recherchiert, Ergebnisse dem Betreuer vorgestellt und eine Arbeitsanweisung für die Materialentnahme entworfen.</t>
         </is>
       </c>
       <c r="I32" s="86" t="n"/>
@@ -4460,7 +4460,7 @@
         </is>
       </c>
       <c r="E33" s="119" t="n">
-        <v>7.5</v>
+        <v>9.75</v>
       </c>
       <c r="F33" s="92" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="E37" s="119" t="n">
-        <v>9.75</v>
+        <v>7.75</v>
       </c>
       <c r="F37" s="92" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         </is>
       </c>
       <c r="E38" s="119" t="n">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
       <c r="F38" s="92" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         </is>
       </c>
       <c r="E39" s="119" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="F39" s="92" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="H39" s="95" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00-11:30 an der OTH, davor und danach im Betrieb. Barcode-Suche umgesetzt: Der eingescannte Code springt zum Artikel und zeigt alle Felder im Dashboard an.</t>
+          <t>Vormittags im Betrieb, ab 10:00 Vorlesung PP bis 13:15 an der OTH, danach nicht mehr im Betrieb. Barcode-Suche umgesetzt: Der eingescannte Code springt zum Artikel und zeigt alle Felder im Dashboard an.</t>
         </is>
       </c>
       <c r="I39" s="86" t="n"/>
@@ -4770,7 +4770,7 @@
         </is>
       </c>
       <c r="E41" s="119" t="n">
-        <v>7.5</v>
+        <v>7.25</v>
       </c>
       <c r="F41" s="92" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="E60" s="119" t="n">
-        <v>7.25</v>
+        <v>7.5</v>
       </c>
       <c r="F60" s="92" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="E61" s="119" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="H61" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00-11:30 an der OTH, davor und danach im Betrieb. Filterfunktion über Bezeichnung, Profil, Maß und Materialgruppe umgesetzt und getestet.</t>
+          <t>Vormittags im Betrieb, ab 10:00 Vorlesung PP bis 13:15 an der OTH, danach nicht mehr im Betrieb. Filterfunktion über Bezeichnung, Profil, Maß und Materialgruppe umgesetzt und getestet.</t>
         </is>
       </c>
       <c r="I61" s="86" t="n"/>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="E75" s="119" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
       </c>
       <c r="H75" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00-11:30 an der OTH, davor und danach im Betrieb. Material-Entnahme umgesetzt: Restlängen werden automatisch angelegt oder mit vorhandenen gleich langen Resten zusammengefasst.</t>
+          <t>Vormittags im Betrieb, ab 10:00 Vorlesung PP bis 13:15 an der OTH, danach nicht mehr im Betrieb. Material-Entnahme umgesetzt: Restlängen werden automatisch angelegt oder mit vorhandenen gleich langen Resten zusammengefasst.</t>
         </is>
       </c>
       <c r="I75" s="86" t="n"/>
@@ -6066,7 +6066,7 @@
         </is>
       </c>
       <c r="E82" s="119" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="H82" s="67" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00-11:30 an der OTH, davor und danach im Betrieb. Datenmodell aus den Excel-Blättern übernommen und die Kernfunktionen portiert: Artikel verwalten, Buchungen, Verlauf und die Material-Entnahme mit Resteverwaltung. 86 reale Artikel-Datensätze und 50 Artikelgruppen übernommen und die Übernahme kontrolliert.</t>
+          <t>Vormittags im Betrieb, ab 10:00 Vorlesung PP bis 13:15 an der OTH, danach nicht mehr im Betrieb. Datenmodell aus den Excel-Blättern übernommen und die Kernfunktionen portiert: Artikel verwalten, Buchungen, Verlauf und die Material-Entnahme mit Resteverwaltung. 86 reale Artikel-Datensätze und 50 Artikelgruppen übernommen und die Übernahme kontrolliert.</t>
         </is>
       </c>
       <c r="I82" s="86" t="n"/>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="H104" s="67" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00-11:30 und Praktikum Regelungstechnik 15:30-17:00 an der OTH, Vormittag im Betrieb. Werkzeugaufnahme fortgesetzt: Kategorien Schweißen MAG/MIG und Schweißen E-Hand vollständig erfasst.</t>
+          <t>Vorlesung PP 10:00-13:15 und Praktikum Regelungstechnik 15:30-17:00 an der OTH, Vormittag im Betrieb. Werkzeugaufnahme fortgesetzt: Kategorien Schweißen MAG/MIG und Schweißen E-Hand vollständig erfasst.</t>
         </is>
       </c>
       <c r="I104" s="86" t="n"/>
@@ -6912,7 +6912,7 @@
         </is>
       </c>
       <c r="E111" s="119" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
       </c>
       <c r="H111" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00-11:30 an der OTH, davor und danach im Betrieb. Marktrecherche zu den Werkzeugen begonnen und Richtpreise je Position gesammelt.</t>
+          <t>Vormittags im Betrieb, ab 10:00 Vorlesung PP bis 13:15 an der OTH, danach nicht mehr im Betrieb. Marktrecherche zu den Werkzeugen begonnen und Richtpreise je Position gesammelt.</t>
         </is>
       </c>
       <c r="I111" s="86" t="n"/>
@@ -7179,7 +7179,7 @@
         </is>
       </c>
       <c r="E118" s="119" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
       </c>
       <c r="H118" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00-11:30 an der OTH, davor und danach im Betrieb. Nutzwertanalyse für die Werkbank-Ausführung aufgestellt: Kriterien festgelegt und gewichtet.</t>
+          <t>Vormittags im Betrieb, ab 10:00 Vorlesung PP bis 13:15 an der OTH, danach nicht mehr im Betrieb. Nutzwertanalyse für die Werkbank-Ausführung aufgestellt: Kriterien festgelegt und gewichtet.</t>
         </is>
       </c>
       <c r="I118" s="86" t="n"/>
@@ -7458,7 +7458,7 @@
       </c>
       <c r="H125" s="67" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00-11:30 und Praktikum Regelungstechnik 15:30-17:00 an der OTH, Vormittag im Betrieb. Recherche zu Schweißtisch-Konzepten und Spannsystemen durchgeführt, Beispiele gesammelt und bewertet.</t>
+          <t>Vorlesung PP 10:00-13:15 und Praktikum Regelungstechnik 15:30-17:00 an der OTH, Vormittag im Betrieb. Recherche zu Schweißtisch-Konzepten und Spannsystemen durchgeführt, Beispiele gesammelt und bewertet.</t>
         </is>
       </c>
       <c r="I125" s="86" t="n"/>
@@ -8037,7 +8037,7 @@
       </c>
       <c r="H147" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00-11:30 und Praktikum Regelungstechnik 15:30-17:00 an der OTH, Vormittag im Betrieb. Mit der CAD-Konstruktion begonnen: Tischplatte mit Lochraster aufgebaut.</t>
+          <t>Vorlesung PP 10:00-13:15 und Praktikum Regelungstechnik 15:30-17:00 an der OTH, Vormittag im Betrieb. Mit der CAD-Konstruktion begonnen: Tischplatte mit Lochraster aufgebaut.</t>
         </is>
       </c>
       <c r="I147" s="86" t="n"/>
@@ -8290,7 +8290,7 @@
         </is>
       </c>
       <c r="E154" s="119" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
       </c>
       <c r="H154" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00-11:30 an der OTH, davor und danach im Betrieb. Kollisionen und Verfahrwege im Modell geprüft und die Führungen angepasst.</t>
+          <t>Vormittags im Betrieb, ab 10:00 Vorlesung PP bis 13:15 an der OTH, danach nicht mehr im Betrieb. Kollisionen und Verfahrwege im Modell geprüft und die Führungen angepasst.</t>
         </is>
       </c>
       <c r="I154" s="86" t="n"/>
@@ -8555,7 +8555,7 @@
         </is>
       </c>
       <c r="E161" s="119" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="H161" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00-11:30 an der OTH, davor und danach im Betrieb. Schweißgerät und Gasflasche vor Ort aufgemessen und die Maße in einer Handskizze festgehalten.</t>
+          <t>Vormittags im Betrieb, ab 10:00 Vorlesung PP bis 13:15 an der OTH, danach nicht mehr im Betrieb. Schweißgerät und Gasflasche vor Ort aufgemessen und die Maße in einer Handskizze festgehalten.</t>
         </is>
       </c>
       <c r="I161" s="86" t="n"/>
@@ -8822,7 +8822,7 @@
         </is>
       </c>
       <c r="E168" s="119" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="H168" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00-11:30 an der OTH, davor und danach im Betrieb. Zwei erste Entwürfe im CAD aufgebaut und gegenübergestellt.</t>
+          <t>Vormittags im Betrieb, ab 10:00 Vorlesung PP bis 13:15 an der OTH, danach nicht mehr im Betrieb. Zwei erste Entwürfe im CAD aufgebaut und gegenübergestellt.</t>
         </is>
       </c>
       <c r="I168" s="86" t="n"/>
@@ -9403,7 +9403,7 @@
         </is>
       </c>
       <c r="E190" s="119" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
       </c>
       <c r="H190" s="94" t="inlineStr">
         <is>
-          <t>Vorlesung PP 10:00-11:30 an der OTH, davor und danach im Betrieb. Variante B überarbeitet, sodass die Gasflasche innerhalb der Aufstandsfläche steht.</t>
+          <t>Vormittags im Betrieb, ab 10:00 Vorlesung PP bis 13:15 an der OTH, danach nicht mehr im Betrieb. Variante B überarbeitet, sodass die Gasflasche innerhalb der Aufstandsfläche steht.</t>
         </is>
       </c>
       <c r="I190" s="86" t="n"/>

--- a/hochschule/Hassine_3399727_Tätigkeitsnachweis.xlsx
+++ b/hochschule/Hassine_3399727_Tätigkeitsnachweis.xlsx
@@ -4334,7 +4334,7 @@
         </is>
       </c>
       <c r="E30" s="119" t="n">
-        <v>7.25</v>
+        <v>8</v>
       </c>
       <c r="F30" s="92" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="E32" s="119" t="n">
-        <v>7.5</v>
+        <v>8.25</v>
       </c>
       <c r="F32" s="92" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="E37" s="119" t="n">
-        <v>7.75</v>
+        <v>8.5</v>
       </c>
       <c r="F37" s="92" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         </is>
       </c>
       <c r="E38" s="119" t="n">
-        <v>7.5</v>
+        <v>8.25</v>
       </c>
       <c r="F38" s="92" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         </is>
       </c>
       <c r="E41" s="119" t="n">
-        <v>7.25</v>
+        <v>8</v>
       </c>
       <c r="F41" s="92" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="E60" s="119" t="n">
-        <v>7.5</v>
+        <v>8.25</v>
       </c>
       <c r="F60" s="92" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="E62" s="119" t="n">
-        <v>7.25</v>
+        <v>8</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="E67" s="119" t="n">
-        <v>7.5</v>
+        <v>8.25</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="H67" s="94" t="inlineStr">
         <is>
-          <t>Versand der Bestandsliste per E-Mail ergänzt und mit Testdaten geprüft.</t>
+          <t>Versand der Bestandsliste per E-Mail ergänzt: Modul erkennt automatisch Outlook, Gmail oder Apple Mail und erzeugt Betreff und Text selbst; eine Checkbox wählt zwischen Entwurf und Direktversand. Mit Testdaten geprüft.</t>
         </is>
       </c>
       <c r="I67" s="86" t="n"/>
@@ -5573,7 +5573,7 @@
         </is>
       </c>
       <c r="E69" s="119" t="n">
-        <v>7.75</v>
+        <v>8.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         </is>
       </c>
       <c r="E70" s="119" t="n">
-        <v>7.5</v>
+        <v>8.25</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="E74" s="119" t="n">
-        <v>7.25</v>
+        <v>8</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         </is>
       </c>
       <c r="E76" s="119" t="n">
-        <v>7.5</v>
+        <v>8.25</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="E77" s="119" t="n">
-        <v>7.75</v>
+        <v>8.5</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         </is>
       </c>
       <c r="E81" s="119" t="n">
-        <v>7.5</v>
+        <v>8.25</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -6107,7 +6107,7 @@
         </is>
       </c>
       <c r="E83" s="119" t="n">
-        <v>7.25</v>
+        <v>8</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -6148,7 +6148,7 @@
         </is>
       </c>
       <c r="E84" s="119" t="n">
-        <v>7.5</v>
+        <v>8.25</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         </is>
       </c>
       <c r="E103" s="119" t="n">
-        <v>7.75</v>
+        <v>8.5</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         </is>
       </c>
       <c r="E105" s="119" t="n">
-        <v>7.5</v>
+        <v>8.25</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         </is>
       </c>
       <c r="E109" s="119" t="n">
-        <v>7.25</v>
+        <v>8</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         </is>
       </c>
       <c r="E110" s="119" t="n">
-        <v>7.5</v>
+        <v>8.25</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
       </c>
       <c r="H112" s="94" t="inlineStr">
         <is>
-          <t>Marktrecherche abgeschlossen und je Kaufteil drei Preisstufen gegenübergestellt.</t>
+          <t>Marktrecherche abgeschlossen und je Kaufteil drei Preisstufen gegenübergestellt, damit die Beschaffung später ohne weitere Recherche entscheiden kann – Kostenschätzung von rund 10.030 € netto über alle sechs Aufgabenbereiche.</t>
         </is>
       </c>
       <c r="I112" s="86" t="n"/>
@@ -6994,7 +6994,7 @@
         </is>
       </c>
       <c r="E113" s="119" t="n">
-        <v>7.75</v>
+        <v>8.5</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         </is>
       </c>
       <c r="E117" s="119" t="n">
-        <v>7.5</v>
+        <v>8.25</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
       </c>
       <c r="H117" s="94" t="inlineStr">
         <is>
-          <t>Zwei weitere Layout-Varianten entwickelt und die drei Konzepte nebeneinandergestellt.</t>
+          <t>Zwei weitere Layout-Varianten entwickelt: K2 Über-Eck (seitliche Werkzeuge) und K3 Bediengang (Schweißer im ~700-mm-Gang), neben dem linearen Erstentwurf K1 nebeneinandergestellt.</t>
         </is>
       </c>
       <c r="I117" s="86" t="n"/>
@@ -7259,7 +7259,7 @@
         </is>
       </c>
       <c r="E120" s="119" t="n">
-        <v>7.25</v>
+        <v>8</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
       </c>
       <c r="H120" s="94" t="inlineStr">
         <is>
-          <t>Nutzwertanalyse für das Layout-Konzept gerechnet und die Ergebnisse ausgewertet.</t>
+          <t>Nutzwertanalyse für das Layout-Konzept gerechnet: K3 Bediengang gewinnt mit Nutzwert 4,20 vor K2 Über-Eck (3,90) und K1 Linear (3,45), braucht dafür aber am meisten Grundfläche.</t>
         </is>
       </c>
       <c r="I120" s="86" t="n"/>
@@ -7362,7 +7362,7 @@
         </is>
       </c>
       <c r="E123" s="119" t="n">
-        <v>7.5</v>
+        <v>8.25</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         </is>
       </c>
       <c r="E126" s="119" t="n">
-        <v>7.75</v>
+        <v>8.5</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         </is>
       </c>
       <c r="E127" s="119" t="n">
-        <v>7.5</v>
+        <v>8.25</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7996,7 +7996,7 @@
       </c>
       <c r="H146" s="94" t="inlineStr">
         <is>
-          <t>Marktrecherche zu Lochplatten durchgeführt, Angebote verglichen und das D16-Raster ausgewählt.</t>
+          <t>Marktrecherche zu Lochplatten durchgeführt, Angebote mit 50×50- und 100×100-Raster in 6 bis 12 mm Dicke verglichen und die Platte 800×500×12 mm im D16-System ausgewählt.</t>
         </is>
       </c>
       <c r="I146" s="86" t="n"/>
@@ -8064,7 +8064,7 @@
         </is>
       </c>
       <c r="E148" s="119" t="n">
-        <v>7.25</v>
+        <v>8</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
       </c>
       <c r="H148" s="94" t="inlineStr">
         <is>
-          <t>Oberteil konstruiert: Träger und Profile modelliert und die Teilenummern vergeben.</t>
+          <t>Oberteil konstruiert: Träger und Profile modelliert und die Teilenummern vergeben – Baugruppe 000-005-104-1 mit zwei Rohren 1500 mm, zwei Rohren 500 mm, einem Rohr 1330 mm und drei Lochplatten, 18,63 kg.</t>
         </is>
       </c>
       <c r="I148" s="86" t="n"/>
@@ -8105,7 +8105,7 @@
         </is>
       </c>
       <c r="E149" s="119" t="n">
-        <v>7.5</v>
+        <v>8.25</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="E152" s="119" t="n">
-        <v>7.25</v>
+        <v>8</v>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="H152" s="94" t="inlineStr">
         <is>
-          <t>Erweiterungssystem als Teleskop-Rahmen konstruiert, beidseitig ausziehbar.</t>
+          <t>Erweiterungssystem als Teleskop-Rahmen konstruiert, beidseitig ausziehbar: Führungsrohr 50×50×2 mit zwei beweglichen Teilen aus je zwei Rohren 40×40×2, Baugruppe 000-005-103-3 mit 6,75 kg.</t>
         </is>
       </c>
       <c r="I152" s="86" t="n"/>
@@ -8263,7 +8263,7 @@
       </c>
       <c r="H153" s="67" t="inlineStr">
         <is>
-          <t>Baugruppen zum Gesamtzusammenbau zusammengeführt und die Struktur geordnet.</t>
+          <t>Baugruppen zum Gesamtzusammenbau (000-005-200-2) zusammengeführt und die Struktur geordnet: Oberteil, Unterteil und Erweiterungssystem zu 52 Teilen mit zusammen 32,98 kg.</t>
         </is>
       </c>
       <c r="I153" s="86" t="n"/>
@@ -8473,7 +8473,7 @@
         </is>
       </c>
       <c r="E159" s="119" t="n">
-        <v>7.5</v>
+        <v>8.25</v>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
       </c>
       <c r="H159" s="94" t="inlineStr">
         <is>
-          <t>Weitere Einzelteilzeichnungen erstellt und die Schriftfelder ausgefüllt.</t>
+          <t>Weitere Einzelteilzeichnungen erstellt und die Schriftfelder ausgefüllt – der komplette Satz umfasst am Ende 15 Zeichnungsblätter für den Schweißtisch.</t>
         </is>
       </c>
       <c r="I159" s="86" t="n"/>
@@ -8610,7 +8610,7 @@
       </c>
       <c r="H162" s="94" t="inlineStr">
         <is>
-          <t>Vereinfachte CAD-Platzhalter für Gerät und Flasche erstellt, um den Bauraum abzubilden.</t>
+          <t>Vereinfachte CAD-Platzhalter für Gerät und Flasche erstellt, um den Bauraum abzubilden: roter Quader für das Schweißgerät (610×430×520 mm), oranger Zylinder für die Gasflasche (Ø220×1640 mm), dazu Grundplatte und Rollen mit 160 mm Bodenfreiheit.</t>
         </is>
       </c>
       <c r="I162" s="86" t="n"/>
@@ -8637,7 +8637,7 @@
         </is>
       </c>
       <c r="E163" s="119" t="n">
-        <v>7.75</v>
+        <v>8.5</v>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
       </c>
       <c r="H163" s="94" t="inlineStr">
         <is>
-          <t>Anforderungsliste aufgestellt: was der Wagen tragen und was er können muss.</t>
+          <t>Anforderungsliste aufgestellt: was der Wagen tragen muss (Schweißgerät, Gasflasche über 1,8 m, Brenner mit Schlauchpaket) und was er können muss (fahrbar, kippsicher, sicher geerdet).</t>
         </is>
       </c>
       <c r="I163" s="86" t="n"/>
@@ -9908,7 +9908,7 @@
       </c>
       <c r="H203" s="94" t="inlineStr">
         <is>
-          <t>Preise recherchiert und die Werkzeugliste mit 35 Positionen bepreist.</t>
+          <t>Preise recherchiert und die Werkzeugliste mit 35 Positionen bepreist: 4.825 € netto, mit 19 % MwSt. 5.742 € brutto.</t>
         </is>
       </c>
       <c r="I203" s="86" t="n"/>
@@ -10031,7 +10031,7 @@
       </c>
       <c r="H206" s="67" t="inlineStr">
         <is>
-          <t>Grundmaße der Werkbank festgelegt und mit den Ergonomienormen abgeglichen.</t>
+          <t>Grundmaße der Werkbank festgelegt (Breite 1500–2000 mm, Tiefe 600 mm, Arbeitshöhe 850–950 mm, Traglast ≥ 500 kg) und mit DIN EN ISO 14738 sowie DIN 33402-2 abgeglichen.</t>
         </is>
       </c>
       <c r="I206" s="86" t="n"/>
@@ -10175,7 +10175,7 @@
       </c>
       <c r="H210" s="67" t="inlineStr">
         <is>
-          <t>Vier Layout-Konzepte entwickelt und die Vor- und Nachteile gegenübergestellt.</t>
+          <t>Vier Layout-Konzepte entwickelt: tiefe Unterschränke, Lochwand mittig mit Hochschränken, schlanke Bank mit mobilem Wagen und durchgehende Systemwand – Vor- und Nachteile gegenübergestellt.</t>
         </is>
       </c>
       <c r="I210" s="86" t="n"/>
@@ -10257,7 +10257,7 @@
       </c>
       <c r="H212" s="67" t="inlineStr">
         <is>
-          <t>Nutzwertanalyse aufgestellt: sieben Kriterien festgelegt und gewichtet.</t>
+          <t>Nutzwertanalyse aufgestellt: sieben Kriterien festgelegt und gewichtet – Flexibilität und Anschaffungskosten mit je 20 % am höchsten, Optik/Wertigkeit mit 5 % am geringsten.</t>
         </is>
       </c>
       <c r="I212" s="86" t="n"/>

--- a/hochschule/Hassine_3399727_Tätigkeitsnachweis.xlsx
+++ b/hochschule/Hassine_3399727_Tätigkeitsnachweis.xlsx
@@ -3842,7 +3842,7 @@
       </c>
       <c r="H17" s="67" t="inlineStr">
         <is>
-          <t>Unterweisung an den Maschinen und Arbeitsplätzen durch den Betreuer. Persönliche Schutzausrüstung erhalten, Arbeitsplatz und Rechner eingerichtet, Zugänge zur CAD-Software und zu den Netzlaufwerken angelegt.</t>
+          <t>Unterweisung an den Maschinen und Arbeitsplätzen durch den Betreuer. Persönliche Schutzausrüstung erhalten und den zugewiesenen Arbeitsplatz eingerichtet.</t>
         </is>
       </c>
       <c r="I17" s="86" t="n"/>

--- a/hochschule/Hassine_3399727_Tätigkeitsnachweis.xlsx
+++ b/hochschule/Hassine_3399727_Tätigkeitsnachweis.xlsx
@@ -3997,11 +3997,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G21" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G21" s="96" t="n"/>
       <c r="H21" s="67" t="n"/>
       <c r="I21" s="86" t="n"/>
       <c r="J21" s="86" t="n"/>
@@ -4029,11 +4025,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G22" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G22" s="96" t="n"/>
       <c r="H22" s="67" t="n"/>
       <c r="I22" s="86" t="n"/>
       <c r="J22" s="86" t="n"/>
@@ -4271,11 +4263,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G28" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G28" s="96" t="n"/>
       <c r="H28" s="67" t="n"/>
       <c r="I28" s="86" t="n"/>
       <c r="J28" s="86" t="n"/>
@@ -4303,11 +4291,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G29" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G29" s="96" t="n"/>
       <c r="H29" s="67" t="n"/>
       <c r="I29" s="86" t="n"/>
       <c r="J29" s="86" t="n"/>
@@ -4509,7 +4493,7 @@
       </c>
       <c r="G34" s="96" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nein</t>
         </is>
       </c>
       <c r="H34" s="67" t="inlineStr">
@@ -4543,11 +4527,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G35" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G35" s="96" t="n"/>
       <c r="H35" s="67" t="n"/>
       <c r="I35" s="86" t="n"/>
       <c r="J35" s="86" t="n"/>
@@ -4575,11 +4555,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G36" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G36" s="96" t="n"/>
       <c r="H36" s="67" t="n"/>
       <c r="I36" s="86" t="n"/>
       <c r="J36" s="86" t="n"/>
@@ -4812,11 +4788,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G42" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G42" s="96" t="n"/>
       <c r="H42" s="67" t="n"/>
       <c r="I42" s="86" t="n"/>
       <c r="J42" s="86" t="n"/>
@@ -4843,11 +4815,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G43" s="13" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G43" s="13" t="n"/>
       <c r="H43" s="74" t="n"/>
       <c r="I43" s="86" t="n"/>
       <c r="J43" s="86" t="n"/>
@@ -5358,7 +5326,7 @@
       </c>
       <c r="G63" s="96" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nein</t>
         </is>
       </c>
       <c r="H63" s="67" t="inlineStr">
@@ -5391,11 +5359,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G64" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G64" s="96" t="n"/>
       <c r="H64" s="67" t="n"/>
       <c r="I64" s="86" t="n"/>
       <c r="J64" s="86" t="n"/>
@@ -5422,11 +5386,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G65" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G65" s="96" t="n"/>
       <c r="H65" s="67" t="n"/>
       <c r="I65" s="86" t="n"/>
       <c r="J65" s="86" t="n"/>
@@ -5459,7 +5419,7 @@
       </c>
       <c r="G66" s="96" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nein</t>
         </is>
       </c>
       <c r="H66" s="94" t="inlineStr">
@@ -5656,11 +5616,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G71" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G71" s="96" t="n"/>
       <c r="H71" s="67" t="n"/>
       <c r="I71" s="86" t="n"/>
       <c r="J71" s="86" t="n"/>
@@ -5687,11 +5643,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G72" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G72" s="96" t="n"/>
       <c r="H72" s="67" t="n"/>
       <c r="I72" s="86" t="n"/>
       <c r="J72" s="86" t="n"/>
@@ -5923,11 +5875,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G78" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G78" s="96" t="n"/>
       <c r="H78" s="67" t="n"/>
       <c r="I78" s="86" t="n"/>
       <c r="J78" s="86" t="n"/>
@@ -5954,11 +5902,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G79" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G79" s="96" t="n"/>
       <c r="H79" s="67" t="n"/>
       <c r="I79" s="86" t="n"/>
       <c r="J79" s="86" t="n"/>
@@ -6190,11 +6134,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G85" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G85" s="96" t="n"/>
       <c r="H85" s="67" t="n"/>
       <c r="I85" s="86" t="n"/>
       <c r="J85" s="86" t="n"/>
@@ -6221,11 +6161,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G86" s="13" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G86" s="13" t="n"/>
       <c r="H86" s="74" t="n"/>
       <c r="I86" s="86" t="n"/>
       <c r="J86" s="86" t="n"/>
@@ -6736,7 +6672,7 @@
       </c>
       <c r="G106" s="96" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nein</t>
         </is>
       </c>
       <c r="H106" s="67" t="inlineStr">
@@ -6769,11 +6705,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G107" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G107" s="96" t="n"/>
       <c r="H107" s="67" t="n"/>
       <c r="I107" s="86" t="n"/>
       <c r="J107" s="86" t="n"/>
@@ -6800,11 +6732,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G108" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G108" s="96" t="n"/>
       <c r="H108" s="67" t="n"/>
       <c r="I108" s="86" t="n"/>
       <c r="J108" s="86" t="n"/>
@@ -7036,11 +6964,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G114" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G114" s="96" t="n"/>
       <c r="H114" s="67" t="n"/>
       <c r="I114" s="86" t="n"/>
       <c r="J114" s="86" t="n"/>
@@ -7067,11 +6991,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G115" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G115" s="96" t="n"/>
       <c r="H115" s="67" t="n"/>
       <c r="I115" s="86" t="n"/>
       <c r="J115" s="86" t="n"/>
@@ -7227,7 +7147,7 @@
       </c>
       <c r="G119" s="96" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nein</t>
         </is>
       </c>
       <c r="H119" s="94" t="inlineStr">
@@ -7301,11 +7221,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G121" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G121" s="96" t="n"/>
       <c r="H121" s="67" t="n"/>
       <c r="I121" s="86" t="n"/>
       <c r="J121" s="86" t="n"/>
@@ -7332,11 +7248,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G122" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G122" s="96" t="n"/>
       <c r="H122" s="67" t="n"/>
       <c r="I122" s="86" t="n"/>
       <c r="J122" s="86" t="n"/>
@@ -7568,11 +7480,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G128" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G128" s="96" t="n"/>
       <c r="H128" s="67" t="n"/>
       <c r="I128" s="86" t="n"/>
       <c r="J128" s="86" t="n"/>
@@ -7599,11 +7507,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G129" s="13" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G129" s="13" t="n"/>
       <c r="H129" s="74" t="n"/>
       <c r="I129" s="86" t="n"/>
       <c r="J129" s="86" t="n"/>
@@ -7950,7 +7854,7 @@
       </c>
       <c r="G145" s="8" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nein</t>
         </is>
       </c>
       <c r="H145" s="94" t="inlineStr">
@@ -8147,11 +8051,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G150" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G150" s="96" t="n"/>
       <c r="H150" s="67" t="n"/>
       <c r="I150" s="86" t="n"/>
       <c r="J150" s="86" t="n"/>
@@ -8178,11 +8078,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G151" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G151" s="96" t="n"/>
       <c r="H151" s="67" t="n"/>
       <c r="I151" s="86" t="n"/>
       <c r="J151" s="86" t="n"/>
@@ -8338,7 +8234,7 @@
       </c>
       <c r="G155" s="96" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nein</t>
         </is>
       </c>
       <c r="H155" s="94" t="inlineStr">
@@ -8412,11 +8308,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G157" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G157" s="96" t="n"/>
       <c r="H157" s="67" t="n"/>
       <c r="I157" s="86" t="n"/>
       <c r="J157" s="86" t="n"/>
@@ -8443,11 +8335,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G158" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G158" s="96" t="n"/>
       <c r="H158" s="67" t="n"/>
       <c r="I158" s="86" t="n"/>
       <c r="J158" s="86" t="n"/>
@@ -8679,11 +8567,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G164" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G164" s="96" t="n"/>
       <c r="H164" s="67" t="n"/>
       <c r="I164" s="86" t="n"/>
       <c r="J164" s="86" t="n"/>
@@ -8710,11 +8594,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G165" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G165" s="96" t="n"/>
       <c r="H165" s="67" t="n"/>
       <c r="I165" s="86" t="n"/>
       <c r="J165" s="86" t="n"/>
@@ -8946,11 +8826,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G171" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G171" s="96" t="n"/>
       <c r="H171" s="67" t="n"/>
       <c r="I171" s="86" t="n"/>
       <c r="J171" s="86" t="n"/>
@@ -8977,11 +8853,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G172" s="13" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G172" s="13" t="n"/>
       <c r="H172" s="74" t="n"/>
       <c r="I172" s="86" t="n"/>
       <c r="J172" s="86" t="n"/>
@@ -9527,11 +9399,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G193" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G193" s="96" t="n"/>
       <c r="H193" s="67" t="n"/>
       <c r="I193" s="86" t="n"/>
       <c r="J193" s="86" t="n"/>
@@ -9558,11 +9426,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G194" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G194" s="96" t="n"/>
       <c r="H194" s="67" t="n"/>
       <c r="I194" s="86" t="n"/>
       <c r="J194" s="86" t="n"/>
@@ -9759,7 +9623,7 @@
       </c>
       <c r="G199" s="96" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nein</t>
         </is>
       </c>
       <c r="H199" s="98" t="inlineStr">
@@ -9792,11 +9656,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G200" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G200" s="96" t="n"/>
       <c r="H200" s="67" t="n"/>
       <c r="I200" s="86" t="n"/>
       <c r="J200" s="86" t="n"/>
@@ -9823,11 +9683,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G201" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G201" s="96" t="n"/>
       <c r="H201" s="67" t="n"/>
       <c r="I201" s="86" t="n"/>
       <c r="J201" s="86" t="n"/>
@@ -10059,11 +9915,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G207" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G207" s="96" t="n"/>
       <c r="H207" s="67" t="n"/>
       <c r="I207" s="86" t="n"/>
       <c r="J207" s="86" t="n"/>
@@ -10090,11 +9942,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G208" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G208" s="96" t="n"/>
       <c r="H208" s="67" t="n"/>
       <c r="I208" s="86" t="n"/>
       <c r="J208" s="86" t="n"/>
@@ -10326,11 +10174,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G214" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G214" s="96" t="n"/>
       <c r="H214" s="67" t="n"/>
       <c r="I214" s="86" t="n"/>
       <c r="J214" s="86" t="n"/>
@@ -10357,11 +10201,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G215" s="13" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G215" s="13" t="n"/>
       <c r="H215" s="74" t="n"/>
       <c r="I215" s="86" t="n"/>
       <c r="J215" s="86" t="n"/>
@@ -10907,11 +10747,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G236" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G236" s="96" t="n"/>
       <c r="H236" s="67" t="n"/>
       <c r="I236" s="86" t="n"/>
       <c r="J236" s="86" t="n"/>
@@ -10938,11 +10774,7 @@
           <t>h</t>
         </is>
       </c>
-      <c r="G237" s="96" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G237" s="96" t="n"/>
       <c r="H237" s="67" t="n"/>
       <c r="I237" s="86" t="n"/>
       <c r="J237" s="86" t="n"/>
